--- a/results/AceAds-DM-outreach-Queensland.xlsx
+++ b/results/AceAds-DM-outreach-Queensland.xlsx
@@ -31485,7 +31485,7 @@
     <row r="1">
       <c r="A1" s="10" t="inlineStr">
         <is>
-          <t>AceAds: Instagram / Facebook outreach, Brisbane</t>
+          <t>AceAds: Instagram / Facebook outreach, Queensland</t>
         </is>
       </c>
     </row>

--- a/results/AceAds-DM-outreach-Queensland.xlsx
+++ b/results/AceAds-DM-outreach-Queensland.xlsx
@@ -12,7 +12,7 @@
     <sheet name="How to work this list" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Leads'!$A$1:$S$413</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Leads'!$A$1:$S$412</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -509,7 +509,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S413"/>
+  <dimension ref="A1:S412"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -16009,12 +16009,12 @@
       </c>
       <c r="D215" s="2" t="inlineStr">
         <is>
-          <t>Sonja Griffioen - Newborn Photography</t>
+          <t>Tiny Tots Physiotherapy - Kathryn Shutt</t>
         </is>
       </c>
       <c r="E215" s="2" t="inlineStr">
         <is>
-          <t>photographer</t>
+          <t>physiotherapist</t>
         </is>
       </c>
       <c r="F215" s="2" t="inlineStr">
@@ -16030,12 +16030,12 @@
       <c r="H215" s="2" t="inlineStr"/>
       <c r="I215" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/sonjagriffioen.newborns/</t>
+          <t>https://www.facebook.com/profile.php?id=100044607326097</t>
         </is>
       </c>
       <c r="J215" s="2" t="inlineStr">
         <is>
-          <t>+61 426 987 722</t>
+          <t>+61 402 092 729</t>
         </is>
       </c>
       <c r="K215" s="2" t="inlineStr"/>
@@ -16046,7 +16046,7 @@
       </c>
       <c r="M215" s="2" t="inlineStr">
         <is>
-          <t>Hi Sonja Griffioen - Newborn Photography team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Sonja Griffioen - Newborn Photography, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
+          <t>Hi Tiny Tots Physiotherapy - Kathryn Shutt team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Tiny Tots Physiotherapy - Kathryn Shutt, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
         </is>
       </c>
       <c r="N215" s="4" t="inlineStr">
@@ -16080,12 +16080,12 @@
       </c>
       <c r="D216" s="2" t="inlineStr">
         <is>
-          <t>Tiny Tots Physiotherapy - Kathryn Shutt</t>
+          <t>Asia Canteen</t>
         </is>
       </c>
       <c r="E216" s="2" t="inlineStr">
         <is>
-          <t>physiotherapist</t>
+          <t>restaurant</t>
         </is>
       </c>
       <c r="F216" s="2" t="inlineStr">
@@ -16101,12 +16101,12 @@
       <c r="H216" s="2" t="inlineStr"/>
       <c r="I216" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/profile.php?id=100044607326097</t>
+          <t>https://www.facebook.com/people/Asia-Canteen/100063772110992/</t>
         </is>
       </c>
       <c r="J216" s="2" t="inlineStr">
         <is>
-          <t>+61 402 092 729</t>
+          <t>+61 7 3351 0668</t>
         </is>
       </c>
       <c r="K216" s="2" t="inlineStr"/>
@@ -16117,7 +16117,7 @@
       </c>
       <c r="M216" s="2" t="inlineStr">
         <is>
-          <t>Hi Tiny Tots Physiotherapy - Kathryn Shutt team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Tiny Tots Physiotherapy - Kathryn Shutt, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
+          <t>Hi Asia Canteen team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Asia Canteen, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
         </is>
       </c>
       <c r="N216" s="4" t="inlineStr">
@@ -16151,7 +16151,7 @@
       </c>
       <c r="D217" s="2" t="inlineStr">
         <is>
-          <t>Asia Canteen</t>
+          <t>Ben's Burgers</t>
         </is>
       </c>
       <c r="E217" s="2" t="inlineStr">
@@ -16172,14 +16172,10 @@
       <c r="H217" s="2" t="inlineStr"/>
       <c r="I217" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/people/Asia-Canteen/100063772110992/</t>
-        </is>
-      </c>
-      <c r="J217" s="2" t="inlineStr">
-        <is>
-          <t>+61 7 3351 0668</t>
-        </is>
-      </c>
+          <t>https://www.facebook.com/bensburgers</t>
+        </is>
+      </c>
+      <c r="J217" s="2" t="inlineStr"/>
       <c r="K217" s="2" t="inlineStr"/>
       <c r="L217" s="2" t="inlineStr">
         <is>
@@ -16188,7 +16184,7 @@
       </c>
       <c r="M217" s="2" t="inlineStr">
         <is>
-          <t>Hi Asia Canteen team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Asia Canteen, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
+          <t>Hi Ben's Burgers team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Ben's Burgers, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
         </is>
       </c>
       <c r="N217" s="4" t="inlineStr">
@@ -16222,7 +16218,7 @@
       </c>
       <c r="D218" s="2" t="inlineStr">
         <is>
-          <t>Ben's Burgers</t>
+          <t>Buncha Buncha</t>
         </is>
       </c>
       <c r="E218" s="2" t="inlineStr">
@@ -16243,7 +16239,7 @@
       <c r="H218" s="2" t="inlineStr"/>
       <c r="I218" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/bensburgers</t>
+          <t>https://m.facebook.com/BunchaBunchaQLD/</t>
         </is>
       </c>
       <c r="J218" s="2" t="inlineStr"/>
@@ -16255,7 +16251,7 @@
       </c>
       <c r="M218" s="2" t="inlineStr">
         <is>
-          <t>Hi Ben's Burgers team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Ben's Burgers, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
+          <t>Hi Buncha Buncha team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Buncha Buncha, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
         </is>
       </c>
       <c r="N218" s="4" t="inlineStr">
@@ -16289,7 +16285,7 @@
       </c>
       <c r="D219" s="2" t="inlineStr">
         <is>
-          <t>Buncha Buncha</t>
+          <t>Ho Choi</t>
         </is>
       </c>
       <c r="E219" s="2" t="inlineStr">
@@ -16310,10 +16306,14 @@
       <c r="H219" s="2" t="inlineStr"/>
       <c r="I219" s="4" t="inlineStr">
         <is>
-          <t>https://m.facebook.com/BunchaBunchaQLD/</t>
-        </is>
-      </c>
-      <c r="J219" s="2" t="inlineStr"/>
+          <t>https://www.facebook.com/p/Ho-Choi-Licensed-Restaurant-100040303334335/</t>
+        </is>
+      </c>
+      <c r="J219" s="2" t="inlineStr">
+        <is>
+          <t>+61 7 3848 3785</t>
+        </is>
+      </c>
       <c r="K219" s="2" t="inlineStr"/>
       <c r="L219" s="2" t="inlineStr">
         <is>
@@ -16322,7 +16322,7 @@
       </c>
       <c r="M219" s="2" t="inlineStr">
         <is>
-          <t>Hi Buncha Buncha team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Buncha Buncha, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
+          <t>Hi Ho Choi team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Ho Choi, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
         </is>
       </c>
       <c r="N219" s="4" t="inlineStr">
@@ -16356,7 +16356,7 @@
       </c>
       <c r="D220" s="2" t="inlineStr">
         <is>
-          <t>Ho Choi</t>
+          <t>Latin Manna</t>
         </is>
       </c>
       <c r="E220" s="2" t="inlineStr">
@@ -16377,12 +16377,12 @@
       <c r="H220" s="2" t="inlineStr"/>
       <c r="I220" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/p/Ho-Choi-Licensed-Restaurant-100040303334335/</t>
+          <t>https://www.facebook.com/LATIN.MANNA</t>
         </is>
       </c>
       <c r="J220" s="2" t="inlineStr">
         <is>
-          <t>+61 7 3848 3785</t>
+          <t>+61 414 769 609</t>
         </is>
       </c>
       <c r="K220" s="2" t="inlineStr"/>
@@ -16393,7 +16393,7 @@
       </c>
       <c r="M220" s="2" t="inlineStr">
         <is>
-          <t>Hi Ho Choi team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Ho Choi, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
+          <t>Hi Latin Manna team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Latin Manna, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
         </is>
       </c>
       <c r="N220" s="4" t="inlineStr">
@@ -16427,7 +16427,7 @@
       </c>
       <c r="D221" s="2" t="inlineStr">
         <is>
-          <t>Latin Manna</t>
+          <t>Nekoland Ramen &amp; Bar</t>
         </is>
       </c>
       <c r="E221" s="2" t="inlineStr">
@@ -16442,18 +16442,18 @@
       </c>
       <c r="G221" s="2" t="inlineStr">
         <is>
-          <t>Facebook</t>
-        </is>
-      </c>
-      <c r="H221" s="2" t="inlineStr"/>
-      <c r="I221" s="4" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/LATIN.MANNA</t>
-        </is>
-      </c>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="H221" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/nekoland.westend</t>
+        </is>
+      </c>
+      <c r="I221" s="2" t="inlineStr"/>
       <c r="J221" s="2" t="inlineStr">
         <is>
-          <t>+61 414 769 609</t>
+          <t>+61 414 771 918</t>
         </is>
       </c>
       <c r="K221" s="2" t="inlineStr"/>
@@ -16464,7 +16464,7 @@
       </c>
       <c r="M221" s="2" t="inlineStr">
         <is>
-          <t>Hi Latin Manna team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Latin Manna, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
+          <t>Hi Nekoland Ramen &amp; Bar team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Nekoland Ramen &amp; Bar, only your Instagram. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
         </is>
       </c>
       <c r="N221" s="4" t="inlineStr">
@@ -16498,7 +16498,7 @@
       </c>
       <c r="D222" s="2" t="inlineStr">
         <is>
-          <t>Nekoland Ramen &amp; Bar</t>
+          <t>Passion Sushi</t>
         </is>
       </c>
       <c r="E222" s="2" t="inlineStr">
@@ -16513,20 +16513,16 @@
       </c>
       <c r="G222" s="2" t="inlineStr">
         <is>
-          <t>Instagram</t>
-        </is>
-      </c>
-      <c r="H222" s="4" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/nekoland.westend</t>
-        </is>
-      </c>
-      <c r="I222" s="2" t="inlineStr"/>
-      <c r="J222" s="2" t="inlineStr">
-        <is>
-          <t>+61 414 771 918</t>
-        </is>
-      </c>
+          <t>Facebook</t>
+        </is>
+      </c>
+      <c r="H222" s="2" t="inlineStr"/>
+      <c r="I222" s="4" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/passionsushi.com.au</t>
+        </is>
+      </c>
+      <c r="J222" s="2" t="inlineStr"/>
       <c r="K222" s="2" t="inlineStr"/>
       <c r="L222" s="2" t="inlineStr">
         <is>
@@ -16535,7 +16531,7 @@
       </c>
       <c r="M222" s="2" t="inlineStr">
         <is>
-          <t>Hi Nekoland Ramen &amp; Bar team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Nekoland Ramen &amp; Bar, only your Instagram. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
+          <t>Hi Passion Sushi team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Passion Sushi, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
         </is>
       </c>
       <c r="N222" s="4" t="inlineStr">
@@ -16569,7 +16565,7 @@
       </c>
       <c r="D223" s="2" t="inlineStr">
         <is>
-          <t>Passion Sushi</t>
+          <t>Stickybeak</t>
         </is>
       </c>
       <c r="E223" s="2" t="inlineStr">
@@ -16584,15 +16580,15 @@
       </c>
       <c r="G223" s="2" t="inlineStr">
         <is>
-          <t>Facebook</t>
-        </is>
-      </c>
-      <c r="H223" s="2" t="inlineStr"/>
-      <c r="I223" s="4" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/passionsushi.com.au</t>
-        </is>
-      </c>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="H223" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/Stickybeakwinebar</t>
+        </is>
+      </c>
+      <c r="I223" s="2" t="inlineStr"/>
       <c r="J223" s="2" t="inlineStr"/>
       <c r="K223" s="2" t="inlineStr"/>
       <c r="L223" s="2" t="inlineStr">
@@ -16602,7 +16598,7 @@
       </c>
       <c r="M223" s="2" t="inlineStr">
         <is>
-          <t>Hi Passion Sushi team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Passion Sushi, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
+          <t>Hi Stickybeak team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Stickybeak, only your Instagram. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
         </is>
       </c>
       <c r="N223" s="4" t="inlineStr">
@@ -16636,7 +16632,7 @@
       </c>
       <c r="D224" s="2" t="inlineStr">
         <is>
-          <t>Stickybeak</t>
+          <t>The White House Waterford</t>
         </is>
       </c>
       <c r="E224" s="2" t="inlineStr">
@@ -16651,15 +16647,15 @@
       </c>
       <c r="G224" s="2" t="inlineStr">
         <is>
-          <t>Instagram</t>
-        </is>
-      </c>
-      <c r="H224" s="4" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/Stickybeakwinebar</t>
-        </is>
-      </c>
-      <c r="I224" s="2" t="inlineStr"/>
+          <t>Facebook</t>
+        </is>
+      </c>
+      <c r="H224" s="2" t="inlineStr"/>
+      <c r="I224" s="4" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/The Whitehouse Waterford</t>
+        </is>
+      </c>
       <c r="J224" s="2" t="inlineStr"/>
       <c r="K224" s="2" t="inlineStr"/>
       <c r="L224" s="2" t="inlineStr">
@@ -16669,7 +16665,7 @@
       </c>
       <c r="M224" s="2" t="inlineStr">
         <is>
-          <t>Hi Stickybeak team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Stickybeak, only your Instagram. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
+          <t>Hi The White House Waterford team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for The White House Waterford, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
         </is>
       </c>
       <c r="N224" s="4" t="inlineStr">
@@ -16703,7 +16699,7 @@
       </c>
       <c r="D225" s="2" t="inlineStr">
         <is>
-          <t>The White House Waterford</t>
+          <t>Wara Wara</t>
         </is>
       </c>
       <c r="E225" s="2" t="inlineStr">
@@ -16724,7 +16720,7 @@
       <c r="H225" s="2" t="inlineStr"/>
       <c r="I225" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/The Whitehouse Waterford</t>
+          <t>https://www.facebook.com/warawarabrisbane</t>
         </is>
       </c>
       <c r="J225" s="2" t="inlineStr"/>
@@ -16736,7 +16732,7 @@
       </c>
       <c r="M225" s="2" t="inlineStr">
         <is>
-          <t>Hi The White House Waterford team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for The White House Waterford, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
+          <t>Hi Wara Wara team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Wara Wara, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
         </is>
       </c>
       <c r="N225" s="4" t="inlineStr">
@@ -16770,12 +16766,12 @@
       </c>
       <c r="D226" s="2" t="inlineStr">
         <is>
-          <t>Wara Wara</t>
+          <t>Clove</t>
         </is>
       </c>
       <c r="E226" s="2" t="inlineStr">
         <is>
-          <t>restaurant</t>
+          <t>takeaway</t>
         </is>
       </c>
       <c r="F226" s="2" t="inlineStr">
@@ -16791,7 +16787,7 @@
       <c r="H226" s="2" t="inlineStr"/>
       <c r="I226" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/warawarabrisbane</t>
+          <t>https://facebook.com/pages/category/Restaurant/CLOVE-WEST-END-107877521487899/</t>
         </is>
       </c>
       <c r="J226" s="2" t="inlineStr"/>
@@ -16803,7 +16799,7 @@
       </c>
       <c r="M226" s="2" t="inlineStr">
         <is>
-          <t>Hi Wara Wara team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Wara Wara, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
+          <t>Hi Clove team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Clove, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
         </is>
       </c>
       <c r="N226" s="4" t="inlineStr">
@@ -16837,7 +16833,7 @@
       </c>
       <c r="D227" s="2" t="inlineStr">
         <is>
-          <t>Clove</t>
+          <t>King of the Wings</t>
         </is>
       </c>
       <c r="E227" s="2" t="inlineStr">
@@ -16858,10 +16854,14 @@
       <c r="H227" s="2" t="inlineStr"/>
       <c r="I227" s="4" t="inlineStr">
         <is>
-          <t>https://facebook.com/pages/category/Restaurant/CLOVE-WEST-END-107877521487899/</t>
-        </is>
-      </c>
-      <c r="J227" s="2" t="inlineStr"/>
+          <t>https://www.facebook.com/kingofthewingsbrisbane/</t>
+        </is>
+      </c>
+      <c r="J227" s="2" t="inlineStr">
+        <is>
+          <t>+61 7 3607 2032</t>
+        </is>
+      </c>
       <c r="K227" s="2" t="inlineStr"/>
       <c r="L227" s="2" t="inlineStr">
         <is>
@@ -16870,7 +16870,7 @@
       </c>
       <c r="M227" s="2" t="inlineStr">
         <is>
-          <t>Hi Clove team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Clove, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
+          <t>Hi King of the Wings team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for King of the Wings, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
         </is>
       </c>
       <c r="N227" s="4" t="inlineStr">
@@ -16904,7 +16904,7 @@
       </c>
       <c r="D228" s="2" t="inlineStr">
         <is>
-          <t>King of the Wings</t>
+          <t>Lily &amp; Lala Kebab</t>
         </is>
       </c>
       <c r="E228" s="2" t="inlineStr">
@@ -16925,14 +16925,10 @@
       <c r="H228" s="2" t="inlineStr"/>
       <c r="I228" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/kingofthewingsbrisbane/</t>
-        </is>
-      </c>
-      <c r="J228" s="2" t="inlineStr">
-        <is>
-          <t>+61 7 3607 2032</t>
-        </is>
-      </c>
+          <t>https://www.facebook.com/people/LilyLalas-Kebab/61568934639796/</t>
+        </is>
+      </c>
+      <c r="J228" s="2" t="inlineStr"/>
       <c r="K228" s="2" t="inlineStr"/>
       <c r="L228" s="2" t="inlineStr">
         <is>
@@ -16941,7 +16937,7 @@
       </c>
       <c r="M228" s="2" t="inlineStr">
         <is>
-          <t>Hi King of the Wings team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for King of the Wings, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
+          <t>Hi Lily &amp; Lala Kebab team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Lily &amp; Lala Kebab, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
         </is>
       </c>
       <c r="N228" s="4" t="inlineStr">
@@ -16975,7 +16971,7 @@
       </c>
       <c r="D229" s="2" t="inlineStr">
         <is>
-          <t>Lily &amp; Lala Kebab</t>
+          <t>Mount Cotton Seafood</t>
         </is>
       </c>
       <c r="E229" s="2" t="inlineStr">
@@ -16996,7 +16992,7 @@
       <c r="H229" s="2" t="inlineStr"/>
       <c r="I229" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/people/LilyLalas-Kebab/61568934639796/</t>
+          <t>https://www.facebook.com/mountcottonseafood</t>
         </is>
       </c>
       <c r="J229" s="2" t="inlineStr"/>
@@ -17008,7 +17004,7 @@
       </c>
       <c r="M229" s="2" t="inlineStr">
         <is>
-          <t>Hi Lily &amp; Lala Kebab team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Lily &amp; Lala Kebab, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
+          <t>Hi Mount Cotton Seafood team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Mount Cotton Seafood, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
         </is>
       </c>
       <c r="N229" s="4" t="inlineStr">
@@ -17042,7 +17038,7 @@
       </c>
       <c r="D230" s="2" t="inlineStr">
         <is>
-          <t>Mount Cotton Seafood</t>
+          <t>Nessie's Fish Bite</t>
         </is>
       </c>
       <c r="E230" s="2" t="inlineStr">
@@ -17063,10 +17059,14 @@
       <c r="H230" s="2" t="inlineStr"/>
       <c r="I230" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/mountcottonseafood</t>
-        </is>
-      </c>
-      <c r="J230" s="2" t="inlineStr"/>
+          <t>http://www.facebook.com/nessiesfishbite</t>
+        </is>
+      </c>
+      <c r="J230" s="2" t="inlineStr">
+        <is>
+          <t>+61 7 3491 8838</t>
+        </is>
+      </c>
       <c r="K230" s="2" t="inlineStr"/>
       <c r="L230" s="2" t="inlineStr">
         <is>
@@ -17075,7 +17075,7 @@
       </c>
       <c r="M230" s="2" t="inlineStr">
         <is>
-          <t>Hi Mount Cotton Seafood team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Mount Cotton Seafood, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
+          <t>Hi Nessie's Fish Bite team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Nessie's Fish Bite, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
         </is>
       </c>
       <c r="N230" s="4" t="inlineStr">
@@ -17109,7 +17109,7 @@
       </c>
       <c r="D231" s="2" t="inlineStr">
         <is>
-          <t>Nessie's Fish Bite</t>
+          <t>Red Hill Seafoods</t>
         </is>
       </c>
       <c r="E231" s="2" t="inlineStr">
@@ -17130,12 +17130,12 @@
       <c r="H231" s="2" t="inlineStr"/>
       <c r="I231" s="4" t="inlineStr">
         <is>
-          <t>http://www.facebook.com/nessiesfishbite</t>
+          <t>https://www.facebook.com/RedHillSeafood</t>
         </is>
       </c>
       <c r="J231" s="2" t="inlineStr">
         <is>
-          <t>+61 7 3491 8838</t>
+          <t>+61 7 3369 1424</t>
         </is>
       </c>
       <c r="K231" s="2" t="inlineStr"/>
@@ -17146,7 +17146,7 @@
       </c>
       <c r="M231" s="2" t="inlineStr">
         <is>
-          <t>Hi Nessie's Fish Bite team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Nessie's Fish Bite, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
+          <t>Hi Red Hill Seafoods team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Red Hill Seafoods, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
         </is>
       </c>
       <c r="N231" s="4" t="inlineStr">
@@ -17180,7 +17180,7 @@
       </c>
       <c r="D232" s="2" t="inlineStr">
         <is>
-          <t>Red Hill Seafoods</t>
+          <t>Rocklea Kebab and Pizza</t>
         </is>
       </c>
       <c r="E232" s="2" t="inlineStr">
@@ -17201,12 +17201,12 @@
       <c r="H232" s="2" t="inlineStr"/>
       <c r="I232" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/RedHillSeafood</t>
+          <t>https://www.facebook.com/RockleaKebabandpizza/</t>
         </is>
       </c>
       <c r="J232" s="2" t="inlineStr">
         <is>
-          <t>+61 7 3369 1424</t>
+          <t>+61 7 3162 2670</t>
         </is>
       </c>
       <c r="K232" s="2" t="inlineStr"/>
@@ -17217,7 +17217,7 @@
       </c>
       <c r="M232" s="2" t="inlineStr">
         <is>
-          <t>Hi Red Hill Seafoods team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Red Hill Seafoods, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
+          <t>Hi Rocklea Kebab and Pizza team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Rocklea Kebab and Pizza, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
         </is>
       </c>
       <c r="N232" s="4" t="inlineStr">
@@ -17251,7 +17251,7 @@
       </c>
       <c r="D233" s="2" t="inlineStr">
         <is>
-          <t>Rocklea Kebab and Pizza</t>
+          <t>The Deck</t>
         </is>
       </c>
       <c r="E233" s="2" t="inlineStr">
@@ -17272,14 +17272,10 @@
       <c r="H233" s="2" t="inlineStr"/>
       <c r="I233" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/RockleaKebabandpizza/</t>
-        </is>
-      </c>
-      <c r="J233" s="2" t="inlineStr">
-        <is>
-          <t>+61 7 3162 2670</t>
-        </is>
-      </c>
+          <t>https://www.facebook.com/thedecktakeawayfood/</t>
+        </is>
+      </c>
+      <c r="J233" s="2" t="inlineStr"/>
       <c r="K233" s="2" t="inlineStr"/>
       <c r="L233" s="2" t="inlineStr">
         <is>
@@ -17288,7 +17284,7 @@
       </c>
       <c r="M233" s="2" t="inlineStr">
         <is>
-          <t>Hi Rocklea Kebab and Pizza team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Rocklea Kebab and Pizza, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
+          <t>Hi The Deck team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for The Deck, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
         </is>
       </c>
       <c r="N233" s="4" t="inlineStr">
@@ -17322,12 +17318,12 @@
       </c>
       <c r="D234" s="2" t="inlineStr">
         <is>
-          <t>The Deck</t>
+          <t>Inksane</t>
         </is>
       </c>
       <c r="E234" s="2" t="inlineStr">
         <is>
-          <t>takeaway</t>
+          <t>tattoo studio</t>
         </is>
       </c>
       <c r="F234" s="2" t="inlineStr">
@@ -17343,10 +17339,14 @@
       <c r="H234" s="2" t="inlineStr"/>
       <c r="I234" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/thedecktakeawayfood/</t>
-        </is>
-      </c>
-      <c r="J234" s="2" t="inlineStr"/>
+          <t>https://facebook.com/inksanetattooqld/</t>
+        </is>
+      </c>
+      <c r="J234" s="2" t="inlineStr">
+        <is>
+          <t>+61 7 3172 6331</t>
+        </is>
+      </c>
       <c r="K234" s="2" t="inlineStr"/>
       <c r="L234" s="2" t="inlineStr">
         <is>
@@ -17355,7 +17355,7 @@
       </c>
       <c r="M234" s="2" t="inlineStr">
         <is>
-          <t>Hi The Deck team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for The Deck, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
+          <t>Hi Inksane team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Inksane, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
         </is>
       </c>
       <c r="N234" s="4" t="inlineStr">
@@ -17389,7 +17389,7 @@
       </c>
       <c r="D235" s="2" t="inlineStr">
         <is>
-          <t>Inksane</t>
+          <t>Save Point Tattoo</t>
         </is>
       </c>
       <c r="E235" s="2" t="inlineStr">
@@ -17410,12 +17410,12 @@
       <c r="H235" s="2" t="inlineStr"/>
       <c r="I235" s="4" t="inlineStr">
         <is>
-          <t>https://facebook.com/inksanetattooqld/</t>
+          <t>https://www.facebook.com/savepointtattoo</t>
         </is>
       </c>
       <c r="J235" s="2" t="inlineStr">
         <is>
-          <t>+61 7 3172 6331</t>
+          <t>+61 434 644 034</t>
         </is>
       </c>
       <c r="K235" s="2" t="inlineStr"/>
@@ -17426,7 +17426,7 @@
       </c>
       <c r="M235" s="2" t="inlineStr">
         <is>
-          <t>Hi Inksane team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Inksane, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
+          <t>Hi Save Point Tattoo team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Save Point Tattoo, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
         </is>
       </c>
       <c r="N235" s="4" t="inlineStr">
@@ -17460,7 +17460,7 @@
       </c>
       <c r="D236" s="2" t="inlineStr">
         <is>
-          <t>Save Point Tattoo</t>
+          <t>Stafford Tattoo</t>
         </is>
       </c>
       <c r="E236" s="2" t="inlineStr">
@@ -17481,12 +17481,12 @@
       <c r="H236" s="2" t="inlineStr"/>
       <c r="I236" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/savepointtattoo</t>
+          <t>https://www.facebook.com/st.tattoos/</t>
         </is>
       </c>
       <c r="J236" s="2" t="inlineStr">
         <is>
-          <t>+61 434 644 034</t>
+          <t>+61 7 3357 6696</t>
         </is>
       </c>
       <c r="K236" s="2" t="inlineStr"/>
@@ -17497,7 +17497,7 @@
       </c>
       <c r="M236" s="2" t="inlineStr">
         <is>
-          <t>Hi Save Point Tattoo team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Save Point Tattoo, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
+          <t>Hi Stafford Tattoo team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Stafford Tattoo, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
         </is>
       </c>
       <c r="N236" s="4" t="inlineStr">
@@ -17531,7 +17531,7 @@
       </c>
       <c r="D237" s="2" t="inlineStr">
         <is>
-          <t>Stafford Tattoo</t>
+          <t>Voodoo Tattoo</t>
         </is>
       </c>
       <c r="E237" s="2" t="inlineStr">
@@ -17552,12 +17552,12 @@
       <c r="H237" s="2" t="inlineStr"/>
       <c r="I237" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/st.tattoos/</t>
+          <t>https://www.facebook.com/Voodoo-Tattoo-193688920647994/</t>
         </is>
       </c>
       <c r="J237" s="2" t="inlineStr">
         <is>
-          <t>+61 7 3357 6696</t>
+          <t>+61 7 3801 2912</t>
         </is>
       </c>
       <c r="K237" s="2" t="inlineStr"/>
@@ -17568,7 +17568,7 @@
       </c>
       <c r="M237" s="2" t="inlineStr">
         <is>
-          <t>Hi Stafford Tattoo team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Stafford Tattoo, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
+          <t>Hi Voodoo Tattoo team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Voodoo Tattoo, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
         </is>
       </c>
       <c r="N237" s="4" t="inlineStr">
@@ -17602,17 +17602,17 @@
       </c>
       <c r="D238" s="2" t="inlineStr">
         <is>
-          <t>Voodoo Tattoo</t>
+          <t>Alloway Farm Market</t>
         </is>
       </c>
       <c r="E238" s="2" t="inlineStr">
         <is>
-          <t>tattoo studio</t>
+          <t>cafe</t>
         </is>
       </c>
       <c r="F238" s="2" t="inlineStr">
         <is>
-          <t>Brisbane</t>
+          <t>Bundaberg</t>
         </is>
       </c>
       <c r="G238" s="2" t="inlineStr">
@@ -17623,14 +17623,10 @@
       <c r="H238" s="2" t="inlineStr"/>
       <c r="I238" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/Voodoo-Tattoo-193688920647994/</t>
-        </is>
-      </c>
-      <c r="J238" s="2" t="inlineStr">
-        <is>
-          <t>+61 7 3801 2912</t>
-        </is>
-      </c>
+          <t>https://www.facebook.com/allowayfarm/</t>
+        </is>
+      </c>
+      <c r="J238" s="2" t="inlineStr"/>
       <c r="K238" s="2" t="inlineStr"/>
       <c r="L238" s="2" t="inlineStr">
         <is>
@@ -17639,7 +17635,7 @@
       </c>
       <c r="M238" s="2" t="inlineStr">
         <is>
-          <t>Hi Voodoo Tattoo team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Voodoo Tattoo, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
+          <t>Hi Alloway Farm Market team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Alloway Farm Market, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
         </is>
       </c>
       <c r="N238" s="4" t="inlineStr">
@@ -17673,12 +17669,12 @@
       </c>
       <c r="D239" s="2" t="inlineStr">
         <is>
-          <t>Alloway Farm Market</t>
+          <t>J-Elec Electrical Contractors</t>
         </is>
       </c>
       <c r="E239" s="2" t="inlineStr">
         <is>
-          <t>cafe</t>
+          <t>trades</t>
         </is>
       </c>
       <c r="F239" s="2" t="inlineStr">
@@ -17694,10 +17690,14 @@
       <c r="H239" s="2" t="inlineStr"/>
       <c r="I239" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/allowayfarm/</t>
-        </is>
-      </c>
-      <c r="J239" s="2" t="inlineStr"/>
+          <t>https://www.facebook.com/jelecelectricalcontractors/</t>
+        </is>
+      </c>
+      <c r="J239" s="2" t="inlineStr">
+        <is>
+          <t>+61 7 4154 3421</t>
+        </is>
+      </c>
       <c r="K239" s="2" t="inlineStr"/>
       <c r="L239" s="2" t="inlineStr">
         <is>
@@ -17706,7 +17706,7 @@
       </c>
       <c r="M239" s="2" t="inlineStr">
         <is>
-          <t>Hi Alloway Farm Market team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Alloway Farm Market, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
+          <t>Hi J-Elec Electrical Contractors team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for J-Elec Electrical Contractors, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
         </is>
       </c>
       <c r="N239" s="4" t="inlineStr">
@@ -17740,17 +17740,17 @@
       </c>
       <c r="D240" s="2" t="inlineStr">
         <is>
-          <t>J-Elec Electrical Contractors</t>
+          <t>Teddy Espresso</t>
         </is>
       </c>
       <c r="E240" s="2" t="inlineStr">
         <is>
-          <t>trades</t>
+          <t>cafe</t>
         </is>
       </c>
       <c r="F240" s="2" t="inlineStr">
         <is>
-          <t>Bundaberg</t>
+          <t>Cairns</t>
         </is>
       </c>
       <c r="G240" s="2" t="inlineStr">
@@ -17761,14 +17761,10 @@
       <c r="H240" s="2" t="inlineStr"/>
       <c r="I240" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/jelecelectricalcontractors/</t>
-        </is>
-      </c>
-      <c r="J240" s="2" t="inlineStr">
-        <is>
-          <t>+61 7 4154 3421</t>
-        </is>
-      </c>
+          <t>https://www.facebook.com/teddyespresso.com.au/</t>
+        </is>
+      </c>
+      <c r="J240" s="2" t="inlineStr"/>
       <c r="K240" s="2" t="inlineStr"/>
       <c r="L240" s="2" t="inlineStr">
         <is>
@@ -17777,7 +17773,7 @@
       </c>
       <c r="M240" s="2" t="inlineStr">
         <is>
-          <t>Hi J-Elec Electrical Contractors team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for J-Elec Electrical Contractors, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
+          <t>Hi Teddy Espresso team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Teddy Espresso, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
         </is>
       </c>
       <c r="N240" s="4" t="inlineStr">
@@ -17811,12 +17807,12 @@
       </c>
       <c r="D241" s="2" t="inlineStr">
         <is>
-          <t>Teddy Espresso</t>
+          <t>Iron strength power and performance</t>
         </is>
       </c>
       <c r="E241" s="2" t="inlineStr">
         <is>
-          <t>cafe</t>
+          <t>gym or studio</t>
         </is>
       </c>
       <c r="F241" s="2" t="inlineStr">
@@ -17832,10 +17828,14 @@
       <c r="H241" s="2" t="inlineStr"/>
       <c r="I241" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/teddyespresso.com.au/</t>
-        </is>
-      </c>
-      <c r="J241" s="2" t="inlineStr"/>
+          <t>https://www.facebook.com/ironstrengthpp/</t>
+        </is>
+      </c>
+      <c r="J241" s="2" t="inlineStr">
+        <is>
+          <t>+61 423 531 278</t>
+        </is>
+      </c>
       <c r="K241" s="2" t="inlineStr"/>
       <c r="L241" s="2" t="inlineStr">
         <is>
@@ -17844,7 +17844,7 @@
       </c>
       <c r="M241" s="2" t="inlineStr">
         <is>
-          <t>Hi Teddy Espresso team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Teddy Espresso, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
+          <t>Hi Iron strength power and performance team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Iron strength power and performance, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
         </is>
       </c>
       <c r="N241" s="4" t="inlineStr">
@@ -17878,12 +17878,12 @@
       </c>
       <c r="D242" s="2" t="inlineStr">
         <is>
-          <t>Iron strength power and performance</t>
+          <t>Tasty Road</t>
         </is>
       </c>
       <c r="E242" s="2" t="inlineStr">
         <is>
-          <t>gym or studio</t>
+          <t>restaurant</t>
         </is>
       </c>
       <c r="F242" s="2" t="inlineStr">
@@ -17899,14 +17899,10 @@
       <c r="H242" s="2" t="inlineStr"/>
       <c r="I242" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/ironstrengthpp/</t>
-        </is>
-      </c>
-      <c r="J242" s="2" t="inlineStr">
-        <is>
-          <t>+61 423 531 278</t>
-        </is>
-      </c>
+          <t>https://facebook.com/tastyroad</t>
+        </is>
+      </c>
+      <c r="J242" s="2" t="inlineStr"/>
       <c r="K242" s="2" t="inlineStr"/>
       <c r="L242" s="2" t="inlineStr">
         <is>
@@ -17915,7 +17911,7 @@
       </c>
       <c r="M242" s="2" t="inlineStr">
         <is>
-          <t>Hi Iron strength power and performance team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Iron strength power and performance, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
+          <t>Hi Tasty Road team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Tasty Road, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
         </is>
       </c>
       <c r="N242" s="4" t="inlineStr">
@@ -17949,17 +17945,17 @@
       </c>
       <c r="D243" s="2" t="inlineStr">
         <is>
-          <t>Tasty Road</t>
+          <t>Boulangerie Vietnam</t>
         </is>
       </c>
       <c r="E243" s="2" t="inlineStr">
         <is>
-          <t>restaurant</t>
+          <t>bakery</t>
         </is>
       </c>
       <c r="F243" s="2" t="inlineStr">
         <is>
-          <t>Cairns</t>
+          <t>Gold Coast</t>
         </is>
       </c>
       <c r="G243" s="2" t="inlineStr">
@@ -17970,10 +17966,14 @@
       <c r="H243" s="2" t="inlineStr"/>
       <c r="I243" s="4" t="inlineStr">
         <is>
-          <t>https://facebook.com/tastyroad</t>
-        </is>
-      </c>
-      <c r="J243" s="2" t="inlineStr"/>
+          <t>https://www.facebook.com/p/Boulangerie-Vietnam-100086495847018/</t>
+        </is>
+      </c>
+      <c r="J243" s="2" t="inlineStr">
+        <is>
+          <t>+61 432 747 703</t>
+        </is>
+      </c>
       <c r="K243" s="2" t="inlineStr"/>
       <c r="L243" s="2" t="inlineStr">
         <is>
@@ -17982,7 +17982,7 @@
       </c>
       <c r="M243" s="2" t="inlineStr">
         <is>
-          <t>Hi Tasty Road team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Tasty Road, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
+          <t>Hi Boulangerie Vietnam team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Boulangerie Vietnam, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
         </is>
       </c>
       <c r="N243" s="4" t="inlineStr">
@@ -18016,7 +18016,7 @@
       </c>
       <c r="D244" s="2" t="inlineStr">
         <is>
-          <t>Boulangerie Vietnam</t>
+          <t>La De Da</t>
         </is>
       </c>
       <c r="E244" s="2" t="inlineStr">
@@ -18037,12 +18037,12 @@
       <c r="H244" s="2" t="inlineStr"/>
       <c r="I244" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/p/Boulangerie-Vietnam-100086495847018/</t>
+          <t>https://facebook.com/ladedabakery/</t>
         </is>
       </c>
       <c r="J244" s="2" t="inlineStr">
         <is>
-          <t>+61 432 747 703</t>
+          <t>+61 7 5599 5688</t>
         </is>
       </c>
       <c r="K244" s="2" t="inlineStr"/>
@@ -18053,7 +18053,7 @@
       </c>
       <c r="M244" s="2" t="inlineStr">
         <is>
-          <t>Hi Boulangerie Vietnam team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Boulangerie Vietnam, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
+          <t>Hi La De Da team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for La De Da, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
         </is>
       </c>
       <c r="N244" s="4" t="inlineStr">
@@ -18087,7 +18087,7 @@
       </c>
       <c r="D245" s="2" t="inlineStr">
         <is>
-          <t>La De Da</t>
+          <t>Lakeside Bakery</t>
         </is>
       </c>
       <c r="E245" s="2" t="inlineStr">
@@ -18108,14 +18108,10 @@
       <c r="H245" s="2" t="inlineStr"/>
       <c r="I245" s="4" t="inlineStr">
         <is>
-          <t>https://facebook.com/ladedabakery/</t>
-        </is>
-      </c>
-      <c r="J245" s="2" t="inlineStr">
-        <is>
-          <t>+61 7 5599 5688</t>
-        </is>
-      </c>
+          <t>https://www.facebook.com/lakesidebakerypalmbeach</t>
+        </is>
+      </c>
+      <c r="J245" s="2" t="inlineStr"/>
       <c r="K245" s="2" t="inlineStr"/>
       <c r="L245" s="2" t="inlineStr">
         <is>
@@ -18124,7 +18120,7 @@
       </c>
       <c r="M245" s="2" t="inlineStr">
         <is>
-          <t>Hi La De Da team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for La De Da, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
+          <t>Hi Lakeside Bakery team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Lakeside Bakery, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
         </is>
       </c>
       <c r="N245" s="4" t="inlineStr">
@@ -18158,7 +18154,7 @@
       </c>
       <c r="D246" s="2" t="inlineStr">
         <is>
-          <t>Lakeside Bakery</t>
+          <t>MR Bake</t>
         </is>
       </c>
       <c r="E246" s="2" t="inlineStr">
@@ -18179,10 +18175,14 @@
       <c r="H246" s="2" t="inlineStr"/>
       <c r="I246" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/lakesidebakerypalmbeach</t>
-        </is>
-      </c>
-      <c r="J246" s="2" t="inlineStr"/>
+          <t>https://www.facebook.com/hellomrbake/</t>
+        </is>
+      </c>
+      <c r="J246" s="2" t="inlineStr">
+        <is>
+          <t>+61 419 917 489</t>
+        </is>
+      </c>
       <c r="K246" s="2" t="inlineStr"/>
       <c r="L246" s="2" t="inlineStr">
         <is>
@@ -18191,7 +18191,7 @@
       </c>
       <c r="M246" s="2" t="inlineStr">
         <is>
-          <t>Hi Lakeside Bakery team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Lakeside Bakery, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
+          <t>Hi MR Bake team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for MR Bake, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
         </is>
       </c>
       <c r="N246" s="4" t="inlineStr">
@@ -18225,7 +18225,7 @@
       </c>
       <c r="D247" s="2" t="inlineStr">
         <is>
-          <t>MR Bake</t>
+          <t>Oriental Bakery</t>
         </is>
       </c>
       <c r="E247" s="2" t="inlineStr">
@@ -18246,12 +18246,12 @@
       <c r="H247" s="2" t="inlineStr"/>
       <c r="I247" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/hellomrbake/</t>
+          <t>https://www.facebook.com/TheOrientalBakery/</t>
         </is>
       </c>
       <c r="J247" s="2" t="inlineStr">
         <is>
-          <t>+61 419 917 489</t>
+          <t>+61 7 5578 5247</t>
         </is>
       </c>
       <c r="K247" s="2" t="inlineStr"/>
@@ -18262,7 +18262,7 @@
       </c>
       <c r="M247" s="2" t="inlineStr">
         <is>
-          <t>Hi MR Bake team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for MR Bake, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
+          <t>Hi Oriental Bakery team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Oriental Bakery, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
         </is>
       </c>
       <c r="N247" s="4" t="inlineStr">
@@ -18296,7 +18296,7 @@
       </c>
       <c r="D248" s="2" t="inlineStr">
         <is>
-          <t>Oriental Bakery</t>
+          <t>Pan 200 Daily Bakery</t>
         </is>
       </c>
       <c r="E248" s="2" t="inlineStr">
@@ -18317,12 +18317,12 @@
       <c r="H248" s="2" t="inlineStr"/>
       <c r="I248" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/TheOrientalBakery/</t>
+          <t>https://www.facebook.com/people/Pan-200-Daily-Bakery/100077636797482/</t>
         </is>
       </c>
       <c r="J248" s="2" t="inlineStr">
         <is>
-          <t>+61 7 5578 5247</t>
+          <t>+61 468 745 122</t>
         </is>
       </c>
       <c r="K248" s="2" t="inlineStr"/>
@@ -18333,7 +18333,7 @@
       </c>
       <c r="M248" s="2" t="inlineStr">
         <is>
-          <t>Hi Oriental Bakery team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Oriental Bakery, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
+          <t>Hi Pan 200 Daily Bakery team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Pan 200 Daily Bakery, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
         </is>
       </c>
       <c r="N248" s="4" t="inlineStr">
@@ -18367,12 +18367,12 @@
       </c>
       <c r="D249" s="2" t="inlineStr">
         <is>
-          <t>Pan 200 Daily Bakery</t>
+          <t>Madocke Beer Brewing Co</t>
         </is>
       </c>
       <c r="E249" s="2" t="inlineStr">
         <is>
-          <t>bakery</t>
+          <t>bar or pub</t>
         </is>
       </c>
       <c r="F249" s="2" t="inlineStr">
@@ -18388,14 +18388,10 @@
       <c r="H249" s="2" t="inlineStr"/>
       <c r="I249" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/people/Pan-200-Daily-Bakery/100077636797482/</t>
-        </is>
-      </c>
-      <c r="J249" s="2" t="inlineStr">
-        <is>
-          <t>+61 468 745 122</t>
-        </is>
-      </c>
+          <t>https://www.facebook.com/madockebeer/</t>
+        </is>
+      </c>
+      <c r="J249" s="2" t="inlineStr"/>
       <c r="K249" s="2" t="inlineStr"/>
       <c r="L249" s="2" t="inlineStr">
         <is>
@@ -18404,7 +18400,7 @@
       </c>
       <c r="M249" s="2" t="inlineStr">
         <is>
-          <t>Hi Pan 200 Daily Bakery team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Pan 200 Daily Bakery, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
+          <t>Hi Madocke Beer Brewing Co team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Madocke Beer Brewing Co, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
         </is>
       </c>
       <c r="N249" s="4" t="inlineStr">
@@ -18438,12 +18434,12 @@
       </c>
       <c r="D250" s="2" t="inlineStr">
         <is>
-          <t>Madocke Beer Brewing Co</t>
+          <t>5th Avenue Hair</t>
         </is>
       </c>
       <c r="E250" s="2" t="inlineStr">
         <is>
-          <t>bar or pub</t>
+          <t>barber or hairdresser</t>
         </is>
       </c>
       <c r="F250" s="2" t="inlineStr">
@@ -18459,7 +18455,7 @@
       <c r="H250" s="2" t="inlineStr"/>
       <c r="I250" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/madockebeer/</t>
+          <t>https://www.facebook.com/people/5th-Avenue-Hair-Palm-Beach/100090549709595/</t>
         </is>
       </c>
       <c r="J250" s="2" t="inlineStr"/>
@@ -18471,7 +18467,7 @@
       </c>
       <c r="M250" s="2" t="inlineStr">
         <is>
-          <t>Hi Madocke Beer Brewing Co team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Madocke Beer Brewing Co, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
+          <t>Hi 5th Avenue Hair team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for 5th Avenue Hair, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
         </is>
       </c>
       <c r="N250" s="4" t="inlineStr">
@@ -18505,7 +18501,7 @@
       </c>
       <c r="D251" s="2" t="inlineStr">
         <is>
-          <t>5th Avenue Hair</t>
+          <t>Barber &amp; Capelli Co</t>
         </is>
       </c>
       <c r="E251" s="2" t="inlineStr">
@@ -18526,10 +18522,14 @@
       <c r="H251" s="2" t="inlineStr"/>
       <c r="I251" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/people/5th-Avenue-Hair-Palm-Beach/100090549709595/</t>
-        </is>
-      </c>
-      <c r="J251" s="2" t="inlineStr"/>
+          <t>https://facebook.com/barberandcapelli</t>
+        </is>
+      </c>
+      <c r="J251" s="2" t="inlineStr">
+        <is>
+          <t>+61 473 948 785</t>
+        </is>
+      </c>
       <c r="K251" s="2" t="inlineStr"/>
       <c r="L251" s="2" t="inlineStr">
         <is>
@@ -18538,7 +18538,7 @@
       </c>
       <c r="M251" s="2" t="inlineStr">
         <is>
-          <t>Hi 5th Avenue Hair team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for 5th Avenue Hair, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
+          <t>Hi Barber &amp; Capelli Co team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Barber &amp; Capelli Co, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
         </is>
       </c>
       <c r="N251" s="4" t="inlineStr">
@@ -18572,7 +18572,7 @@
       </c>
       <c r="D252" s="2" t="inlineStr">
         <is>
-          <t>Barber &amp; Capelli Co</t>
+          <t>Bimbos Hair</t>
         </is>
       </c>
       <c r="E252" s="2" t="inlineStr">
@@ -18587,18 +18587,22 @@
       </c>
       <c r="G252" s="2" t="inlineStr">
         <is>
-          <t>Facebook</t>
-        </is>
-      </c>
-      <c r="H252" s="2" t="inlineStr"/>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="H252" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/bimbos.gc/</t>
+        </is>
+      </c>
       <c r="I252" s="4" t="inlineStr">
         <is>
-          <t>https://facebook.com/barberandcapelli</t>
+          <t>https://www.facebook.com/p/Blondie-hair-co-100078309943317/</t>
         </is>
       </c>
       <c r="J252" s="2" t="inlineStr">
         <is>
-          <t>+61 473 948 785</t>
+          <t>+61 7 5598 2355</t>
         </is>
       </c>
       <c r="K252" s="2" t="inlineStr"/>
@@ -18609,7 +18613,7 @@
       </c>
       <c r="M252" s="2" t="inlineStr">
         <is>
-          <t>Hi Barber &amp; Capelli Co team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Barber &amp; Capelli Co, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
+          <t>Hi Bimbos Hair team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Bimbos Hair, only your Instagram. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
         </is>
       </c>
       <c r="N252" s="4" t="inlineStr">
@@ -18643,7 +18647,7 @@
       </c>
       <c r="D253" s="2" t="inlineStr">
         <is>
-          <t>Bimbos Hair</t>
+          <t>Brazabarber</t>
         </is>
       </c>
       <c r="E253" s="2" t="inlineStr">
@@ -18658,22 +18662,18 @@
       </c>
       <c r="G253" s="2" t="inlineStr">
         <is>
-          <t>Instagram</t>
-        </is>
-      </c>
-      <c r="H253" s="4" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/bimbos.gc/</t>
-        </is>
-      </c>
+          <t>Facebook</t>
+        </is>
+      </c>
+      <c r="H253" s="2" t="inlineStr"/>
       <c r="I253" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/p/Blondie-hair-co-100078309943317/</t>
+          <t>https://www.facebook.com/brazabarbergc/about/</t>
         </is>
       </c>
       <c r="J253" s="2" t="inlineStr">
         <is>
-          <t>+61 7 5598 2355</t>
+          <t>+61 412 399 950</t>
         </is>
       </c>
       <c r="K253" s="2" t="inlineStr"/>
@@ -18684,7 +18684,7 @@
       </c>
       <c r="M253" s="2" t="inlineStr">
         <is>
-          <t>Hi Bimbos Hair team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Bimbos Hair, only your Instagram. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
+          <t>Hi Brazabarber team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Brazabarber, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
         </is>
       </c>
       <c r="N253" s="4" t="inlineStr">
@@ -18718,7 +18718,7 @@
       </c>
       <c r="D254" s="2" t="inlineStr">
         <is>
-          <t>Brazabarber</t>
+          <t>Colour Nation</t>
         </is>
       </c>
       <c r="E254" s="2" t="inlineStr">
@@ -18739,12 +18739,12 @@
       <c r="H254" s="2" t="inlineStr"/>
       <c r="I254" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/brazabarbergc/about/</t>
+          <t>https://www.facebook.com/colournationpalmbeach/</t>
         </is>
       </c>
       <c r="J254" s="2" t="inlineStr">
         <is>
-          <t>+61 412 399 950</t>
+          <t>+61 7 5525 6444</t>
         </is>
       </c>
       <c r="K254" s="2" t="inlineStr"/>
@@ -18755,7 +18755,7 @@
       </c>
       <c r="M254" s="2" t="inlineStr">
         <is>
-          <t>Hi Brazabarber team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Brazabarber, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
+          <t>Hi Colour Nation team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Colour Nation, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
         </is>
       </c>
       <c r="N254" s="4" t="inlineStr">
@@ -18789,7 +18789,7 @@
       </c>
       <c r="D255" s="2" t="inlineStr">
         <is>
-          <t>Colour Nation</t>
+          <t>Get Smart Hair Body &amp; Soul</t>
         </is>
       </c>
       <c r="E255" s="2" t="inlineStr">
@@ -18810,12 +18810,12 @@
       <c r="H255" s="2" t="inlineStr"/>
       <c r="I255" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/colournationpalmbeach/</t>
+          <t>https://www.facebook.com/getsmarthairbodysoul/</t>
         </is>
       </c>
       <c r="J255" s="2" t="inlineStr">
         <is>
-          <t>+61 7 5525 6444</t>
+          <t>+61 7 5576 1770</t>
         </is>
       </c>
       <c r="K255" s="2" t="inlineStr"/>
@@ -18826,7 +18826,7 @@
       </c>
       <c r="M255" s="2" t="inlineStr">
         <is>
-          <t>Hi Colour Nation team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Colour Nation, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
+          <t>Hi Get Smart Hair Body &amp; Soul team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Get Smart Hair Body &amp; Soul, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
         </is>
       </c>
       <c r="N255" s="4" t="inlineStr">
@@ -18860,7 +18860,7 @@
       </c>
       <c r="D256" s="2" t="inlineStr">
         <is>
-          <t>Get Smart Hair Body &amp; Soul</t>
+          <t>Hair Affair</t>
         </is>
       </c>
       <c r="E256" s="2" t="inlineStr">
@@ -18881,12 +18881,12 @@
       <c r="H256" s="2" t="inlineStr"/>
       <c r="I256" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/getsmarthairbodysoul/</t>
+          <t>https://www.facebook.com/HairAffairBurleigh/</t>
         </is>
       </c>
       <c r="J256" s="2" t="inlineStr">
         <is>
-          <t>+61 7 5576 1770</t>
+          <t>+61 7 5535 2405</t>
         </is>
       </c>
       <c r="K256" s="2" t="inlineStr"/>
@@ -18897,7 +18897,7 @@
       </c>
       <c r="M256" s="2" t="inlineStr">
         <is>
-          <t>Hi Get Smart Hair Body &amp; Soul team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Get Smart Hair Body &amp; Soul, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
+          <t>Hi Hair Affair team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Hair Affair, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
         </is>
       </c>
       <c r="N256" s="4" t="inlineStr">
@@ -18931,7 +18931,7 @@
       </c>
       <c r="D257" s="2" t="inlineStr">
         <is>
-          <t>Hair Affair</t>
+          <t>Hair by Serena</t>
         </is>
       </c>
       <c r="E257" s="2" t="inlineStr">
@@ -18952,12 +18952,12 @@
       <c r="H257" s="2" t="inlineStr"/>
       <c r="I257" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/HairAffairBurleigh/</t>
+          <t>https://www.facebook.com/hairbyserena.goldcoast/</t>
         </is>
       </c>
       <c r="J257" s="2" t="inlineStr">
         <is>
-          <t>+61 7 5535 2405</t>
+          <t>+61 424 517 323</t>
         </is>
       </c>
       <c r="K257" s="2" t="inlineStr"/>
@@ -18968,7 +18968,7 @@
       </c>
       <c r="M257" s="2" t="inlineStr">
         <is>
-          <t>Hi Hair Affair team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Hair Affair, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
+          <t>Hi Hair by Serena team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Hair by Serena, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
         </is>
       </c>
       <c r="N257" s="4" t="inlineStr">
@@ -19002,7 +19002,7 @@
       </c>
       <c r="D258" s="2" t="inlineStr">
         <is>
-          <t>Hair by Serena</t>
+          <t>Intro Hairdressing</t>
         </is>
       </c>
       <c r="E258" s="2" t="inlineStr">
@@ -19023,12 +19023,12 @@
       <c r="H258" s="2" t="inlineStr"/>
       <c r="I258" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/hairbyserena.goldcoast/</t>
+          <t>https://www.facebook.com/Intro-Hair-Burleigh-1626887570895425/</t>
         </is>
       </c>
       <c r="J258" s="2" t="inlineStr">
         <is>
-          <t>+61 424 517 323</t>
+          <t>+61 7 5535 6625</t>
         </is>
       </c>
       <c r="K258" s="2" t="inlineStr"/>
@@ -19039,7 +19039,7 @@
       </c>
       <c r="M258" s="2" t="inlineStr">
         <is>
-          <t>Hi Hair by Serena team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Hair by Serena, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
+          <t>Hi Intro Hairdressing team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Intro Hairdressing, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
         </is>
       </c>
       <c r="N258" s="4" t="inlineStr">
@@ -19073,7 +19073,7 @@
       </c>
       <c r="D259" s="2" t="inlineStr">
         <is>
-          <t>Intro Hairdressing</t>
+          <t>Jeannie's Barber Shop</t>
         </is>
       </c>
       <c r="E259" s="2" t="inlineStr">
@@ -19094,12 +19094,12 @@
       <c r="H259" s="2" t="inlineStr"/>
       <c r="I259" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/Intro-Hair-Burleigh-1626887570895425/</t>
+          <t>https://www.facebook.com/jeanniesbarbershop/</t>
         </is>
       </c>
       <c r="J259" s="2" t="inlineStr">
         <is>
-          <t>+61 7 5535 6625</t>
+          <t>+61 427 019 157</t>
         </is>
       </c>
       <c r="K259" s="2" t="inlineStr"/>
@@ -19110,7 +19110,7 @@
       </c>
       <c r="M259" s="2" t="inlineStr">
         <is>
-          <t>Hi Intro Hairdressing team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Intro Hairdressing, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
+          <t>Hi Jeannie's Barber Shop team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Jeannie's Barber Shop, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
         </is>
       </c>
       <c r="N259" s="4" t="inlineStr">
@@ -19144,7 +19144,7 @@
       </c>
       <c r="D260" s="2" t="inlineStr">
         <is>
-          <t>Jeannie's Barber Shop</t>
+          <t>Keli's Kuts</t>
         </is>
       </c>
       <c r="E260" s="2" t="inlineStr">
@@ -19165,12 +19165,12 @@
       <c r="H260" s="2" t="inlineStr"/>
       <c r="I260" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/jeanniesbarbershop/</t>
+          <t>https://www.facebook.com/KelisKutz/</t>
         </is>
       </c>
       <c r="J260" s="2" t="inlineStr">
         <is>
-          <t>+61 427 019 157</t>
+          <t>+61 7 5554 6969</t>
         </is>
       </c>
       <c r="K260" s="2" t="inlineStr"/>
@@ -19181,7 +19181,7 @@
       </c>
       <c r="M260" s="2" t="inlineStr">
         <is>
-          <t>Hi Jeannie's Barber Shop team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Jeannie's Barber Shop, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
+          <t>Hi Keli's Kuts team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Keli's Kuts, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
         </is>
       </c>
       <c r="N260" s="4" t="inlineStr">
@@ -19215,7 +19215,7 @@
       </c>
       <c r="D261" s="2" t="inlineStr">
         <is>
-          <t>Keli's Kuts</t>
+          <t>Love is in the hair</t>
         </is>
       </c>
       <c r="E261" s="2" t="inlineStr">
@@ -19236,12 +19236,12 @@
       <c r="H261" s="2" t="inlineStr"/>
       <c r="I261" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/KelisKutz/</t>
+          <t>https://www.facebook.com/loveisinthehairhairsalon/</t>
         </is>
       </c>
       <c r="J261" s="2" t="inlineStr">
         <is>
-          <t>+61 7 5554 6969</t>
+          <t>+61 429 828 254</t>
         </is>
       </c>
       <c r="K261" s="2" t="inlineStr"/>
@@ -19252,7 +19252,7 @@
       </c>
       <c r="M261" s="2" t="inlineStr">
         <is>
-          <t>Hi Keli's Kuts team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Keli's Kuts, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
+          <t>Hi Love is in the hair team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Love is in the hair, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
         </is>
       </c>
       <c r="N261" s="4" t="inlineStr">
@@ -19286,7 +19286,7 @@
       </c>
       <c r="D262" s="2" t="inlineStr">
         <is>
-          <t>Love is in the hair</t>
+          <t>Newlengths Hairdressing</t>
         </is>
       </c>
       <c r="E262" s="2" t="inlineStr">
@@ -19307,12 +19307,12 @@
       <c r="H262" s="2" t="inlineStr"/>
       <c r="I262" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/loveisinthehairhairsalon/</t>
+          <t>https://www.facebook.com/NewlengthsNobbyBeach/</t>
         </is>
       </c>
       <c r="J262" s="2" t="inlineStr">
         <is>
-          <t>+61 429 828 254</t>
+          <t>+61 427 201 006</t>
         </is>
       </c>
       <c r="K262" s="2" t="inlineStr"/>
@@ -19323,7 +19323,7 @@
       </c>
       <c r="M262" s="2" t="inlineStr">
         <is>
-          <t>Hi Love is in the hair team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Love is in the hair, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
+          <t>Hi Newlengths Hairdressing team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Newlengths Hairdressing, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
         </is>
       </c>
       <c r="N262" s="4" t="inlineStr">
@@ -19357,7 +19357,7 @@
       </c>
       <c r="D263" s="2" t="inlineStr">
         <is>
-          <t>Newlengths Hairdressing</t>
+          <t>Old Wiley's Barbershop</t>
         </is>
       </c>
       <c r="E263" s="2" t="inlineStr">
@@ -19378,14 +19378,10 @@
       <c r="H263" s="2" t="inlineStr"/>
       <c r="I263" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/NewlengthsNobbyBeach/</t>
-        </is>
-      </c>
-      <c r="J263" s="2" t="inlineStr">
-        <is>
-          <t>+61 427 201 006</t>
-        </is>
-      </c>
+          <t>https://www.facebook.com/p/Old-Wileys-Barbershop-100063607865296/</t>
+        </is>
+      </c>
+      <c r="J263" s="2" t="inlineStr"/>
       <c r="K263" s="2" t="inlineStr"/>
       <c r="L263" s="2" t="inlineStr">
         <is>
@@ -19394,7 +19390,7 @@
       </c>
       <c r="M263" s="2" t="inlineStr">
         <is>
-          <t>Hi Newlengths Hairdressing team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Newlengths Hairdressing, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
+          <t>Hi Old Wiley's Barbershop team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Old Wiley's Barbershop, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
         </is>
       </c>
       <c r="N263" s="4" t="inlineStr">
@@ -19428,7 +19424,7 @@
       </c>
       <c r="D264" s="2" t="inlineStr">
         <is>
-          <t>Old Wiley's Barbershop</t>
+          <t>Rachael's Hair Studio</t>
         </is>
       </c>
       <c r="E264" s="2" t="inlineStr">
@@ -19449,10 +19445,14 @@
       <c r="H264" s="2" t="inlineStr"/>
       <c r="I264" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/p/Old-Wileys-Barbershop-100063607865296/</t>
-        </is>
-      </c>
-      <c r="J264" s="2" t="inlineStr"/>
+          <t>https://www.facebook.com/profile.php?id=100063804390042</t>
+        </is>
+      </c>
+      <c r="J264" s="2" t="inlineStr">
+        <is>
+          <t>+61 7 5536 2737</t>
+        </is>
+      </c>
       <c r="K264" s="2" t="inlineStr"/>
       <c r="L264" s="2" t="inlineStr">
         <is>
@@ -19461,7 +19461,7 @@
       </c>
       <c r="M264" s="2" t="inlineStr">
         <is>
-          <t>Hi Old Wiley's Barbershop team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Old Wiley's Barbershop, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
+          <t>Hi Rachael's Hair Studio team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Rachael's Hair Studio, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
         </is>
       </c>
       <c r="N264" s="4" t="inlineStr">
@@ -19495,7 +19495,7 @@
       </c>
       <c r="D265" s="2" t="inlineStr">
         <is>
-          <t>Rachael's Hair Studio</t>
+          <t>Saltydogs Barber Shop</t>
         </is>
       </c>
       <c r="E265" s="2" t="inlineStr">
@@ -19516,12 +19516,12 @@
       <c r="H265" s="2" t="inlineStr"/>
       <c r="I265" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/profile.php?id=100063804390042</t>
+          <t>https://www.facebook.com/people/Salty-dogs-barber-shop/100050556597140/</t>
         </is>
       </c>
       <c r="J265" s="2" t="inlineStr">
         <is>
-          <t>+61 7 5536 2737</t>
+          <t>+61 414 825 368</t>
         </is>
       </c>
       <c r="K265" s="2" t="inlineStr"/>
@@ -19532,7 +19532,7 @@
       </c>
       <c r="M265" s="2" t="inlineStr">
         <is>
-          <t>Hi Rachael's Hair Studio team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Rachael's Hair Studio, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
+          <t>Hi Saltydogs Barber Shop team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Saltydogs Barber Shop, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
         </is>
       </c>
       <c r="N265" s="4" t="inlineStr">
@@ -19566,7 +19566,7 @@
       </c>
       <c r="D266" s="2" t="inlineStr">
         <is>
-          <t>Saltydogs Barber Shop</t>
+          <t>Style Addict</t>
         </is>
       </c>
       <c r="E266" s="2" t="inlineStr">
@@ -19581,20 +19581,16 @@
       </c>
       <c r="G266" s="2" t="inlineStr">
         <is>
-          <t>Facebook</t>
-        </is>
-      </c>
-      <c r="H266" s="2" t="inlineStr"/>
-      <c r="I266" s="4" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/people/Salty-dogs-barber-shop/100050556597140/</t>
-        </is>
-      </c>
-      <c r="J266" s="2" t="inlineStr">
-        <is>
-          <t>+61 414 825 368</t>
-        </is>
-      </c>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="H266" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/styleaddict_hairmastery/?hl=en</t>
+        </is>
+      </c>
+      <c r="I266" s="2" t="inlineStr"/>
+      <c r="J266" s="2" t="inlineStr"/>
       <c r="K266" s="2" t="inlineStr"/>
       <c r="L266" s="2" t="inlineStr">
         <is>
@@ -19603,7 +19599,7 @@
       </c>
       <c r="M266" s="2" t="inlineStr">
         <is>
-          <t>Hi Saltydogs Barber Shop team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Saltydogs Barber Shop, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
+          <t>Hi Style Addict team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Style Addict, only your Instagram. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
         </is>
       </c>
       <c r="N266" s="4" t="inlineStr">
@@ -19632,12 +19628,12 @@
       </c>
       <c r="C267" s="2" t="inlineStr">
         <is>
-          <t>No website found</t>
+          <t>Site shows an error</t>
         </is>
       </c>
       <c r="D267" s="2" t="inlineStr">
         <is>
-          <t>Style Addict</t>
+          <t>This studio&amp;co</t>
         </is>
       </c>
       <c r="E267" s="2" t="inlineStr">
@@ -19657,20 +19653,32 @@
       </c>
       <c r="H267" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/styleaddict_hairmastery/?hl=en</t>
-        </is>
-      </c>
-      <c r="I267" s="2" t="inlineStr"/>
-      <c r="J267" s="2" t="inlineStr"/>
-      <c r="K267" s="2" t="inlineStr"/>
+          <t>https://instagram.com/this.studioandco</t>
+        </is>
+      </c>
+      <c r="I267" s="4" t="inlineStr">
+        <is>
+          <t>https://facebook.com/this.studioandco</t>
+        </is>
+      </c>
+      <c r="J267" s="2" t="inlineStr">
+        <is>
+          <t>+61 402 100 721</t>
+        </is>
+      </c>
+      <c r="K267" s="4" t="inlineStr">
+        <is>
+          <t>https://thisstudioandco.com.au</t>
+        </is>
+      </c>
       <c r="L267" s="2" t="inlineStr">
         <is>
-          <t>no website listed, only social media (verify on Google Maps)</t>
+          <t>homepage shows an error page (HTTP 404)</t>
         </is>
       </c>
       <c r="M267" s="2" t="inlineStr">
         <is>
-          <t>Hi Style Addict team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Style Addict, only your Instagram. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
+          <t>Hi This studio&amp;co team! [one real detail from their page]. We're AceAds, a web design studio. We noticed your website was showing an error page when we tried it. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
         </is>
       </c>
       <c r="N267" s="4" t="inlineStr">
@@ -19699,12 +19707,12 @@
       </c>
       <c r="C268" s="2" t="inlineStr">
         <is>
-          <t>Site shows an error</t>
+          <t>No website found</t>
         </is>
       </c>
       <c r="D268" s="2" t="inlineStr">
         <is>
-          <t>This studio&amp;co</t>
+          <t>Zina Hair Studio</t>
         </is>
       </c>
       <c r="E268" s="2" t="inlineStr">
@@ -19719,37 +19727,29 @@
       </c>
       <c r="G268" s="2" t="inlineStr">
         <is>
-          <t>Instagram</t>
-        </is>
-      </c>
-      <c r="H268" s="4" t="inlineStr">
-        <is>
-          <t>https://instagram.com/this.studioandco</t>
-        </is>
-      </c>
+          <t>Facebook</t>
+        </is>
+      </c>
+      <c r="H268" s="2" t="inlineStr"/>
       <c r="I268" s="4" t="inlineStr">
         <is>
-          <t>https://facebook.com/this.studioandco</t>
+          <t>https://www.facebook.com/zinahairstudio/</t>
         </is>
       </c>
       <c r="J268" s="2" t="inlineStr">
         <is>
-          <t>+61 402 100 721</t>
-        </is>
-      </c>
-      <c r="K268" s="4" t="inlineStr">
-        <is>
-          <t>https://thisstudioandco.com.au</t>
-        </is>
-      </c>
+          <t>+61 410 105 180</t>
+        </is>
+      </c>
+      <c r="K268" s="2" t="inlineStr"/>
       <c r="L268" s="2" t="inlineStr">
         <is>
-          <t>homepage shows an error page (HTTP 404)</t>
+          <t>no website listed, only social media (verify on Google Maps)</t>
         </is>
       </c>
       <c r="M268" s="2" t="inlineStr">
         <is>
-          <t>Hi This studio&amp;co team! [one real detail from their page]. We're AceAds, a web design studio. We noticed your website was showing an error page when we tried it. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
+          <t>Hi Zina Hair Studio team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Zina Hair Studio, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
         </is>
       </c>
       <c r="N268" s="4" t="inlineStr">
@@ -19783,12 +19783,12 @@
       </c>
       <c r="D269" s="2" t="inlineStr">
         <is>
-          <t>Zina Hair Studio</t>
+          <t>LV lashes &amp; brows</t>
         </is>
       </c>
       <c r="E269" s="2" t="inlineStr">
         <is>
-          <t>barber or hairdresser</t>
+          <t>beauty salon</t>
         </is>
       </c>
       <c r="F269" s="2" t="inlineStr">
@@ -19798,18 +19798,18 @@
       </c>
       <c r="G269" s="2" t="inlineStr">
         <is>
-          <t>Facebook</t>
-        </is>
-      </c>
-      <c r="H269" s="2" t="inlineStr"/>
-      <c r="I269" s="4" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/zinahairstudio/</t>
-        </is>
-      </c>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="H269" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/lv_lashes.and.brows/</t>
+        </is>
+      </c>
+      <c r="I269" s="2" t="inlineStr"/>
       <c r="J269" s="2" t="inlineStr">
         <is>
-          <t>+61 410 105 180</t>
+          <t>+61 450 553 112</t>
         </is>
       </c>
       <c r="K269" s="2" t="inlineStr"/>
@@ -19820,7 +19820,7 @@
       </c>
       <c r="M269" s="2" t="inlineStr">
         <is>
-          <t>Hi Zina Hair Studio team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Zina Hair Studio, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
+          <t>Hi LV lashes &amp; brows team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for LV lashes &amp; brows, only your Instagram. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
         </is>
       </c>
       <c r="N269" s="4" t="inlineStr">
@@ -19854,7 +19854,7 @@
       </c>
       <c r="D270" s="2" t="inlineStr">
         <is>
-          <t>LV lashes &amp; brows</t>
+          <t>The Courtyard Co</t>
         </is>
       </c>
       <c r="E270" s="2" t="inlineStr">
@@ -19869,18 +19869,18 @@
       </c>
       <c r="G270" s="2" t="inlineStr">
         <is>
-          <t>Instagram</t>
-        </is>
-      </c>
-      <c r="H270" s="4" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/lv_lashes.and.brows/</t>
-        </is>
-      </c>
-      <c r="I270" s="2" t="inlineStr"/>
+          <t>Facebook</t>
+        </is>
+      </c>
+      <c r="H270" s="2" t="inlineStr"/>
+      <c r="I270" s="4" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/frontyardsgc/</t>
+        </is>
+      </c>
       <c r="J270" s="2" t="inlineStr">
         <is>
-          <t>+61 450 553 112</t>
+          <t>+61 479 077 953</t>
         </is>
       </c>
       <c r="K270" s="2" t="inlineStr"/>
@@ -19891,7 +19891,7 @@
       </c>
       <c r="M270" s="2" t="inlineStr">
         <is>
-          <t>Hi LV lashes &amp; brows team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for LV lashes &amp; brows, only your Instagram. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
+          <t>Hi The Courtyard Co team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for The Courtyard Co, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
         </is>
       </c>
       <c r="N270" s="4" t="inlineStr">
@@ -19925,12 +19925,12 @@
       </c>
       <c r="D271" s="2" t="inlineStr">
         <is>
-          <t>The Courtyard Co</t>
+          <t>Desire</t>
         </is>
       </c>
       <c r="E271" s="2" t="inlineStr">
         <is>
-          <t>beauty salon</t>
+          <t>boutique</t>
         </is>
       </c>
       <c r="F271" s="2" t="inlineStr">
@@ -19946,12 +19946,12 @@
       <c r="H271" s="2" t="inlineStr"/>
       <c r="I271" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/frontyardsgc/</t>
+          <t>https://facebook.com/people/Desire-on-James/100057670328902</t>
         </is>
       </c>
       <c r="J271" s="2" t="inlineStr">
         <is>
-          <t>+61 479 077 953</t>
+          <t>+61 432 357 151</t>
         </is>
       </c>
       <c r="K271" s="2" t="inlineStr"/>
@@ -19962,7 +19962,7 @@
       </c>
       <c r="M271" s="2" t="inlineStr">
         <is>
-          <t>Hi The Courtyard Co team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for The Courtyard Co, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
+          <t>Hi Desire team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Desire, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
         </is>
       </c>
       <c r="N271" s="4" t="inlineStr">
@@ -19996,7 +19996,7 @@
       </c>
       <c r="D272" s="2" t="inlineStr">
         <is>
-          <t>Desire</t>
+          <t>The Best Things Jewellery</t>
         </is>
       </c>
       <c r="E272" s="2" t="inlineStr">
@@ -20017,12 +20017,12 @@
       <c r="H272" s="2" t="inlineStr"/>
       <c r="I272" s="4" t="inlineStr">
         <is>
-          <t>https://facebook.com/people/Desire-on-James/100057670328902</t>
+          <t>https://www.facebook.com/2251GCHWY/</t>
         </is>
       </c>
       <c r="J272" s="2" t="inlineStr">
         <is>
-          <t>+61 432 357 151</t>
+          <t>+61 7 5572 7711</t>
         </is>
       </c>
       <c r="K272" s="2" t="inlineStr"/>
@@ -20033,7 +20033,7 @@
       </c>
       <c r="M272" s="2" t="inlineStr">
         <is>
-          <t>Hi Desire team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Desire, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
+          <t>Hi The Best Things Jewellery team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for The Best Things Jewellery, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
         </is>
       </c>
       <c r="N272" s="4" t="inlineStr">
@@ -20067,12 +20067,12 @@
       </c>
       <c r="D273" s="2" t="inlineStr">
         <is>
-          <t>The Best Things Jewellery</t>
+          <t>BJ Snacks</t>
         </is>
       </c>
       <c r="E273" s="2" t="inlineStr">
         <is>
-          <t>boutique</t>
+          <t>cafe</t>
         </is>
       </c>
       <c r="F273" s="2" t="inlineStr">
@@ -20088,12 +20088,12 @@
       <c r="H273" s="2" t="inlineStr"/>
       <c r="I273" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/2251GCHWY/</t>
+          <t>https://www.facebook.com/Bjsnacksburleighheads/</t>
         </is>
       </c>
       <c r="J273" s="2" t="inlineStr">
         <is>
-          <t>+61 7 5572 7711</t>
+          <t>+61 7 5593 5270</t>
         </is>
       </c>
       <c r="K273" s="2" t="inlineStr"/>
@@ -20104,7 +20104,7 @@
       </c>
       <c r="M273" s="2" t="inlineStr">
         <is>
-          <t>Hi The Best Things Jewellery team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for The Best Things Jewellery, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
+          <t>Hi BJ Snacks team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for BJ Snacks, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
         </is>
       </c>
       <c r="N273" s="4" t="inlineStr">
@@ -20138,7 +20138,7 @@
       </c>
       <c r="D274" s="2" t="inlineStr">
         <is>
-          <t>BJ Snacks</t>
+          <t>Café Biaggi</t>
         </is>
       </c>
       <c r="E274" s="2" t="inlineStr">
@@ -20159,12 +20159,12 @@
       <c r="H274" s="2" t="inlineStr"/>
       <c r="I274" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/Bjsnacksburleighheads/</t>
+          <t>https://www.facebook.com/Cafe-Biaggi-110229862373489/</t>
         </is>
       </c>
       <c r="J274" s="2" t="inlineStr">
         <is>
-          <t>+61 7 5593 5270</t>
+          <t>+61 7 5593 7072</t>
         </is>
       </c>
       <c r="K274" s="2" t="inlineStr"/>
@@ -20175,7 +20175,7 @@
       </c>
       <c r="M274" s="2" t="inlineStr">
         <is>
-          <t>Hi BJ Snacks team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for BJ Snacks, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
+          <t>Hi Café Biaggi team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Café Biaggi, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
         </is>
       </c>
       <c r="N274" s="4" t="inlineStr">
@@ -20209,7 +20209,7 @@
       </c>
       <c r="D275" s="2" t="inlineStr">
         <is>
-          <t>Café Biaggi</t>
+          <t>Canteen Coffee</t>
         </is>
       </c>
       <c r="E275" s="2" t="inlineStr">
@@ -20230,14 +20230,10 @@
       <c r="H275" s="2" t="inlineStr"/>
       <c r="I275" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/Cafe-Biaggi-110229862373489/</t>
-        </is>
-      </c>
-      <c r="J275" s="2" t="inlineStr">
-        <is>
-          <t>+61 7 5593 7072</t>
-        </is>
-      </c>
+          <t>https://www.facebook.com/CanteenCoffeeandKitchen/</t>
+        </is>
+      </c>
+      <c r="J275" s="2" t="inlineStr"/>
       <c r="K275" s="2" t="inlineStr"/>
       <c r="L275" s="2" t="inlineStr">
         <is>
@@ -20246,7 +20242,7 @@
       </c>
       <c r="M275" s="2" t="inlineStr">
         <is>
-          <t>Hi Café Biaggi team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Café Biaggi, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
+          <t>Hi Canteen Coffee team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Canteen Coffee, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
         </is>
       </c>
       <c r="N275" s="4" t="inlineStr">
@@ -20280,7 +20276,7 @@
       </c>
       <c r="D276" s="2" t="inlineStr">
         <is>
-          <t>Canteen Coffee</t>
+          <t>Commune</t>
         </is>
       </c>
       <c r="E276" s="2" t="inlineStr">
@@ -20301,10 +20297,14 @@
       <c r="H276" s="2" t="inlineStr"/>
       <c r="I276" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/CanteenCoffeeandKitchen/</t>
-        </is>
-      </c>
-      <c r="J276" s="2" t="inlineStr"/>
+          <t>https://www.facebook.com/Commune-188007077908552/</t>
+        </is>
+      </c>
+      <c r="J276" s="2" t="inlineStr">
+        <is>
+          <t>+61 7 5520 3377</t>
+        </is>
+      </c>
       <c r="K276" s="2" t="inlineStr"/>
       <c r="L276" s="2" t="inlineStr">
         <is>
@@ -20313,7 +20313,7 @@
       </c>
       <c r="M276" s="2" t="inlineStr">
         <is>
-          <t>Hi Canteen Coffee team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Canteen Coffee, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
+          <t>Hi Commune team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Commune, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
         </is>
       </c>
       <c r="N276" s="4" t="inlineStr">
@@ -20347,7 +20347,7 @@
       </c>
       <c r="D277" s="2" t="inlineStr">
         <is>
-          <t>Commune</t>
+          <t>Daily Grind</t>
         </is>
       </c>
       <c r="E277" s="2" t="inlineStr">
@@ -20368,12 +20368,12 @@
       <c r="H277" s="2" t="inlineStr"/>
       <c r="I277" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/Commune-188007077908552/</t>
+          <t>https://www.facebook.com/dailygrindburleigh/</t>
         </is>
       </c>
       <c r="J277" s="2" t="inlineStr">
         <is>
-          <t>+61 7 5520 3377</t>
+          <t>+61 449 075 032</t>
         </is>
       </c>
       <c r="K277" s="2" t="inlineStr"/>
@@ -20384,7 +20384,7 @@
       </c>
       <c r="M277" s="2" t="inlineStr">
         <is>
-          <t>Hi Commune team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Commune, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
+          <t>Hi Daily Grind team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Daily Grind, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
         </is>
       </c>
       <c r="N277" s="4" t="inlineStr">
@@ -20418,7 +20418,7 @@
       </c>
       <c r="D278" s="2" t="inlineStr">
         <is>
-          <t>Daily Grind</t>
+          <t>Doki Doki Cafe Bar</t>
         </is>
       </c>
       <c r="E278" s="2" t="inlineStr">
@@ -20433,20 +20433,16 @@
       </c>
       <c r="G278" s="2" t="inlineStr">
         <is>
-          <t>Facebook</t>
-        </is>
-      </c>
-      <c r="H278" s="2" t="inlineStr"/>
-      <c r="I278" s="4" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/dailygrindburleigh/</t>
-        </is>
-      </c>
-      <c r="J278" s="2" t="inlineStr">
-        <is>
-          <t>+61 449 075 032</t>
-        </is>
-      </c>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="H278" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/cafe_bar_dokidoki/</t>
+        </is>
+      </c>
+      <c r="I278" s="2" t="inlineStr"/>
+      <c r="J278" s="2" t="inlineStr"/>
       <c r="K278" s="2" t="inlineStr"/>
       <c r="L278" s="2" t="inlineStr">
         <is>
@@ -20455,7 +20451,7 @@
       </c>
       <c r="M278" s="2" t="inlineStr">
         <is>
-          <t>Hi Daily Grind team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Daily Grind, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
+          <t>Hi Doki Doki Cafe Bar team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Doki Doki Cafe Bar, only your Instagram. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
         </is>
       </c>
       <c r="N278" s="4" t="inlineStr">
@@ -20489,7 +20485,7 @@
       </c>
       <c r="D279" s="2" t="inlineStr">
         <is>
-          <t>Doki Doki Cafe Bar</t>
+          <t>Fresh Coffee Bar</t>
         </is>
       </c>
       <c r="E279" s="2" t="inlineStr">
@@ -20504,16 +20500,20 @@
       </c>
       <c r="G279" s="2" t="inlineStr">
         <is>
-          <t>Instagram</t>
-        </is>
-      </c>
-      <c r="H279" s="4" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/cafe_bar_dokidoki/</t>
-        </is>
-      </c>
-      <c r="I279" s="2" t="inlineStr"/>
-      <c r="J279" s="2" t="inlineStr"/>
+          <t>Facebook</t>
+        </is>
+      </c>
+      <c r="H279" s="2" t="inlineStr"/>
+      <c r="I279" s="4" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/FreshCoffeeBarVarsity/</t>
+        </is>
+      </c>
+      <c r="J279" s="2" t="inlineStr">
+        <is>
+          <t>+61 7 5580 8468</t>
+        </is>
+      </c>
       <c r="K279" s="2" t="inlineStr"/>
       <c r="L279" s="2" t="inlineStr">
         <is>
@@ -20522,7 +20522,7 @@
       </c>
       <c r="M279" s="2" t="inlineStr">
         <is>
-          <t>Hi Doki Doki Cafe Bar team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Doki Doki Cafe Bar, only your Instagram. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
+          <t>Hi Fresh Coffee Bar team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Fresh Coffee Bar, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
         </is>
       </c>
       <c r="N279" s="4" t="inlineStr">
@@ -20556,7 +20556,7 @@
       </c>
       <c r="D280" s="2" t="inlineStr">
         <is>
-          <t>Fresh Coffee Bar</t>
+          <t>Hide N Seek Espresso</t>
         </is>
       </c>
       <c r="E280" s="2" t="inlineStr">
@@ -20577,12 +20577,12 @@
       <c r="H280" s="2" t="inlineStr"/>
       <c r="I280" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/FreshCoffeeBarVarsity/</t>
+          <t>https://www.facebook.com/hidenseekespresso13/</t>
         </is>
       </c>
       <c r="J280" s="2" t="inlineStr">
         <is>
-          <t>+61 7 5580 8468</t>
+          <t>+61 447 593 827</t>
         </is>
       </c>
       <c r="K280" s="2" t="inlineStr"/>
@@ -20593,7 +20593,7 @@
       </c>
       <c r="M280" s="2" t="inlineStr">
         <is>
-          <t>Hi Fresh Coffee Bar team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Fresh Coffee Bar, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
+          <t>Hi Hide N Seek Espresso team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Hide N Seek Espresso, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
         </is>
       </c>
       <c r="N280" s="4" t="inlineStr">
@@ -20627,7 +20627,7 @@
       </c>
       <c r="D281" s="2" t="inlineStr">
         <is>
-          <t>Hide N Seek Espresso</t>
+          <t>Little Bandits Coffee &amp; More</t>
         </is>
       </c>
       <c r="E281" s="2" t="inlineStr">
@@ -20642,20 +20642,16 @@
       </c>
       <c r="G281" s="2" t="inlineStr">
         <is>
-          <t>Facebook</t>
-        </is>
-      </c>
-      <c r="H281" s="2" t="inlineStr"/>
-      <c r="I281" s="4" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/hidenseekespresso13/</t>
-        </is>
-      </c>
-      <c r="J281" s="2" t="inlineStr">
-        <is>
-          <t>+61 447 593 827</t>
-        </is>
-      </c>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="H281" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/littlebanditscoffee/</t>
+        </is>
+      </c>
+      <c r="I281" s="2" t="inlineStr"/>
+      <c r="J281" s="2" t="inlineStr"/>
       <c r="K281" s="2" t="inlineStr"/>
       <c r="L281" s="2" t="inlineStr">
         <is>
@@ -20664,7 +20660,7 @@
       </c>
       <c r="M281" s="2" t="inlineStr">
         <is>
-          <t>Hi Hide N Seek Espresso team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Hide N Seek Espresso, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
+          <t>Hi Little Bandits Coffee &amp; More team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Little Bandits Coffee &amp; More, only your Instagram. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
         </is>
       </c>
       <c r="N281" s="4" t="inlineStr">
@@ -20698,7 +20694,7 @@
       </c>
       <c r="D282" s="2" t="inlineStr">
         <is>
-          <t>Little Bandits Coffee &amp; More</t>
+          <t>More Coffee Please</t>
         </is>
       </c>
       <c r="E282" s="2" t="inlineStr">
@@ -20713,16 +20709,20 @@
       </c>
       <c r="G282" s="2" t="inlineStr">
         <is>
-          <t>Instagram</t>
-        </is>
-      </c>
-      <c r="H282" s="4" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/littlebanditscoffee/</t>
-        </is>
-      </c>
-      <c r="I282" s="2" t="inlineStr"/>
-      <c r="J282" s="2" t="inlineStr"/>
+          <t>Facebook</t>
+        </is>
+      </c>
+      <c r="H282" s="2" t="inlineStr"/>
+      <c r="I282" s="4" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/morecoffeepleasecafe/</t>
+        </is>
+      </c>
+      <c r="J282" s="2" t="inlineStr">
+        <is>
+          <t>+61 7 5536 7456</t>
+        </is>
+      </c>
       <c r="K282" s="2" t="inlineStr"/>
       <c r="L282" s="2" t="inlineStr">
         <is>
@@ -20731,7 +20731,7 @@
       </c>
       <c r="M282" s="2" t="inlineStr">
         <is>
-          <t>Hi Little Bandits Coffee &amp; More team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Little Bandits Coffee &amp; More, only your Instagram. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
+          <t>Hi More Coffee Please team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for More Coffee Please, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
         </is>
       </c>
       <c r="N282" s="4" t="inlineStr">
@@ -20760,12 +20760,12 @@
       </c>
       <c r="C283" s="2" t="inlineStr">
         <is>
-          <t>No website found</t>
+          <t>Site shows an error</t>
         </is>
       </c>
       <c r="D283" s="2" t="inlineStr">
         <is>
-          <t>More Coffee Please</t>
+          <t>Niche &amp; Co</t>
         </is>
       </c>
       <c r="E283" s="2" t="inlineStr">
@@ -20780,29 +20780,37 @@
       </c>
       <c r="G283" s="2" t="inlineStr">
         <is>
-          <t>Facebook</t>
-        </is>
-      </c>
-      <c r="H283" s="2" t="inlineStr"/>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="H283" s="4" t="inlineStr">
+        <is>
+          <t>https://instagram.com/nicheandco</t>
+        </is>
+      </c>
       <c r="I283" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/morecoffeepleasecafe/</t>
+          <t>https://facebook.com/nicheandco</t>
         </is>
       </c>
       <c r="J283" s="2" t="inlineStr">
         <is>
-          <t>+61 7 5536 7456</t>
-        </is>
-      </c>
-      <c r="K283" s="2" t="inlineStr"/>
+          <t>+61 7 5598 2535</t>
+        </is>
+      </c>
+      <c r="K283" s="4" t="inlineStr">
+        <is>
+          <t>https://nicheandco.com.au</t>
+        </is>
+      </c>
       <c r="L283" s="2" t="inlineStr">
         <is>
-          <t>no website listed, only social media (verify on Google Maps)</t>
+          <t>homepage shows an error page (HTTP 404)</t>
         </is>
       </c>
       <c r="M283" s="2" t="inlineStr">
         <is>
-          <t>Hi More Coffee Please team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for More Coffee Please, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
+          <t>Hi Niche &amp; Co team! [one real detail from their page]. We're AceAds, a web design studio. We noticed your website was showing an error page when we tried it. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
         </is>
       </c>
       <c r="N283" s="4" t="inlineStr">
@@ -20831,12 +20839,12 @@
       </c>
       <c r="C284" s="2" t="inlineStr">
         <is>
-          <t>Site shows an error</t>
+          <t>No website found</t>
         </is>
       </c>
       <c r="D284" s="2" t="inlineStr">
         <is>
-          <t>Niche &amp; Co</t>
+          <t>Profile Coffee Co-Lab</t>
         </is>
       </c>
       <c r="E284" s="2" t="inlineStr">
@@ -20856,32 +20864,20 @@
       </c>
       <c r="H284" s="4" t="inlineStr">
         <is>
-          <t>https://instagram.com/nicheandco</t>
-        </is>
-      </c>
-      <c r="I284" s="4" t="inlineStr">
-        <is>
-          <t>https://facebook.com/nicheandco</t>
-        </is>
-      </c>
-      <c r="J284" s="2" t="inlineStr">
-        <is>
-          <t>+61 7 5598 2535</t>
-        </is>
-      </c>
-      <c r="K284" s="4" t="inlineStr">
-        <is>
-          <t>https://nicheandco.com.au</t>
-        </is>
-      </c>
+          <t>https://www.instagram.com/profile_coffee_colab/</t>
+        </is>
+      </c>
+      <c r="I284" s="2" t="inlineStr"/>
+      <c r="J284" s="2" t="inlineStr"/>
+      <c r="K284" s="2" t="inlineStr"/>
       <c r="L284" s="2" t="inlineStr">
         <is>
-          <t>homepage shows an error page (HTTP 404)</t>
+          <t>no website listed, only social media (verify on Google Maps)</t>
         </is>
       </c>
       <c r="M284" s="2" t="inlineStr">
         <is>
-          <t>Hi Niche &amp; Co team! [one real detail from their page]. We're AceAds, a web design studio. We noticed your website was showing an error page when we tried it. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
+          <t>Hi Profile Coffee Co-Lab team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Profile Coffee Co-Lab, only your Instagram. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
         </is>
       </c>
       <c r="N284" s="4" t="inlineStr">
@@ -20915,7 +20911,7 @@
       </c>
       <c r="D285" s="2" t="inlineStr">
         <is>
-          <t>Profile Coffee Co-Lab</t>
+          <t>Quade &amp; Co</t>
         </is>
       </c>
       <c r="E285" s="2" t="inlineStr">
@@ -20935,10 +20931,14 @@
       </c>
       <c r="H285" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/profile_coffee_colab/</t>
-        </is>
-      </c>
-      <c r="I285" s="2" t="inlineStr"/>
+          <t>https://instagram.com/quadeandco</t>
+        </is>
+      </c>
+      <c r="I285" s="4" t="inlineStr">
+        <is>
+          <t>https://facebook.com/quadeandco</t>
+        </is>
+      </c>
       <c r="J285" s="2" t="inlineStr"/>
       <c r="K285" s="2" t="inlineStr"/>
       <c r="L285" s="2" t="inlineStr">
@@ -20948,7 +20948,7 @@
       </c>
       <c r="M285" s="2" t="inlineStr">
         <is>
-          <t>Hi Profile Coffee Co-Lab team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Profile Coffee Co-Lab, only your Instagram. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
+          <t>Hi Quade &amp; Co team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Quade &amp; Co, only your Instagram. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
         </is>
       </c>
       <c r="N285" s="4" t="inlineStr">
@@ -20982,7 +20982,7 @@
       </c>
       <c r="D286" s="2" t="inlineStr">
         <is>
-          <t>Quade &amp; Co</t>
+          <t>See Yö Cafe &amp; Bakery</t>
         </is>
       </c>
       <c r="E286" s="2" t="inlineStr">
@@ -20997,20 +20997,20 @@
       </c>
       <c r="G286" s="2" t="inlineStr">
         <is>
-          <t>Instagram</t>
-        </is>
-      </c>
-      <c r="H286" s="4" t="inlineStr">
-        <is>
-          <t>https://instagram.com/quadeandco</t>
-        </is>
-      </c>
+          <t>Facebook</t>
+        </is>
+      </c>
+      <c r="H286" s="2" t="inlineStr"/>
       <c r="I286" s="4" t="inlineStr">
         <is>
-          <t>https://facebook.com/quadeandco</t>
-        </is>
-      </c>
-      <c r="J286" s="2" t="inlineStr"/>
+          <t>https://www.facebook.com/marieanitas/</t>
+        </is>
+      </c>
+      <c r="J286" s="2" t="inlineStr">
+        <is>
+          <t>+61 7 5572 3224</t>
+        </is>
+      </c>
       <c r="K286" s="2" t="inlineStr"/>
       <c r="L286" s="2" t="inlineStr">
         <is>
@@ -21019,7 +21019,7 @@
       </c>
       <c r="M286" s="2" t="inlineStr">
         <is>
-          <t>Hi Quade &amp; Co team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Quade &amp; Co, only your Instagram. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
+          <t>Hi See Yö Cafe &amp; Bakery team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for See Yö Cafe &amp; Bakery, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
         </is>
       </c>
       <c r="N286" s="4" t="inlineStr">
@@ -21053,7 +21053,7 @@
       </c>
       <c r="D287" s="2" t="inlineStr">
         <is>
-          <t>See Yö Cafe &amp; Bakery</t>
+          <t>Sens Coffee Co</t>
         </is>
       </c>
       <c r="E287" s="2" t="inlineStr">
@@ -21068,18 +21068,22 @@
       </c>
       <c r="G287" s="2" t="inlineStr">
         <is>
-          <t>Facebook</t>
-        </is>
-      </c>
-      <c r="H287" s="2" t="inlineStr"/>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="H287" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/sens_coffee_co/</t>
+        </is>
+      </c>
       <c r="I287" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/marieanitas/</t>
+          <t>https://www.facebook.com/p/SENS-COFEE-CO-Southport-61564429171125/</t>
         </is>
       </c>
       <c r="J287" s="2" t="inlineStr">
         <is>
-          <t>+61 7 5572 3224</t>
+          <t>+61 452 017 367</t>
         </is>
       </c>
       <c r="K287" s="2" t="inlineStr"/>
@@ -21090,7 +21094,7 @@
       </c>
       <c r="M287" s="2" t="inlineStr">
         <is>
-          <t>Hi See Yö Cafe &amp; Bakery team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for See Yö Cafe &amp; Bakery, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
+          <t>Hi Sens Coffee Co team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Sens Coffee Co, only your Instagram. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
         </is>
       </c>
       <c r="N287" s="4" t="inlineStr">
@@ -21124,7 +21128,7 @@
       </c>
       <c r="D288" s="2" t="inlineStr">
         <is>
-          <t>Sens Coffee Co</t>
+          <t>Social Brew</t>
         </is>
       </c>
       <c r="E288" s="2" t="inlineStr">
@@ -21139,24 +21143,16 @@
       </c>
       <c r="G288" s="2" t="inlineStr">
         <is>
-          <t>Instagram</t>
-        </is>
-      </c>
-      <c r="H288" s="4" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/sens_coffee_co/</t>
-        </is>
-      </c>
+          <t>Facebook</t>
+        </is>
+      </c>
+      <c r="H288" s="2" t="inlineStr"/>
       <c r="I288" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/p/SENS-COFEE-CO-Southport-61564429171125/</t>
-        </is>
-      </c>
-      <c r="J288" s="2" t="inlineStr">
-        <is>
-          <t>+61 452 017 367</t>
-        </is>
-      </c>
+          <t>https://www.facebook.com/socialbrewburleigh/</t>
+        </is>
+      </c>
+      <c r="J288" s="2" t="inlineStr"/>
       <c r="K288" s="2" t="inlineStr"/>
       <c r="L288" s="2" t="inlineStr">
         <is>
@@ -21165,7 +21161,7 @@
       </c>
       <c r="M288" s="2" t="inlineStr">
         <is>
-          <t>Hi Sens Coffee Co team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Sens Coffee Co, only your Instagram. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
+          <t>Hi Social Brew team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Social Brew, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
         </is>
       </c>
       <c r="N288" s="4" t="inlineStr">
@@ -21199,7 +21195,7 @@
       </c>
       <c r="D289" s="2" t="inlineStr">
         <is>
-          <t>Social Brew</t>
+          <t>Street Corner Espresso</t>
         </is>
       </c>
       <c r="E289" s="2" t="inlineStr">
@@ -21220,10 +21216,14 @@
       <c r="H289" s="2" t="inlineStr"/>
       <c r="I289" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/socialbrewburleigh/</t>
-        </is>
-      </c>
-      <c r="J289" s="2" t="inlineStr"/>
+          <t>https://www.facebook.com/StreetCornerEspresso/</t>
+        </is>
+      </c>
+      <c r="J289" s="2" t="inlineStr">
+        <is>
+          <t>+61 7 5520 0886</t>
+        </is>
+      </c>
       <c r="K289" s="2" t="inlineStr"/>
       <c r="L289" s="2" t="inlineStr">
         <is>
@@ -21232,7 +21232,7 @@
       </c>
       <c r="M289" s="2" t="inlineStr">
         <is>
-          <t>Hi Social Brew team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Social Brew, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
+          <t>Hi Street Corner Espresso team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Street Corner Espresso, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
         </is>
       </c>
       <c r="N289" s="4" t="inlineStr">
@@ -21266,7 +21266,7 @@
       </c>
       <c r="D290" s="2" t="inlineStr">
         <is>
-          <t>Street Corner Espresso</t>
+          <t>The Kumara Patch</t>
         </is>
       </c>
       <c r="E290" s="2" t="inlineStr">
@@ -21287,12 +21287,12 @@
       <c r="H290" s="2" t="inlineStr"/>
       <c r="I290" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/StreetCornerEspresso/</t>
+          <t>https://www.facebook.com/thekumarapatch/</t>
         </is>
       </c>
       <c r="J290" s="2" t="inlineStr">
         <is>
-          <t>+61 7 5520 0886</t>
+          <t>+61 7 5539 4243</t>
         </is>
       </c>
       <c r="K290" s="2" t="inlineStr"/>
@@ -21303,7 +21303,7 @@
       </c>
       <c r="M290" s="2" t="inlineStr">
         <is>
-          <t>Hi Street Corner Espresso team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Street Corner Espresso, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
+          <t>Hi The Kumara Patch team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for The Kumara Patch, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
         </is>
       </c>
       <c r="N290" s="4" t="inlineStr">
@@ -21337,7 +21337,7 @@
       </c>
       <c r="D291" s="2" t="inlineStr">
         <is>
-          <t>The Kumara Patch</t>
+          <t>The Palm Coffee</t>
         </is>
       </c>
       <c r="E291" s="2" t="inlineStr">
@@ -21352,18 +21352,22 @@
       </c>
       <c r="G291" s="2" t="inlineStr">
         <is>
-          <t>Facebook</t>
-        </is>
-      </c>
-      <c r="H291" s="2" t="inlineStr"/>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="H291" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/the_palmcoffee</t>
+        </is>
+      </c>
       <c r="I291" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/thekumarapatch/</t>
+          <t>https://www.facebook.com/thepalmscoffees/</t>
         </is>
       </c>
       <c r="J291" s="2" t="inlineStr">
         <is>
-          <t>+61 7 5539 4243</t>
+          <t>+61 410 812 975</t>
         </is>
       </c>
       <c r="K291" s="2" t="inlineStr"/>
@@ -21374,7 +21378,7 @@
       </c>
       <c r="M291" s="2" t="inlineStr">
         <is>
-          <t>Hi The Kumara Patch team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for The Kumara Patch, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
+          <t>Hi The Palm Coffee team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for The Palm Coffee, only your Instagram. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
         </is>
       </c>
       <c r="N291" s="4" t="inlineStr">
@@ -21408,7 +21412,7 @@
       </c>
       <c r="D292" s="2" t="inlineStr">
         <is>
-          <t>The Palm Coffee</t>
+          <t>The Press Cafe</t>
         </is>
       </c>
       <c r="E292" s="2" t="inlineStr">
@@ -21423,22 +21427,18 @@
       </c>
       <c r="G292" s="2" t="inlineStr">
         <is>
-          <t>Instagram</t>
-        </is>
-      </c>
-      <c r="H292" s="4" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/the_palmcoffee</t>
-        </is>
-      </c>
+          <t>Facebook</t>
+        </is>
+      </c>
+      <c r="H292" s="2" t="inlineStr"/>
       <c r="I292" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/thepalmscoffees/</t>
+          <t>https://www.facebook.com/thepresscafecoomera/</t>
         </is>
       </c>
       <c r="J292" s="2" t="inlineStr">
         <is>
-          <t>+61 410 812 975</t>
+          <t>+61 417 402 174</t>
         </is>
       </c>
       <c r="K292" s="2" t="inlineStr"/>
@@ -21449,7 +21449,7 @@
       </c>
       <c r="M292" s="2" t="inlineStr">
         <is>
-          <t>Hi The Palm Coffee team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for The Palm Coffee, only your Instagram. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
+          <t>Hi The Press Cafe team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for The Press Cafe, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
         </is>
       </c>
       <c r="N292" s="4" t="inlineStr">
@@ -21483,7 +21483,7 @@
       </c>
       <c r="D293" s="2" t="inlineStr">
         <is>
-          <t>The Press Cafe</t>
+          <t>The Treehouse</t>
         </is>
       </c>
       <c r="E293" s="2" t="inlineStr">
@@ -21504,14 +21504,10 @@
       <c r="H293" s="2" t="inlineStr"/>
       <c r="I293" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/thepresscafecoomera/</t>
-        </is>
-      </c>
-      <c r="J293" s="2" t="inlineStr">
-        <is>
-          <t>+61 417 402 174</t>
-        </is>
-      </c>
+          <t>https://www.facebook.com/treehouseonthehill/</t>
+        </is>
+      </c>
+      <c r="J293" s="2" t="inlineStr"/>
       <c r="K293" s="2" t="inlineStr"/>
       <c r="L293" s="2" t="inlineStr">
         <is>
@@ -21520,7 +21516,7 @@
       </c>
       <c r="M293" s="2" t="inlineStr">
         <is>
-          <t>Hi The Press Cafe team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for The Press Cafe, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
+          <t>Hi The Treehouse team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for The Treehouse, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
         </is>
       </c>
       <c r="N293" s="4" t="inlineStr">
@@ -21554,7 +21550,7 @@
       </c>
       <c r="D294" s="2" t="inlineStr">
         <is>
-          <t>The Treehouse</t>
+          <t>Third Base</t>
         </is>
       </c>
       <c r="E294" s="2" t="inlineStr">
@@ -21569,15 +21565,15 @@
       </c>
       <c r="G294" s="2" t="inlineStr">
         <is>
-          <t>Facebook</t>
-        </is>
-      </c>
-      <c r="H294" s="2" t="inlineStr"/>
-      <c r="I294" s="4" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/treehouseonthehill/</t>
-        </is>
-      </c>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="H294" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/thirdbasepalmbeach/</t>
+        </is>
+      </c>
+      <c r="I294" s="2" t="inlineStr"/>
       <c r="J294" s="2" t="inlineStr"/>
       <c r="K294" s="2" t="inlineStr"/>
       <c r="L294" s="2" t="inlineStr">
@@ -21587,7 +21583,7 @@
       </c>
       <c r="M294" s="2" t="inlineStr">
         <is>
-          <t>Hi The Treehouse team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for The Treehouse, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
+          <t>Hi Third Base team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Third Base, only your Instagram. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
         </is>
       </c>
       <c r="N294" s="4" t="inlineStr">
@@ -21621,7 +21617,7 @@
       </c>
       <c r="D295" s="2" t="inlineStr">
         <is>
-          <t>Third Base</t>
+          <t>Vegepatch Studios</t>
         </is>
       </c>
       <c r="E295" s="2" t="inlineStr">
@@ -21641,7 +21637,7 @@
       </c>
       <c r="H295" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/thirdbasepalmbeach/</t>
+          <t>https://www.instagram.com/vegepatchstudios</t>
         </is>
       </c>
       <c r="I295" s="2" t="inlineStr"/>
@@ -21654,7 +21650,7 @@
       </c>
       <c r="M295" s="2" t="inlineStr">
         <is>
-          <t>Hi Third Base team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Third Base, only your Instagram. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
+          <t>Hi Vegepatch Studios team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Vegepatch Studios, only your Instagram. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
         </is>
       </c>
       <c r="N295" s="4" t="inlineStr">
@@ -21688,12 +21684,12 @@
       </c>
       <c r="D296" s="2" t="inlineStr">
         <is>
-          <t>Vegepatch Studios</t>
+          <t>Broccoli Brothers</t>
         </is>
       </c>
       <c r="E296" s="2" t="inlineStr">
         <is>
-          <t>cafe</t>
+          <t>deli or specialty food</t>
         </is>
       </c>
       <c r="F296" s="2" t="inlineStr">
@@ -21703,16 +21699,20 @@
       </c>
       <c r="G296" s="2" t="inlineStr">
         <is>
-          <t>Instagram</t>
-        </is>
-      </c>
-      <c r="H296" s="4" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/vegepatchstudios</t>
-        </is>
-      </c>
-      <c r="I296" s="2" t="inlineStr"/>
-      <c r="J296" s="2" t="inlineStr"/>
+          <t>Facebook</t>
+        </is>
+      </c>
+      <c r="H296" s="2" t="inlineStr"/>
+      <c r="I296" s="4" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/Broccoli.Brothers.Treetops.Plaza/</t>
+        </is>
+      </c>
+      <c r="J296" s="2" t="inlineStr">
+        <is>
+          <t>+61 7 5522 0066</t>
+        </is>
+      </c>
       <c r="K296" s="2" t="inlineStr"/>
       <c r="L296" s="2" t="inlineStr">
         <is>
@@ -21721,7 +21721,7 @@
       </c>
       <c r="M296" s="2" t="inlineStr">
         <is>
-          <t>Hi Vegepatch Studios team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Vegepatch Studios, only your Instagram. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
+          <t>Hi Broccoli Brothers team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Broccoli Brothers, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
         </is>
       </c>
       <c r="N296" s="4" t="inlineStr">
@@ -21755,7 +21755,7 @@
       </c>
       <c r="D297" s="2" t="inlineStr">
         <is>
-          <t>Broccoli Brothers</t>
+          <t>Gold Coast Growers Market</t>
         </is>
       </c>
       <c r="E297" s="2" t="inlineStr">
@@ -21776,12 +21776,12 @@
       <c r="H297" s="2" t="inlineStr"/>
       <c r="I297" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/Broccoli.Brothers.Treetops.Plaza/</t>
+          <t>https://www.facebook.com/p/Gold-Coast-Growers-Market-100063543881581/</t>
         </is>
       </c>
       <c r="J297" s="2" t="inlineStr">
         <is>
-          <t>+61 7 5522 0066</t>
+          <t>+61 412 697 263</t>
         </is>
       </c>
       <c r="K297" s="2" t="inlineStr"/>
@@ -21792,7 +21792,7 @@
       </c>
       <c r="M297" s="2" t="inlineStr">
         <is>
-          <t>Hi Broccoli Brothers team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Broccoli Brothers, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
+          <t>Hi Gold Coast Growers Market team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Gold Coast Growers Market, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
         </is>
       </c>
       <c r="N297" s="4" t="inlineStr">
@@ -21826,7 +21826,7 @@
       </c>
       <c r="D298" s="2" t="inlineStr">
         <is>
-          <t>Gold Coast Growers Market</t>
+          <t>Kingswood Park Butchery</t>
         </is>
       </c>
       <c r="E298" s="2" t="inlineStr">
@@ -21847,12 +21847,12 @@
       <c r="H298" s="2" t="inlineStr"/>
       <c r="I298" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/p/Gold-Coast-Growers-Market-100063543881581/</t>
+          <t>https://www.facebook.com/Kingswoodparkbutchery/</t>
         </is>
       </c>
       <c r="J298" s="2" t="inlineStr">
         <is>
-          <t>+61 412 697 263</t>
+          <t>+61 7 5534 4054</t>
         </is>
       </c>
       <c r="K298" s="2" t="inlineStr"/>
@@ -21863,7 +21863,7 @@
       </c>
       <c r="M298" s="2" t="inlineStr">
         <is>
-          <t>Hi Gold Coast Growers Market team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Gold Coast Growers Market, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
+          <t>Hi Kingswood Park Butchery team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Kingswood Park Butchery, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
         </is>
       </c>
       <c r="N298" s="4" t="inlineStr">
@@ -21897,7 +21897,7 @@
       </c>
       <c r="D299" s="2" t="inlineStr">
         <is>
-          <t>Kingswood Park Butchery</t>
+          <t>Lakeside Quality Meats</t>
         </is>
       </c>
       <c r="E299" s="2" t="inlineStr">
@@ -21912,18 +21912,22 @@
       </c>
       <c r="G299" s="2" t="inlineStr">
         <is>
-          <t>Facebook</t>
-        </is>
-      </c>
-      <c r="H299" s="2" t="inlineStr"/>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="H299" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/lakeside_quality_meats</t>
+        </is>
+      </c>
       <c r="I299" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/Kingswoodparkbutchery/</t>
+          <t>https://www.facebook.com/lakesidequalitymeatspalmbeach/</t>
         </is>
       </c>
       <c r="J299" s="2" t="inlineStr">
         <is>
-          <t>+61 7 5534 4054</t>
+          <t>+61 7 5534 5704</t>
         </is>
       </c>
       <c r="K299" s="2" t="inlineStr"/>
@@ -21934,7 +21938,7 @@
       </c>
       <c r="M299" s="2" t="inlineStr">
         <is>
-          <t>Hi Kingswood Park Butchery team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Kingswood Park Butchery, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
+          <t>Hi Lakeside Quality Meats team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Lakeside Quality Meats, only your Instagram. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
         </is>
       </c>
       <c r="N299" s="4" t="inlineStr">
@@ -21968,7 +21972,7 @@
       </c>
       <c r="D300" s="2" t="inlineStr">
         <is>
-          <t>Lakeside Quality Meats</t>
+          <t>Loveday’s Quality Meats</t>
         </is>
       </c>
       <c r="E300" s="2" t="inlineStr">
@@ -21983,22 +21987,18 @@
       </c>
       <c r="G300" s="2" t="inlineStr">
         <is>
-          <t>Instagram</t>
-        </is>
-      </c>
-      <c r="H300" s="4" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/lakeside_quality_meats</t>
-        </is>
-      </c>
+          <t>Facebook</t>
+        </is>
+      </c>
+      <c r="H300" s="2" t="inlineStr"/>
       <c r="I300" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/lakesidequalitymeatspalmbeach/</t>
+          <t>https://www.facebook.com/lovedaysqualitymeats/</t>
         </is>
       </c>
       <c r="J300" s="2" t="inlineStr">
         <is>
-          <t>+61 7 5534 5704</t>
+          <t>+61 7 5593 5023</t>
         </is>
       </c>
       <c r="K300" s="2" t="inlineStr"/>
@@ -22009,7 +22009,7 @@
       </c>
       <c r="M300" s="2" t="inlineStr">
         <is>
-          <t>Hi Lakeside Quality Meats team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Lakeside Quality Meats, only your Instagram. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
+          <t>Hi Loveday’s Quality Meats team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Loveday’s Quality Meats, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
         </is>
       </c>
       <c r="N300" s="4" t="inlineStr">
@@ -22043,7 +22043,7 @@
       </c>
       <c r="D301" s="2" t="inlineStr">
         <is>
-          <t>Loveday’s Quality Meats</t>
+          <t>Salt &amp; Smoke Meat Co</t>
         </is>
       </c>
       <c r="E301" s="2" t="inlineStr">
@@ -22058,18 +22058,22 @@
       </c>
       <c r="G301" s="2" t="inlineStr">
         <is>
-          <t>Facebook</t>
-        </is>
-      </c>
-      <c r="H301" s="2" t="inlineStr"/>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="H301" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/saltandsmoke_meatco/</t>
+        </is>
+      </c>
       <c r="I301" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/lovedaysqualitymeats/</t>
+          <t>https://www.facebook.com/saltandsmokemeatco/</t>
         </is>
       </c>
       <c r="J301" s="2" t="inlineStr">
         <is>
-          <t>+61 7 5593 5023</t>
+          <t>+61 7 5690 3893</t>
         </is>
       </c>
       <c r="K301" s="2" t="inlineStr"/>
@@ -22080,7 +22084,7 @@
       </c>
       <c r="M301" s="2" t="inlineStr">
         <is>
-          <t>Hi Loveday’s Quality Meats team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Loveday’s Quality Meats, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
+          <t>Hi Salt &amp; Smoke Meat Co team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Salt &amp; Smoke Meat Co, only your Instagram. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
         </is>
       </c>
       <c r="N301" s="4" t="inlineStr">
@@ -22114,7 +22118,7 @@
       </c>
       <c r="D302" s="2" t="inlineStr">
         <is>
-          <t>Salt &amp; Smoke Meat Co</t>
+          <t>The Butcher's Table</t>
         </is>
       </c>
       <c r="E302" s="2" t="inlineStr">
@@ -22129,22 +22133,18 @@
       </c>
       <c r="G302" s="2" t="inlineStr">
         <is>
-          <t>Instagram</t>
-        </is>
-      </c>
-      <c r="H302" s="4" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/saltandsmoke_meatco/</t>
-        </is>
-      </c>
+          <t>Facebook</t>
+        </is>
+      </c>
+      <c r="H302" s="2" t="inlineStr"/>
       <c r="I302" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/saltandsmokemeatco/</t>
+          <t>https://facebook.com/thebutcherstablenerang</t>
         </is>
       </c>
       <c r="J302" s="2" t="inlineStr">
         <is>
-          <t>+61 7 5690 3893</t>
+          <t>+61 7 5502 2019</t>
         </is>
       </c>
       <c r="K302" s="2" t="inlineStr"/>
@@ -22155,7 +22155,7 @@
       </c>
       <c r="M302" s="2" t="inlineStr">
         <is>
-          <t>Hi Salt &amp; Smoke Meat Co team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Salt &amp; Smoke Meat Co, only your Instagram. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
+          <t>Hi The Butcher's Table team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for The Butcher's Table, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
         </is>
       </c>
       <c r="N302" s="4" t="inlineStr">
@@ -22189,7 +22189,7 @@
       </c>
       <c r="D303" s="2" t="inlineStr">
         <is>
-          <t>The Butcher's Table</t>
+          <t>Vish Fruit &amp; Veg</t>
         </is>
       </c>
       <c r="E303" s="2" t="inlineStr">
@@ -22204,18 +22204,22 @@
       </c>
       <c r="G303" s="2" t="inlineStr">
         <is>
-          <t>Facebook</t>
-        </is>
-      </c>
-      <c r="H303" s="2" t="inlineStr"/>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="H303" s="4" t="inlineStr">
+        <is>
+          <t>https://instagram.com/vishnusfreshfruitsanvegetables</t>
+        </is>
+      </c>
       <c r="I303" s="4" t="inlineStr">
         <is>
-          <t>https://facebook.com/thebutcherstablenerang</t>
+          <t>https://facebook.com/people/Vish-Fruit-veg/100063856403485</t>
         </is>
       </c>
       <c r="J303" s="2" t="inlineStr">
         <is>
-          <t>+61 7 5502 2019</t>
+          <t>+61 449 807 590</t>
         </is>
       </c>
       <c r="K303" s="2" t="inlineStr"/>
@@ -22226,7 +22230,7 @@
       </c>
       <c r="M303" s="2" t="inlineStr">
         <is>
-          <t>Hi The Butcher's Table team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for The Butcher's Table, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
+          <t>Hi Vish Fruit &amp; Veg team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Vish Fruit &amp; Veg, only your Instagram. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
         </is>
       </c>
       <c r="N303" s="4" t="inlineStr">
@@ -22260,12 +22264,12 @@
       </c>
       <c r="D304" s="2" t="inlineStr">
         <is>
-          <t>Vish Fruit &amp; Veg</t>
+          <t>Impact Furniture Finishers</t>
         </is>
       </c>
       <c r="E304" s="2" t="inlineStr">
         <is>
-          <t>deli or specialty food</t>
+          <t>gift or homewares</t>
         </is>
       </c>
       <c r="F304" s="2" t="inlineStr">
@@ -22275,22 +22279,18 @@
       </c>
       <c r="G304" s="2" t="inlineStr">
         <is>
-          <t>Instagram</t>
-        </is>
-      </c>
-      <c r="H304" s="4" t="inlineStr">
-        <is>
-          <t>https://instagram.com/vishnusfreshfruitsanvegetables</t>
-        </is>
-      </c>
+          <t>Facebook</t>
+        </is>
+      </c>
+      <c r="H304" s="2" t="inlineStr"/>
       <c r="I304" s="4" t="inlineStr">
         <is>
-          <t>https://facebook.com/people/Vish-Fruit-veg/100063856403485</t>
+          <t>https://www.facebook.com/ImpactFurnitureFinishers/</t>
         </is>
       </c>
       <c r="J304" s="2" t="inlineStr">
         <is>
-          <t>+61 449 807 590</t>
+          <t>+61 7 5598 4155</t>
         </is>
       </c>
       <c r="K304" s="2" t="inlineStr"/>
@@ -22301,7 +22301,7 @@
       </c>
       <c r="M304" s="2" t="inlineStr">
         <is>
-          <t>Hi Vish Fruit &amp; Veg team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Vish Fruit &amp; Veg, only your Instagram. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
+          <t>Hi Impact Furniture Finishers team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Impact Furniture Finishers, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
         </is>
       </c>
       <c r="N304" s="4" t="inlineStr">
@@ -22335,12 +22335,12 @@
       </c>
       <c r="D305" s="2" t="inlineStr">
         <is>
-          <t>Impact Furniture Finishers</t>
+          <t>Starke Fitness</t>
         </is>
       </c>
       <c r="E305" s="2" t="inlineStr">
         <is>
-          <t>gift or homewares</t>
+          <t>gym or studio</t>
         </is>
       </c>
       <c r="F305" s="2" t="inlineStr">
@@ -22356,12 +22356,12 @@
       <c r="H305" s="2" t="inlineStr"/>
       <c r="I305" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/ImpactFurnitureFinishers/</t>
+          <t>https://www.facebook.com/starketraining/</t>
         </is>
       </c>
       <c r="J305" s="2" t="inlineStr">
         <is>
-          <t>+61 7 5598 4155</t>
+          <t>+61 424 578 105</t>
         </is>
       </c>
       <c r="K305" s="2" t="inlineStr"/>
@@ -22372,7 +22372,7 @@
       </c>
       <c r="M305" s="2" t="inlineStr">
         <is>
-          <t>Hi Impact Furniture Finishers team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Impact Furniture Finishers, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
+          <t>Hi Starke Fitness team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Starke Fitness, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
         </is>
       </c>
       <c r="N305" s="4" t="inlineStr">
@@ -22406,12 +22406,12 @@
       </c>
       <c r="D306" s="2" t="inlineStr">
         <is>
-          <t>Starke Fitness</t>
+          <t>Bundall Smash Repairs</t>
         </is>
       </c>
       <c r="E306" s="2" t="inlineStr">
         <is>
-          <t>gym or studio</t>
+          <t>mechanic</t>
         </is>
       </c>
       <c r="F306" s="2" t="inlineStr">
@@ -22427,12 +22427,12 @@
       <c r="H306" s="2" t="inlineStr"/>
       <c r="I306" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/starketraining/</t>
+          <t>https://www.facebook.com/BundallSmash/</t>
         </is>
       </c>
       <c r="J306" s="2" t="inlineStr">
         <is>
-          <t>+61 424 578 105</t>
+          <t>+61 7 5570 3444</t>
         </is>
       </c>
       <c r="K306" s="2" t="inlineStr"/>
@@ -22443,7 +22443,7 @@
       </c>
       <c r="M306" s="2" t="inlineStr">
         <is>
-          <t>Hi Starke Fitness team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Starke Fitness, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
+          <t>Hi Bundall Smash Repairs team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Bundall Smash Repairs, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
         </is>
       </c>
       <c r="N306" s="4" t="inlineStr">
@@ -22477,7 +22477,7 @@
       </c>
       <c r="D307" s="2" t="inlineStr">
         <is>
-          <t>Bundall Smash Repairs</t>
+          <t>Craig's Detailing</t>
         </is>
       </c>
       <c r="E307" s="2" t="inlineStr">
@@ -22498,14 +22498,10 @@
       <c r="H307" s="2" t="inlineStr"/>
       <c r="I307" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/BundallSmash/</t>
-        </is>
-      </c>
-      <c r="J307" s="2" t="inlineStr">
-        <is>
-          <t>+61 7 5570 3444</t>
-        </is>
-      </c>
+          <t>https://www.facebook.com/Craigs-Detailing-118049508275423/</t>
+        </is>
+      </c>
+      <c r="J307" s="2" t="inlineStr"/>
       <c r="K307" s="2" t="inlineStr"/>
       <c r="L307" s="2" t="inlineStr">
         <is>
@@ -22514,7 +22510,7 @@
       </c>
       <c r="M307" s="2" t="inlineStr">
         <is>
-          <t>Hi Bundall Smash Repairs team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Bundall Smash Repairs, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
+          <t>Hi Craig's Detailing team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Craig's Detailing, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
         </is>
       </c>
       <c r="N307" s="4" t="inlineStr">
@@ -22548,7 +22544,7 @@
       </c>
       <c r="D308" s="2" t="inlineStr">
         <is>
-          <t>Craig's Detailing</t>
+          <t>George Gray Motors</t>
         </is>
       </c>
       <c r="E308" s="2" t="inlineStr">
@@ -22569,10 +22565,14 @@
       <c r="H308" s="2" t="inlineStr"/>
       <c r="I308" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/Craigs-Detailing-118049508275423/</t>
-        </is>
-      </c>
-      <c r="J308" s="2" t="inlineStr"/>
+          <t>https://www.facebook.com/pages/category/Automotive-Repair-Shop/George-Gray-Motors-1800438436943462/</t>
+        </is>
+      </c>
+      <c r="J308" s="2" t="inlineStr">
+        <is>
+          <t>+61 7 5576 3202</t>
+        </is>
+      </c>
       <c r="K308" s="2" t="inlineStr"/>
       <c r="L308" s="2" t="inlineStr">
         <is>
@@ -22581,7 +22581,7 @@
       </c>
       <c r="M308" s="2" t="inlineStr">
         <is>
-          <t>Hi Craig's Detailing team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Craig's Detailing, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
+          <t>Hi George Gray Motors team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for George Gray Motors, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
         </is>
       </c>
       <c r="N308" s="4" t="inlineStr">
@@ -22615,7 +22615,7 @@
       </c>
       <c r="D309" s="2" t="inlineStr">
         <is>
-          <t>George Gray Motors</t>
+          <t>Guys Bodyworks</t>
         </is>
       </c>
       <c r="E309" s="2" t="inlineStr">
@@ -22636,12 +22636,12 @@
       <c r="H309" s="2" t="inlineStr"/>
       <c r="I309" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/pages/category/Automotive-Repair-Shop/George-Gray-Motors-1800438436943462/</t>
+          <t>https://www.facebook.com/pages/Guys-Bodyworks-Southport/190128311365007</t>
         </is>
       </c>
       <c r="J309" s="2" t="inlineStr">
         <is>
-          <t>+61 7 5576 3202</t>
+          <t>+61 7 5532 1392</t>
         </is>
       </c>
       <c r="K309" s="2" t="inlineStr"/>
@@ -22652,7 +22652,7 @@
       </c>
       <c r="M309" s="2" t="inlineStr">
         <is>
-          <t>Hi George Gray Motors team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for George Gray Motors, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
+          <t>Hi Guys Bodyworks team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Guys Bodyworks, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
         </is>
       </c>
       <c r="N309" s="4" t="inlineStr">
@@ -22686,7 +22686,7 @@
       </c>
       <c r="D310" s="2" t="inlineStr">
         <is>
-          <t>Guys Bodyworks</t>
+          <t>ToyoTechniks</t>
         </is>
       </c>
       <c r="E310" s="2" t="inlineStr">
@@ -22707,12 +22707,12 @@
       <c r="H310" s="2" t="inlineStr"/>
       <c r="I310" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/pages/Guys-Bodyworks-Southport/190128311365007</t>
+          <t>https://www.facebook.com/p/Toyotechniks-100063546062838/</t>
         </is>
       </c>
       <c r="J310" s="2" t="inlineStr">
         <is>
-          <t>+61 7 5532 1392</t>
+          <t>+61 7 5591 1449</t>
         </is>
       </c>
       <c r="K310" s="2" t="inlineStr"/>
@@ -22723,7 +22723,7 @@
       </c>
       <c r="M310" s="2" t="inlineStr">
         <is>
-          <t>Hi Guys Bodyworks team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Guys Bodyworks, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
+          <t>Hi ToyoTechniks team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for ToyoTechniks, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
         </is>
       </c>
       <c r="N310" s="4" t="inlineStr">
@@ -22757,7 +22757,7 @@
       </c>
       <c r="D311" s="2" t="inlineStr">
         <is>
-          <t>ToyoTechniks</t>
+          <t>Woodys Auto Electrics</t>
         </is>
       </c>
       <c r="E311" s="2" t="inlineStr">
@@ -22778,12 +22778,12 @@
       <c r="H311" s="2" t="inlineStr"/>
       <c r="I311" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/p/Toyotechniks-100063546062838/</t>
+          <t>https://www.facebook.com/p/Woodys-Auto-Electrics-100054551465189/</t>
         </is>
       </c>
       <c r="J311" s="2" t="inlineStr">
         <is>
-          <t>+61 7 5591 1449</t>
+          <t>+61 7 5575 2312</t>
         </is>
       </c>
       <c r="K311" s="2" t="inlineStr"/>
@@ -22794,7 +22794,7 @@
       </c>
       <c r="M311" s="2" t="inlineStr">
         <is>
-          <t>Hi ToyoTechniks team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for ToyoTechniks, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
+          <t>Hi Woodys Auto Electrics team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Woodys Auto Electrics, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
         </is>
       </c>
       <c r="N311" s="4" t="inlineStr">
@@ -22828,12 +22828,12 @@
       </c>
       <c r="D312" s="2" t="inlineStr">
         <is>
-          <t>Woodys Auto Electrics</t>
+          <t>Burleigh Pet &amp; Stockfeed Supplies</t>
         </is>
       </c>
       <c r="E312" s="2" t="inlineStr">
         <is>
-          <t>mechanic</t>
+          <t>pet business</t>
         </is>
       </c>
       <c r="F312" s="2" t="inlineStr">
@@ -22849,12 +22849,12 @@
       <c r="H312" s="2" t="inlineStr"/>
       <c r="I312" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/p/Woodys-Auto-Electrics-100054551465189/</t>
+          <t>https://www.facebook.com/pg/Burleigh-Pet-Stockfeed-Supplies-893075937451992/about/</t>
         </is>
       </c>
       <c r="J312" s="2" t="inlineStr">
         <is>
-          <t>+61 7 5575 2312</t>
+          <t>+61 7 5520 6662</t>
         </is>
       </c>
       <c r="K312" s="2" t="inlineStr"/>
@@ -22865,7 +22865,7 @@
       </c>
       <c r="M312" s="2" t="inlineStr">
         <is>
-          <t>Hi Woodys Auto Electrics team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Woodys Auto Electrics, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
+          <t>Hi Burleigh Pet &amp; Stockfeed Supplies team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Burleigh Pet &amp; Stockfeed Supplies, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
         </is>
       </c>
       <c r="N312" s="4" t="inlineStr">
@@ -22899,12 +22899,12 @@
       </c>
       <c r="D313" s="2" t="inlineStr">
         <is>
-          <t>Burleigh Pet &amp; Stockfeed Supplies</t>
+          <t>German Sausages</t>
         </is>
       </c>
       <c r="E313" s="2" t="inlineStr">
         <is>
-          <t>pet business</t>
+          <t>restaurant</t>
         </is>
       </c>
       <c r="F313" s="2" t="inlineStr">
@@ -22920,14 +22920,10 @@
       <c r="H313" s="2" t="inlineStr"/>
       <c r="I313" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/pg/Burleigh-Pet-Stockfeed-Supplies-893075937451992/about/</t>
-        </is>
-      </c>
-      <c r="J313" s="2" t="inlineStr">
-        <is>
-          <t>+61 7 5520 6662</t>
-        </is>
-      </c>
+          <t>https://www.facebook.com/www.facebook.com/pages/german-Sausages</t>
+        </is>
+      </c>
+      <c r="J313" s="2" t="inlineStr"/>
       <c r="K313" s="2" t="inlineStr"/>
       <c r="L313" s="2" t="inlineStr">
         <is>
@@ -22936,7 +22932,7 @@
       </c>
       <c r="M313" s="2" t="inlineStr">
         <is>
-          <t>Hi Burleigh Pet &amp; Stockfeed Supplies team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Burleigh Pet &amp; Stockfeed Supplies, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
+          <t>Hi German Sausages team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for German Sausages, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
         </is>
       </c>
       <c r="N313" s="4" t="inlineStr">
@@ -22970,7 +22966,7 @@
       </c>
       <c r="D314" s="2" t="inlineStr">
         <is>
-          <t>German Sausages</t>
+          <t>Magic Wok Chinese Restaurant</t>
         </is>
       </c>
       <c r="E314" s="2" t="inlineStr">
@@ -22991,10 +22987,14 @@
       <c r="H314" s="2" t="inlineStr"/>
       <c r="I314" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/www.facebook.com/pages/german-Sausages</t>
-        </is>
-      </c>
-      <c r="J314" s="2" t="inlineStr"/>
+          <t>https://www.facebook.com/profile.php?id=100065273629487</t>
+        </is>
+      </c>
+      <c r="J314" s="2" t="inlineStr">
+        <is>
+          <t>+61 7 5535 8619</t>
+        </is>
+      </c>
       <c r="K314" s="2" t="inlineStr"/>
       <c r="L314" s="2" t="inlineStr">
         <is>
@@ -23003,7 +23003,7 @@
       </c>
       <c r="M314" s="2" t="inlineStr">
         <is>
-          <t>Hi German Sausages team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for German Sausages, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
+          <t>Hi Magic Wok Chinese Restaurant team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Magic Wok Chinese Restaurant, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
         </is>
       </c>
       <c r="N314" s="4" t="inlineStr">
@@ -23037,7 +23037,7 @@
       </c>
       <c r="D315" s="2" t="inlineStr">
         <is>
-          <t>Magic Wok Chinese Restaurant</t>
+          <t>Master Sushi</t>
         </is>
       </c>
       <c r="E315" s="2" t="inlineStr">
@@ -23058,12 +23058,12 @@
       <c r="H315" s="2" t="inlineStr"/>
       <c r="I315" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/profile.php?id=100065273629487</t>
+          <t>https://www.facebook.com/pages/Master-Sushi/157277494310497</t>
         </is>
       </c>
       <c r="J315" s="2" t="inlineStr">
         <is>
-          <t>+61 7 5535 8619</t>
+          <t>+61 7 5526 7557</t>
         </is>
       </c>
       <c r="K315" s="2" t="inlineStr"/>
@@ -23074,7 +23074,7 @@
       </c>
       <c r="M315" s="2" t="inlineStr">
         <is>
-          <t>Hi Magic Wok Chinese Restaurant team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Magic Wok Chinese Restaurant, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
+          <t>Hi Master Sushi team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Master Sushi, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
         </is>
       </c>
       <c r="N315" s="4" t="inlineStr">
@@ -23108,7 +23108,7 @@
       </c>
       <c r="D316" s="2" t="inlineStr">
         <is>
-          <t>Master Sushi</t>
+          <t>Michael's Kitchen</t>
         </is>
       </c>
       <c r="E316" s="2" t="inlineStr">
@@ -23129,12 +23129,12 @@
       <c r="H316" s="2" t="inlineStr"/>
       <c r="I316" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/pages/Master-Sushi/157277494310497</t>
+          <t>https://www.facebook.com/p/Michaels-Kitchen-Chinese-Takeaway-100063715285734/</t>
         </is>
       </c>
       <c r="J316" s="2" t="inlineStr">
         <is>
-          <t>+61 7 5526 7557</t>
+          <t>+61 7 5523 1833</t>
         </is>
       </c>
       <c r="K316" s="2" t="inlineStr"/>
@@ -23145,7 +23145,7 @@
       </c>
       <c r="M316" s="2" t="inlineStr">
         <is>
-          <t>Hi Master Sushi team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Master Sushi, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
+          <t>Hi Michael's Kitchen team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Michael's Kitchen, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
         </is>
       </c>
       <c r="N316" s="4" t="inlineStr">
@@ -23179,7 +23179,7 @@
       </c>
       <c r="D317" s="2" t="inlineStr">
         <is>
-          <t>Michael's Kitchen</t>
+          <t>Shogun Japanese</t>
         </is>
       </c>
       <c r="E317" s="2" t="inlineStr">
@@ -23200,12 +23200,12 @@
       <c r="H317" s="2" t="inlineStr"/>
       <c r="I317" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/p/Michaels-Kitchen-Chinese-Takeaway-100063715285734/</t>
+          <t>https://www.facebook.com/goldcoastshogunjapaneserestaurant</t>
         </is>
       </c>
       <c r="J317" s="2" t="inlineStr">
         <is>
-          <t>+61 7 5523 1833</t>
+          <t>+61 7 5528 6998</t>
         </is>
       </c>
       <c r="K317" s="2" t="inlineStr"/>
@@ -23216,7 +23216,7 @@
       </c>
       <c r="M317" s="2" t="inlineStr">
         <is>
-          <t>Hi Michael's Kitchen team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Michael's Kitchen, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
+          <t>Hi Shogun Japanese team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Shogun Japanese, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
         </is>
       </c>
       <c r="N317" s="4" t="inlineStr">
@@ -23250,7 +23250,7 @@
       </c>
       <c r="D318" s="2" t="inlineStr">
         <is>
-          <t>Shogun Japanese</t>
+          <t>Sogno Italiano</t>
         </is>
       </c>
       <c r="E318" s="2" t="inlineStr">
@@ -23271,12 +23271,12 @@
       <c r="H318" s="2" t="inlineStr"/>
       <c r="I318" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/goldcoastshogunjapaneserestaurant</t>
+          <t>https://www.facebook.com/sognoitalian0/</t>
         </is>
       </c>
       <c r="J318" s="2" t="inlineStr">
         <is>
-          <t>+61 7 5528 6998</t>
+          <t>+61 7 5633 4494</t>
         </is>
       </c>
       <c r="K318" s="2" t="inlineStr"/>
@@ -23287,7 +23287,7 @@
       </c>
       <c r="M318" s="2" t="inlineStr">
         <is>
-          <t>Hi Shogun Japanese team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Shogun Japanese, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
+          <t>Hi Sogno Italiano team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Sogno Italiano, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
         </is>
       </c>
       <c r="N318" s="4" t="inlineStr">
@@ -23321,7 +23321,7 @@
       </c>
       <c r="D319" s="2" t="inlineStr">
         <is>
-          <t>Sogno Italiano</t>
+          <t>Supranee’s Pork Crackling</t>
         </is>
       </c>
       <c r="E319" s="2" t="inlineStr">
@@ -23342,12 +23342,12 @@
       <c r="H319" s="2" t="inlineStr"/>
       <c r="I319" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/sognoitalian0/</t>
+          <t>https://www.facebook.com/p/Supranees-pork-crackling-thai-groceries-100064069959236/</t>
         </is>
       </c>
       <c r="J319" s="2" t="inlineStr">
         <is>
-          <t>+61 7 5633 4494</t>
+          <t>+61 7 5533 9284</t>
         </is>
       </c>
       <c r="K319" s="2" t="inlineStr"/>
@@ -23358,7 +23358,7 @@
       </c>
       <c r="M319" s="2" t="inlineStr">
         <is>
-          <t>Hi Sogno Italiano team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Sogno Italiano, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
+          <t>Hi Supranee’s Pork Crackling team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Supranee’s Pork Crackling, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
         </is>
       </c>
       <c r="N319" s="4" t="inlineStr">
@@ -23392,7 +23392,7 @@
       </c>
       <c r="D320" s="2" t="inlineStr">
         <is>
-          <t>Supranee’s Pork Crackling</t>
+          <t>Sushi Train</t>
         </is>
       </c>
       <c r="E320" s="2" t="inlineStr">
@@ -23407,20 +23407,16 @@
       </c>
       <c r="G320" s="2" t="inlineStr">
         <is>
-          <t>Facebook</t>
-        </is>
-      </c>
-      <c r="H320" s="2" t="inlineStr"/>
-      <c r="I320" s="4" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/p/Supranees-pork-crackling-thai-groceries-100064069959236/</t>
-        </is>
-      </c>
-      <c r="J320" s="2" t="inlineStr">
-        <is>
-          <t>+61 7 5533 9284</t>
-        </is>
-      </c>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="H320" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/sushitrain_coomera/</t>
+        </is>
+      </c>
+      <c r="I320" s="2" t="inlineStr"/>
+      <c r="J320" s="2" t="inlineStr"/>
       <c r="K320" s="2" t="inlineStr"/>
       <c r="L320" s="2" t="inlineStr">
         <is>
@@ -23429,7 +23425,7 @@
       </c>
       <c r="M320" s="2" t="inlineStr">
         <is>
-          <t>Hi Supranee’s Pork Crackling team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Supranee’s Pork Crackling, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
+          <t>Hi Sushi Train team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Sushi Train, only your Instagram. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
         </is>
       </c>
       <c r="N320" s="4" t="inlineStr">
@@ -23463,7 +23459,7 @@
       </c>
       <c r="D321" s="2" t="inlineStr">
         <is>
-          <t>Sushi Train</t>
+          <t>Sushi at Palm Beach</t>
         </is>
       </c>
       <c r="E321" s="2" t="inlineStr">
@@ -23478,16 +23474,20 @@
       </c>
       <c r="G321" s="2" t="inlineStr">
         <is>
-          <t>Instagram</t>
-        </is>
-      </c>
-      <c r="H321" s="4" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/sushitrain_coomera/</t>
-        </is>
-      </c>
-      <c r="I321" s="2" t="inlineStr"/>
-      <c r="J321" s="2" t="inlineStr"/>
+          <t>Facebook</t>
+        </is>
+      </c>
+      <c r="H321" s="2" t="inlineStr"/>
+      <c r="I321" s="4" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/SushiAtPalmBeach/</t>
+        </is>
+      </c>
+      <c r="J321" s="2" t="inlineStr">
+        <is>
+          <t>+61 7 5534 6911</t>
+        </is>
+      </c>
       <c r="K321" s="2" t="inlineStr"/>
       <c r="L321" s="2" t="inlineStr">
         <is>
@@ -23496,7 +23496,7 @@
       </c>
       <c r="M321" s="2" t="inlineStr">
         <is>
-          <t>Hi Sushi Train team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Sushi Train, only your Instagram. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
+          <t>Hi Sushi at Palm Beach team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Sushi at Palm Beach, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
         </is>
       </c>
       <c r="N321" s="4" t="inlineStr">
@@ -23530,7 +23530,7 @@
       </c>
       <c r="D322" s="2" t="inlineStr">
         <is>
-          <t>Sushi at Palm Beach</t>
+          <t>The Greek Joint Brews And BBQs</t>
         </is>
       </c>
       <c r="E322" s="2" t="inlineStr">
@@ -23551,12 +23551,12 @@
       <c r="H322" s="2" t="inlineStr"/>
       <c r="I322" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/SushiAtPalmBeach/</t>
+          <t>https://www.facebook.com/thegreekjointburleigh</t>
         </is>
       </c>
       <c r="J322" s="2" t="inlineStr">
         <is>
-          <t>+61 7 5534 6911</t>
+          <t>+61 7 5535 2562</t>
         </is>
       </c>
       <c r="K322" s="2" t="inlineStr"/>
@@ -23567,7 +23567,7 @@
       </c>
       <c r="M322" s="2" t="inlineStr">
         <is>
-          <t>Hi Sushi at Palm Beach team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Sushi at Palm Beach, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
+          <t>Hi The Greek Joint Brews And BBQs team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for The Greek Joint Brews And BBQs, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
         </is>
       </c>
       <c r="N322" s="4" t="inlineStr">
@@ -23601,7 +23601,7 @@
       </c>
       <c r="D323" s="2" t="inlineStr">
         <is>
-          <t>The Greek Joint Brews And BBQs</t>
+          <t>Tokyo Kitchen</t>
         </is>
       </c>
       <c r="E323" s="2" t="inlineStr">
@@ -23616,18 +23616,18 @@
       </c>
       <c r="G323" s="2" t="inlineStr">
         <is>
-          <t>Facebook</t>
-        </is>
-      </c>
-      <c r="H323" s="2" t="inlineStr"/>
-      <c r="I323" s="4" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/thegreekjointburleigh</t>
-        </is>
-      </c>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="H323" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/tokyokitchenpalmbeach/</t>
+        </is>
+      </c>
+      <c r="I323" s="2" t="inlineStr"/>
       <c r="J323" s="2" t="inlineStr">
         <is>
-          <t>+61 7 5535 2562</t>
+          <t>+61 466 924 660</t>
         </is>
       </c>
       <c r="K323" s="2" t="inlineStr"/>
@@ -23638,7 +23638,7 @@
       </c>
       <c r="M323" s="2" t="inlineStr">
         <is>
-          <t>Hi The Greek Joint Brews And BBQs team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for The Greek Joint Brews And BBQs, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
+          <t>Hi Tokyo Kitchen team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Tokyo Kitchen, only your Instagram. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
         </is>
       </c>
       <c r="N323" s="4" t="inlineStr">
@@ -23672,7 +23672,7 @@
       </c>
       <c r="D324" s="2" t="inlineStr">
         <is>
-          <t>Tokyo Kitchen</t>
+          <t>Zhang Liang Malatang</t>
         </is>
       </c>
       <c r="E324" s="2" t="inlineStr">
@@ -23687,20 +23687,16 @@
       </c>
       <c r="G324" s="2" t="inlineStr">
         <is>
-          <t>Instagram</t>
-        </is>
-      </c>
-      <c r="H324" s="4" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/tokyokitchenpalmbeach/</t>
-        </is>
-      </c>
-      <c r="I324" s="2" t="inlineStr"/>
-      <c r="J324" s="2" t="inlineStr">
-        <is>
-          <t>+61 466 924 660</t>
-        </is>
-      </c>
+          <t>Facebook</t>
+        </is>
+      </c>
+      <c r="H324" s="2" t="inlineStr"/>
+      <c r="I324" s="4" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/p/Zhang-Liang-Malatang-Southport-100076346656014/</t>
+        </is>
+      </c>
+      <c r="J324" s="2" t="inlineStr"/>
       <c r="K324" s="2" t="inlineStr"/>
       <c r="L324" s="2" t="inlineStr">
         <is>
@@ -23709,7 +23705,7 @@
       </c>
       <c r="M324" s="2" t="inlineStr">
         <is>
-          <t>Hi Tokyo Kitchen team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Tokyo Kitchen, only your Instagram. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
+          <t>Hi Zhang Liang Malatang team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Zhang Liang Malatang, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
         </is>
       </c>
       <c r="N324" s="4" t="inlineStr">
@@ -23743,12 +23739,12 @@
       </c>
       <c r="D325" s="2" t="inlineStr">
         <is>
-          <t>Zhang Liang Malatang</t>
+          <t>Fat Chicken</t>
         </is>
       </c>
       <c r="E325" s="2" t="inlineStr">
         <is>
-          <t>restaurant</t>
+          <t>takeaway</t>
         </is>
       </c>
       <c r="F325" s="2" t="inlineStr">
@@ -23764,7 +23760,7 @@
       <c r="H325" s="2" t="inlineStr"/>
       <c r="I325" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/p/Zhang-Liang-Malatang-Southport-100076346656014/</t>
+          <t>https://www.facebook.com/people/Fat-Chicken-West-Burleigh/100063635289144/</t>
         </is>
       </c>
       <c r="J325" s="2" t="inlineStr"/>
@@ -23776,7 +23772,7 @@
       </c>
       <c r="M325" s="2" t="inlineStr">
         <is>
-          <t>Hi Zhang Liang Malatang team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Zhang Liang Malatang, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
+          <t>Hi Fat Chicken team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Fat Chicken, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
         </is>
       </c>
       <c r="N325" s="4" t="inlineStr">
@@ -23810,7 +23806,7 @@
       </c>
       <c r="D326" s="2" t="inlineStr">
         <is>
-          <t>Fat Chicken</t>
+          <t>MOFOS Tweed Heads</t>
         </is>
       </c>
       <c r="E326" s="2" t="inlineStr">
@@ -23831,10 +23827,14 @@
       <c r="H326" s="2" t="inlineStr"/>
       <c r="I326" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/people/Fat-Chicken-West-Burleigh/100063635289144/</t>
-        </is>
-      </c>
-      <c r="J326" s="2" t="inlineStr"/>
+          <t>https://www.facebook.com/MOFOSTWEEDHEADS/</t>
+        </is>
+      </c>
+      <c r="J326" s="2" t="inlineStr">
+        <is>
+          <t>+61 434 099 876</t>
+        </is>
+      </c>
       <c r="K326" s="2" t="inlineStr"/>
       <c r="L326" s="2" t="inlineStr">
         <is>
@@ -23843,7 +23843,7 @@
       </c>
       <c r="M326" s="2" t="inlineStr">
         <is>
-          <t>Hi Fat Chicken team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Fat Chicken, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
+          <t>Hi MOFOS Tweed Heads team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for MOFOS Tweed Heads, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
         </is>
       </c>
       <c r="N326" s="4" t="inlineStr">
@@ -23877,7 +23877,7 @@
       </c>
       <c r="D327" s="2" t="inlineStr">
         <is>
-          <t>MOFOS Tweed Heads</t>
+          <t>Notorious E.A.T Food Truck</t>
         </is>
       </c>
       <c r="E327" s="2" t="inlineStr">
@@ -23898,12 +23898,12 @@
       <c r="H327" s="2" t="inlineStr"/>
       <c r="I327" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/MOFOSTWEEDHEADS/</t>
+          <t>https://www.facebook.com/notoriouseat/</t>
         </is>
       </c>
       <c r="J327" s="2" t="inlineStr">
         <is>
-          <t>+61 434 099 876</t>
+          <t>+61 419 472 407</t>
         </is>
       </c>
       <c r="K327" s="2" t="inlineStr"/>
@@ -23914,7 +23914,7 @@
       </c>
       <c r="M327" s="2" t="inlineStr">
         <is>
-          <t>Hi MOFOS Tweed Heads team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for MOFOS Tweed Heads, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
+          <t>Hi Notorious E.A.T Food Truck team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Notorious E.A.T Food Truck, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
         </is>
       </c>
       <c r="N327" s="4" t="inlineStr">
@@ -23948,12 +23948,12 @@
       </c>
       <c r="D328" s="2" t="inlineStr">
         <is>
-          <t>Notorious E.A.T Food Truck</t>
+          <t>Haree Tattoo Studio</t>
         </is>
       </c>
       <c r="E328" s="2" t="inlineStr">
         <is>
-          <t>takeaway</t>
+          <t>tattoo studio</t>
         </is>
       </c>
       <c r="F328" s="2" t="inlineStr">
@@ -23969,14 +23969,10 @@
       <c r="H328" s="2" t="inlineStr"/>
       <c r="I328" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/notoriouseat/</t>
-        </is>
-      </c>
-      <c r="J328" s="2" t="inlineStr">
-        <is>
-          <t>+61 419 472 407</t>
-        </is>
-      </c>
+          <t>https://www.facebook.com/hareetattoostudio/</t>
+        </is>
+      </c>
+      <c r="J328" s="2" t="inlineStr"/>
       <c r="K328" s="2" t="inlineStr"/>
       <c r="L328" s="2" t="inlineStr">
         <is>
@@ -23985,7 +23981,7 @@
       </c>
       <c r="M328" s="2" t="inlineStr">
         <is>
-          <t>Hi Notorious E.A.T Food Truck team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Notorious E.A.T Food Truck, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
+          <t>Hi Haree Tattoo Studio team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Haree Tattoo Studio, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
         </is>
       </c>
       <c r="N328" s="4" t="inlineStr">
@@ -24019,7 +24015,7 @@
       </c>
       <c r="D329" s="2" t="inlineStr">
         <is>
-          <t>Haree Tattoo Studio</t>
+          <t>Inkhanced Cosmetic Tattoo</t>
         </is>
       </c>
       <c r="E329" s="2" t="inlineStr">
@@ -24034,16 +24030,24 @@
       </c>
       <c r="G329" s="2" t="inlineStr">
         <is>
-          <t>Facebook</t>
-        </is>
-      </c>
-      <c r="H329" s="2" t="inlineStr"/>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="H329" s="4" t="inlineStr">
+        <is>
+          <t>https://instagram.com/inkhanced</t>
+        </is>
+      </c>
       <c r="I329" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/hareetattoostudio/</t>
-        </is>
-      </c>
-      <c r="J329" s="2" t="inlineStr"/>
+          <t>https://facebook.com/Inkhanced</t>
+        </is>
+      </c>
+      <c r="J329" s="2" t="inlineStr">
+        <is>
+          <t>+61 406 917 329</t>
+        </is>
+      </c>
       <c r="K329" s="2" t="inlineStr"/>
       <c r="L329" s="2" t="inlineStr">
         <is>
@@ -24052,7 +24056,7 @@
       </c>
       <c r="M329" s="2" t="inlineStr">
         <is>
-          <t>Hi Haree Tattoo Studio team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Haree Tattoo Studio, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
+          <t>Hi Inkhanced Cosmetic Tattoo team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Inkhanced Cosmetic Tattoo, only your Instagram. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
         </is>
       </c>
       <c r="N329" s="4" t="inlineStr">
@@ -24086,7 +24090,7 @@
       </c>
       <c r="D330" s="2" t="inlineStr">
         <is>
-          <t>Inkhanced Cosmetic Tattoo</t>
+          <t>La Femme Tattoo House</t>
         </is>
       </c>
       <c r="E330" s="2" t="inlineStr">
@@ -24106,19 +24110,11 @@
       </c>
       <c r="H330" s="4" t="inlineStr">
         <is>
-          <t>https://instagram.com/inkhanced</t>
-        </is>
-      </c>
-      <c r="I330" s="4" t="inlineStr">
-        <is>
-          <t>https://facebook.com/Inkhanced</t>
-        </is>
-      </c>
-      <c r="J330" s="2" t="inlineStr">
-        <is>
-          <t>+61 406 917 329</t>
-        </is>
-      </c>
+          <t>https://www.instagram.com/lafemmetattoohouse/</t>
+        </is>
+      </c>
+      <c r="I330" s="2" t="inlineStr"/>
+      <c r="J330" s="2" t="inlineStr"/>
       <c r="K330" s="2" t="inlineStr"/>
       <c r="L330" s="2" t="inlineStr">
         <is>
@@ -24127,7 +24123,7 @@
       </c>
       <c r="M330" s="2" t="inlineStr">
         <is>
-          <t>Hi Inkhanced Cosmetic Tattoo team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Inkhanced Cosmetic Tattoo, only your Instagram. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
+          <t>Hi La Femme Tattoo House team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for La Femme Tattoo House, only your Instagram. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
         </is>
       </c>
       <c r="N330" s="4" t="inlineStr">
@@ -24161,7 +24157,7 @@
       </c>
       <c r="D331" s="2" t="inlineStr">
         <is>
-          <t>La Femme Tattoo House</t>
+          <t>Vision Tattoo Studio</t>
         </is>
       </c>
       <c r="E331" s="2" t="inlineStr">
@@ -24181,11 +24177,19 @@
       </c>
       <c r="H331" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/lafemmetattoohouse/</t>
-        </is>
-      </c>
-      <c r="I331" s="2" t="inlineStr"/>
-      <c r="J331" s="2" t="inlineStr"/>
+          <t>https://instagram.com/visiontattoomiami</t>
+        </is>
+      </c>
+      <c r="I331" s="4" t="inlineStr">
+        <is>
+          <t>https://facebook.com/visiontattoomiami</t>
+        </is>
+      </c>
+      <c r="J331" s="2" t="inlineStr">
+        <is>
+          <t>+61 7 5648 1664</t>
+        </is>
+      </c>
       <c r="K331" s="2" t="inlineStr"/>
       <c r="L331" s="2" t="inlineStr">
         <is>
@@ -24194,7 +24198,7 @@
       </c>
       <c r="M331" s="2" t="inlineStr">
         <is>
-          <t>Hi La Femme Tattoo House team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for La Femme Tattoo House, only your Instagram. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
+          <t>Hi Vision Tattoo Studio team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Vision Tattoo Studio, only your Instagram. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
         </is>
       </c>
       <c r="N331" s="4" t="inlineStr">
@@ -24228,37 +24232,33 @@
       </c>
       <c r="D332" s="2" t="inlineStr">
         <is>
-          <t>Vision Tattoo Studio</t>
+          <t>Federal Hotel</t>
         </is>
       </c>
       <c r="E332" s="2" t="inlineStr">
         <is>
-          <t>tattoo studio</t>
+          <t>bar or pub</t>
         </is>
       </c>
       <c r="F332" s="2" t="inlineStr">
         <is>
-          <t>Gold Coast</t>
+          <t>Ipswich</t>
         </is>
       </c>
       <c r="G332" s="2" t="inlineStr">
         <is>
-          <t>Instagram</t>
-        </is>
-      </c>
-      <c r="H332" s="4" t="inlineStr">
-        <is>
-          <t>https://instagram.com/visiontattoomiami</t>
-        </is>
-      </c>
+          <t>Facebook</t>
+        </is>
+      </c>
+      <c r="H332" s="2" t="inlineStr"/>
       <c r="I332" s="4" t="inlineStr">
         <is>
-          <t>https://facebook.com/visiontattoomiami</t>
+          <t>https://www.facebook.com/FederalHotelIpswich/</t>
         </is>
       </c>
       <c r="J332" s="2" t="inlineStr">
         <is>
-          <t>+61 7 5648 1664</t>
+          <t>+61 7 3281 4855</t>
         </is>
       </c>
       <c r="K332" s="2" t="inlineStr"/>
@@ -24269,7 +24269,7 @@
       </c>
       <c r="M332" s="2" t="inlineStr">
         <is>
-          <t>Hi Vision Tattoo Studio team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Vision Tattoo Studio, only your Instagram. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
+          <t>Hi Federal Hotel team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Federal Hotel, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
         </is>
       </c>
       <c r="N332" s="4" t="inlineStr">
@@ -24303,12 +24303,12 @@
       </c>
       <c r="D333" s="2" t="inlineStr">
         <is>
-          <t>Federal Hotel</t>
+          <t>HeavyW8 Barbers</t>
         </is>
       </c>
       <c r="E333" s="2" t="inlineStr">
         <is>
-          <t>bar or pub</t>
+          <t>barber or hairdresser</t>
         </is>
       </c>
       <c r="F333" s="2" t="inlineStr">
@@ -24324,12 +24324,12 @@
       <c r="H333" s="2" t="inlineStr"/>
       <c r="I333" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/FederalHotelIpswich/</t>
+          <t>https://www.facebook.com/HeavyW8Barbers/</t>
         </is>
       </c>
       <c r="J333" s="2" t="inlineStr">
         <is>
-          <t>+61 7 3281 4855</t>
+          <t>+61 411 428 917</t>
         </is>
       </c>
       <c r="K333" s="2" t="inlineStr"/>
@@ -24340,7 +24340,7 @@
       </c>
       <c r="M333" s="2" t="inlineStr">
         <is>
-          <t>Hi Federal Hotel team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Federal Hotel, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
+          <t>Hi HeavyW8 Barbers team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for HeavyW8 Barbers, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
         </is>
       </c>
       <c r="N333" s="4" t="inlineStr">
@@ -24374,12 +24374,12 @@
       </c>
       <c r="D334" s="2" t="inlineStr">
         <is>
-          <t>HeavyW8 Barbers</t>
+          <t>Ellen &amp; Rod Cafe</t>
         </is>
       </c>
       <c r="E334" s="2" t="inlineStr">
         <is>
-          <t>barber or hairdresser</t>
+          <t>cafe</t>
         </is>
       </c>
       <c r="F334" s="2" t="inlineStr">
@@ -24395,12 +24395,12 @@
       <c r="H334" s="2" t="inlineStr"/>
       <c r="I334" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/HeavyW8Barbers/</t>
+          <t>https://www.facebook.com/Ellenandrod/</t>
         </is>
       </c>
       <c r="J334" s="2" t="inlineStr">
         <is>
-          <t>+61 411 428 917</t>
+          <t>+61 488 598 290</t>
         </is>
       </c>
       <c r="K334" s="2" t="inlineStr"/>
@@ -24411,7 +24411,7 @@
       </c>
       <c r="M334" s="2" t="inlineStr">
         <is>
-          <t>Hi HeavyW8 Barbers team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for HeavyW8 Barbers, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
+          <t>Hi Ellen &amp; Rod Cafe team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Ellen &amp; Rod Cafe, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
         </is>
       </c>
       <c r="N334" s="4" t="inlineStr">
@@ -24445,7 +24445,7 @@
       </c>
       <c r="D335" s="2" t="inlineStr">
         <is>
-          <t>Ellen &amp; Rod Cafe</t>
+          <t>The Chambers Cafe</t>
         </is>
       </c>
       <c r="E335" s="2" t="inlineStr">
@@ -24466,12 +24466,12 @@
       <c r="H335" s="2" t="inlineStr"/>
       <c r="I335" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/Ellenandrod/</t>
+          <t>https://www.facebook.com/thechamberscafe</t>
         </is>
       </c>
       <c r="J335" s="2" t="inlineStr">
         <is>
-          <t>+61 488 598 290</t>
+          <t>+61 491 875 347</t>
         </is>
       </c>
       <c r="K335" s="2" t="inlineStr"/>
@@ -24482,7 +24482,7 @@
       </c>
       <c r="M335" s="2" t="inlineStr">
         <is>
-          <t>Hi Ellen &amp; Rod Cafe team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Ellen &amp; Rod Cafe, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
+          <t>Hi The Chambers Cafe team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for The Chambers Cafe, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
         </is>
       </c>
       <c r="N335" s="4" t="inlineStr">
@@ -24516,7 +24516,7 @@
       </c>
       <c r="D336" s="2" t="inlineStr">
         <is>
-          <t>The Chambers Cafe</t>
+          <t>Tower Central Cafe</t>
         </is>
       </c>
       <c r="E336" s="2" t="inlineStr">
@@ -24537,12 +24537,12 @@
       <c r="H336" s="2" t="inlineStr"/>
       <c r="I336" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/thechamberscafe</t>
+          <t>https://www.facebook.com/towercentralcafeipswich/</t>
         </is>
       </c>
       <c r="J336" s="2" t="inlineStr">
         <is>
-          <t>+61 491 875 347</t>
+          <t>+61 7 3812 3157</t>
         </is>
       </c>
       <c r="K336" s="2" t="inlineStr"/>
@@ -24553,7 +24553,7 @@
       </c>
       <c r="M336" s="2" t="inlineStr">
         <is>
-          <t>Hi The Chambers Cafe team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for The Chambers Cafe, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
+          <t>Hi Tower Central Cafe team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Tower Central Cafe, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
         </is>
       </c>
       <c r="N336" s="4" t="inlineStr">
@@ -24587,12 +24587,12 @@
       </c>
       <c r="D337" s="2" t="inlineStr">
         <is>
-          <t>Tower Central Cafe</t>
+          <t>Hoe Inn Food Bar</t>
         </is>
       </c>
       <c r="E337" s="2" t="inlineStr">
         <is>
-          <t>cafe</t>
+          <t>takeaway</t>
         </is>
       </c>
       <c r="F337" s="2" t="inlineStr">
@@ -24608,12 +24608,12 @@
       <c r="H337" s="2" t="inlineStr"/>
       <c r="I337" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/towercentralcafeipswich/</t>
+          <t>https://www.facebook.com/HoeInnFoodBar/</t>
         </is>
       </c>
       <c r="J337" s="2" t="inlineStr">
         <is>
-          <t>+61 7 3812 3157</t>
+          <t>+61 7 3281 3822</t>
         </is>
       </c>
       <c r="K337" s="2" t="inlineStr"/>
@@ -24624,7 +24624,7 @@
       </c>
       <c r="M337" s="2" t="inlineStr">
         <is>
-          <t>Hi Tower Central Cafe team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Tower Central Cafe, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
+          <t>Hi Hoe Inn Food Bar team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Hoe Inn Food Bar, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
         </is>
       </c>
       <c r="N337" s="4" t="inlineStr">
@@ -24658,33 +24658,33 @@
       </c>
       <c r="D338" s="2" t="inlineStr">
         <is>
-          <t>Hoe Inn Food Bar</t>
+          <t>Miaá Lashes</t>
         </is>
       </c>
       <c r="E338" s="2" t="inlineStr">
         <is>
-          <t>takeaway</t>
+          <t>beauty salon</t>
         </is>
       </c>
       <c r="F338" s="2" t="inlineStr">
         <is>
-          <t>Ipswich</t>
+          <t>Logan</t>
         </is>
       </c>
       <c r="G338" s="2" t="inlineStr">
         <is>
-          <t>Facebook</t>
-        </is>
-      </c>
-      <c r="H338" s="2" t="inlineStr"/>
-      <c r="I338" s="4" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/HoeInnFoodBar/</t>
-        </is>
-      </c>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="H338" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/miaalashes_/?igshid=YmMyMTA2M2Y=</t>
+        </is>
+      </c>
+      <c r="I338" s="2" t="inlineStr"/>
       <c r="J338" s="2" t="inlineStr">
         <is>
-          <t>+61 7 3281 3822</t>
+          <t>+61 413 430 741</t>
         </is>
       </c>
       <c r="K338" s="2" t="inlineStr"/>
@@ -24695,7 +24695,7 @@
       </c>
       <c r="M338" s="2" t="inlineStr">
         <is>
-          <t>Hi Hoe Inn Food Bar team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Hoe Inn Food Bar, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
+          <t>Hi Miaá Lashes team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Miaá Lashes, only your Instagram. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
         </is>
       </c>
       <c r="N338" s="4" t="inlineStr">
@@ -24729,33 +24729,33 @@
       </c>
       <c r="D339" s="2" t="inlineStr">
         <is>
-          <t>Miaá Lashes</t>
+          <t>Hot Property Realty</t>
         </is>
       </c>
       <c r="E339" s="2" t="inlineStr">
         <is>
-          <t>beauty salon</t>
+          <t>real estate agent</t>
         </is>
       </c>
       <c r="F339" s="2" t="inlineStr">
         <is>
-          <t>Logan</t>
+          <t>Mackay</t>
         </is>
       </c>
       <c r="G339" s="2" t="inlineStr">
         <is>
-          <t>Instagram</t>
-        </is>
-      </c>
-      <c r="H339" s="4" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/miaalashes_/?igshid=YmMyMTA2M2Y=</t>
-        </is>
-      </c>
-      <c r="I339" s="2" t="inlineStr"/>
+          <t>Facebook</t>
+        </is>
+      </c>
+      <c r="H339" s="2" t="inlineStr"/>
+      <c r="I339" s="4" t="inlineStr">
+        <is>
+          <t>https://facebook.com/hotpropertymackay</t>
+        </is>
+      </c>
       <c r="J339" s="2" t="inlineStr">
         <is>
-          <t>+61 413 430 741</t>
+          <t>+61 7 4942 8855</t>
         </is>
       </c>
       <c r="K339" s="2" t="inlineStr"/>
@@ -24766,7 +24766,7 @@
       </c>
       <c r="M339" s="2" t="inlineStr">
         <is>
-          <t>Hi Miaá Lashes team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Miaá Lashes, only your Instagram. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
+          <t>Hi Hot Property Realty team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Hot Property Realty, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
         </is>
       </c>
       <c r="N339" s="4" t="inlineStr">
@@ -24800,17 +24800,17 @@
       </c>
       <c r="D340" s="2" t="inlineStr">
         <is>
-          <t>Hot Property Realty</t>
+          <t>SG Cafe</t>
         </is>
       </c>
       <c r="E340" s="2" t="inlineStr">
         <is>
-          <t>real estate agent</t>
+          <t>bakery</t>
         </is>
       </c>
       <c r="F340" s="2" t="inlineStr">
         <is>
-          <t>Mackay</t>
+          <t>Moreton Bay</t>
         </is>
       </c>
       <c r="G340" s="2" t="inlineStr">
@@ -24821,12 +24821,12 @@
       <c r="H340" s="2" t="inlineStr"/>
       <c r="I340" s="4" t="inlineStr">
         <is>
-          <t>https://facebook.com/hotpropertymackay</t>
+          <t>https://www.facebook.com/sgcafe.com.au/</t>
         </is>
       </c>
       <c r="J340" s="2" t="inlineStr">
         <is>
-          <t>+61 7 4942 8855</t>
+          <t>+61 7 5432 3071</t>
         </is>
       </c>
       <c r="K340" s="2" t="inlineStr"/>
@@ -24837,7 +24837,7 @@
       </c>
       <c r="M340" s="2" t="inlineStr">
         <is>
-          <t>Hi Hot Property Realty team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Hot Property Realty, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
+          <t>Hi SG Cafe team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for SG Cafe, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
         </is>
       </c>
       <c r="N340" s="4" t="inlineStr">
@@ -24871,12 +24871,12 @@
       </c>
       <c r="D341" s="2" t="inlineStr">
         <is>
-          <t>SG Cafe</t>
+          <t>Cuts on Cresthaven</t>
         </is>
       </c>
       <c r="E341" s="2" t="inlineStr">
         <is>
-          <t>bakery</t>
+          <t>barber or hairdresser</t>
         </is>
       </c>
       <c r="F341" s="2" t="inlineStr">
@@ -24892,12 +24892,12 @@
       <c r="H341" s="2" t="inlineStr"/>
       <c r="I341" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/sgcafe.com.au/</t>
+          <t>https://www.facebook.com/profile.php/?id=100054399854687</t>
         </is>
       </c>
       <c r="J341" s="2" t="inlineStr">
         <is>
-          <t>+61 7 5432 3071</t>
+          <t>+61 7 5499 0042</t>
         </is>
       </c>
       <c r="K341" s="2" t="inlineStr"/>
@@ -24908,7 +24908,7 @@
       </c>
       <c r="M341" s="2" t="inlineStr">
         <is>
-          <t>Hi SG Cafe team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for SG Cafe, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
+          <t>Hi Cuts on Cresthaven team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Cuts on Cresthaven, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
         </is>
       </c>
       <c r="N341" s="4" t="inlineStr">
@@ -24942,7 +24942,7 @@
       </c>
       <c r="D342" s="2" t="inlineStr">
         <is>
-          <t>Cuts on Cresthaven</t>
+          <t>Hair on Archer</t>
         </is>
       </c>
       <c r="E342" s="2" t="inlineStr">
@@ -24963,12 +24963,12 @@
       <c r="H342" s="2" t="inlineStr"/>
       <c r="I342" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/profile.php/?id=100054399854687</t>
+          <t>https://www.facebook.com/haironarcher/</t>
         </is>
       </c>
       <c r="J342" s="2" t="inlineStr">
         <is>
-          <t>+61 7 5499 0042</t>
+          <t>+61 410 882 702</t>
         </is>
       </c>
       <c r="K342" s="2" t="inlineStr"/>
@@ -24979,7 +24979,7 @@
       </c>
       <c r="M342" s="2" t="inlineStr">
         <is>
-          <t>Hi Cuts on Cresthaven team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Cuts on Cresthaven, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
+          <t>Hi Hair on Archer team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Hair on Archer, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
         </is>
       </c>
       <c r="N342" s="4" t="inlineStr">
@@ -25013,12 +25013,12 @@
       </c>
       <c r="D343" s="2" t="inlineStr">
         <is>
-          <t>Hair on Archer</t>
+          <t>Sway on Bribie</t>
         </is>
       </c>
       <c r="E343" s="2" t="inlineStr">
         <is>
-          <t>barber or hairdresser</t>
+          <t>boutique</t>
         </is>
       </c>
       <c r="F343" s="2" t="inlineStr">
@@ -25034,12 +25034,12 @@
       <c r="H343" s="2" t="inlineStr"/>
       <c r="I343" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/haironarcher/</t>
+          <t>https://www.facebook.com/SwayonBribie</t>
         </is>
       </c>
       <c r="J343" s="2" t="inlineStr">
         <is>
-          <t>+61 410 882 702</t>
+          <t>+61 439 757 772</t>
         </is>
       </c>
       <c r="K343" s="2" t="inlineStr"/>
@@ -25050,7 +25050,7 @@
       </c>
       <c r="M343" s="2" t="inlineStr">
         <is>
-          <t>Hi Hair on Archer team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Hair on Archer, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
+          <t>Hi Sway on Bribie team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Sway on Bribie, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
         </is>
       </c>
       <c r="N343" s="4" t="inlineStr">
@@ -25084,12 +25084,12 @@
       </c>
       <c r="D344" s="2" t="inlineStr">
         <is>
-          <t>Sway on Bribie</t>
+          <t>Gather and Feast</t>
         </is>
       </c>
       <c r="E344" s="2" t="inlineStr">
         <is>
-          <t>boutique</t>
+          <t>cafe</t>
         </is>
       </c>
       <c r="F344" s="2" t="inlineStr">
@@ -25105,14 +25105,10 @@
       <c r="H344" s="2" t="inlineStr"/>
       <c r="I344" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/SwayonBribie</t>
-        </is>
-      </c>
-      <c r="J344" s="2" t="inlineStr">
-        <is>
-          <t>+61 439 757 772</t>
-        </is>
-      </c>
+          <t>https://m.facebook.com/gatherandfeastcafe</t>
+        </is>
+      </c>
+      <c r="J344" s="2" t="inlineStr"/>
       <c r="K344" s="2" t="inlineStr"/>
       <c r="L344" s="2" t="inlineStr">
         <is>
@@ -25121,7 +25117,7 @@
       </c>
       <c r="M344" s="2" t="inlineStr">
         <is>
-          <t>Hi Sway on Bribie team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Sway on Bribie, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
+          <t>Hi Gather and Feast team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Gather and Feast, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
         </is>
       </c>
       <c r="N344" s="4" t="inlineStr">
@@ -25155,7 +25151,7 @@
       </c>
       <c r="D345" s="2" t="inlineStr">
         <is>
-          <t>Gather and Feast</t>
+          <t>The Beach Shak Cafe</t>
         </is>
       </c>
       <c r="E345" s="2" t="inlineStr">
@@ -25176,7 +25172,7 @@
       <c r="H345" s="2" t="inlineStr"/>
       <c r="I345" s="4" t="inlineStr">
         <is>
-          <t>https://m.facebook.com/gatherandfeastcafe</t>
+          <t>https://www.facebook.com/thebeachshakcafe/</t>
         </is>
       </c>
       <c r="J345" s="2" t="inlineStr"/>
@@ -25188,7 +25184,7 @@
       </c>
       <c r="M345" s="2" t="inlineStr">
         <is>
-          <t>Hi Gather and Feast team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Gather and Feast, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
+          <t>Hi The Beach Shak Cafe team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for The Beach Shak Cafe, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
         </is>
       </c>
       <c r="N345" s="4" t="inlineStr">
@@ -25222,7 +25218,7 @@
       </c>
       <c r="D346" s="2" t="inlineStr">
         <is>
-          <t>The Beach Shak Cafe</t>
+          <t>Village Deli Bongaree</t>
         </is>
       </c>
       <c r="E346" s="2" t="inlineStr">
@@ -25237,16 +25233,24 @@
       </c>
       <c r="G346" s="2" t="inlineStr">
         <is>
-          <t>Facebook</t>
-        </is>
-      </c>
-      <c r="H346" s="2" t="inlineStr"/>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="H346" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/village_deli_bongaree/</t>
+        </is>
+      </c>
       <c r="I346" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/thebeachshakcafe/</t>
-        </is>
-      </c>
-      <c r="J346" s="2" t="inlineStr"/>
+          <t>https://www.facebook.com/villagedelibongaree</t>
+        </is>
+      </c>
+      <c r="J346" s="2" t="inlineStr">
+        <is>
+          <t>+61 7 3408 4188</t>
+        </is>
+      </c>
       <c r="K346" s="2" t="inlineStr"/>
       <c r="L346" s="2" t="inlineStr">
         <is>
@@ -25255,7 +25259,7 @@
       </c>
       <c r="M346" s="2" t="inlineStr">
         <is>
-          <t>Hi The Beach Shak Cafe team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for The Beach Shak Cafe, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
+          <t>Hi Village Deli Bongaree team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Village Deli Bongaree, only your Instagram. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
         </is>
       </c>
       <c r="N346" s="4" t="inlineStr">
@@ -25289,12 +25293,12 @@
       </c>
       <c r="D347" s="2" t="inlineStr">
         <is>
-          <t>Village Deli Bongaree</t>
+          <t>JEZ Automotive</t>
         </is>
       </c>
       <c r="E347" s="2" t="inlineStr">
         <is>
-          <t>cafe</t>
+          <t>mechanic</t>
         </is>
       </c>
       <c r="F347" s="2" t="inlineStr">
@@ -25304,24 +25308,16 @@
       </c>
       <c r="G347" s="2" t="inlineStr">
         <is>
-          <t>Instagram</t>
-        </is>
-      </c>
-      <c r="H347" s="4" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/village_deli_bongaree/</t>
-        </is>
-      </c>
+          <t>Facebook</t>
+        </is>
+      </c>
+      <c r="H347" s="2" t="inlineStr"/>
       <c r="I347" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/villagedelibongaree</t>
-        </is>
-      </c>
-      <c r="J347" s="2" t="inlineStr">
-        <is>
-          <t>+61 7 3408 4188</t>
-        </is>
-      </c>
+          <t>https://www.facebook.com/JezAutomotive/</t>
+        </is>
+      </c>
+      <c r="J347" s="2" t="inlineStr"/>
       <c r="K347" s="2" t="inlineStr"/>
       <c r="L347" s="2" t="inlineStr">
         <is>
@@ -25330,7 +25326,7 @@
       </c>
       <c r="M347" s="2" t="inlineStr">
         <is>
-          <t>Hi Village Deli Bongaree team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Village Deli Bongaree, only your Instagram. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
+          <t>Hi JEZ Automotive team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for JEZ Automotive, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
         </is>
       </c>
       <c r="N347" s="4" t="inlineStr">
@@ -25364,12 +25360,12 @@
       </c>
       <c r="D348" s="2" t="inlineStr">
         <is>
-          <t>JEZ Automotive</t>
+          <t>Bongaree Pet Food</t>
         </is>
       </c>
       <c r="E348" s="2" t="inlineStr">
         <is>
-          <t>mechanic</t>
+          <t>pet business</t>
         </is>
       </c>
       <c r="F348" s="2" t="inlineStr">
@@ -25385,10 +25381,14 @@
       <c r="H348" s="2" t="inlineStr"/>
       <c r="I348" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/JezAutomotive/</t>
-        </is>
-      </c>
-      <c r="J348" s="2" t="inlineStr"/>
+          <t>https://www.facebook.com/profile.php/?id=100057076285153</t>
+        </is>
+      </c>
+      <c r="J348" s="2" t="inlineStr">
+        <is>
+          <t>+61 455 372 014</t>
+        </is>
+      </c>
       <c r="K348" s="2" t="inlineStr"/>
       <c r="L348" s="2" t="inlineStr">
         <is>
@@ -25397,7 +25397,7 @@
       </c>
       <c r="M348" s="2" t="inlineStr">
         <is>
-          <t>Hi JEZ Automotive team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for JEZ Automotive, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
+          <t>Hi Bongaree Pet Food team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Bongaree Pet Food, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
         </is>
       </c>
       <c r="N348" s="4" t="inlineStr">
@@ -25431,12 +25431,12 @@
       </c>
       <c r="D349" s="2" t="inlineStr">
         <is>
-          <t>Bongaree Pet Food</t>
+          <t>Council Corner Cafe</t>
         </is>
       </c>
       <c r="E349" s="2" t="inlineStr">
         <is>
-          <t>pet business</t>
+          <t>takeaway</t>
         </is>
       </c>
       <c r="F349" s="2" t="inlineStr">
@@ -25452,14 +25452,10 @@
       <c r="H349" s="2" t="inlineStr"/>
       <c r="I349" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/profile.php/?id=100057076285153</t>
-        </is>
-      </c>
-      <c r="J349" s="2" t="inlineStr">
-        <is>
-          <t>+61 455 372 014</t>
-        </is>
-      </c>
+          <t>https://www.facebook.com/p/Council-Corner-Cafe-61560625214132/</t>
+        </is>
+      </c>
+      <c r="J349" s="2" t="inlineStr"/>
       <c r="K349" s="2" t="inlineStr"/>
       <c r="L349" s="2" t="inlineStr">
         <is>
@@ -25468,7 +25464,7 @@
       </c>
       <c r="M349" s="2" t="inlineStr">
         <is>
-          <t>Hi Bongaree Pet Food team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Bongaree Pet Food, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
+          <t>Hi Council Corner Cafe team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Council Corner Cafe, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
         </is>
       </c>
       <c r="N349" s="4" t="inlineStr">
@@ -25502,7 +25498,7 @@
       </c>
       <c r="D350" s="2" t="inlineStr">
         <is>
-          <t>Council Corner Cafe</t>
+          <t>Fishermans Daughter</t>
         </is>
       </c>
       <c r="E350" s="2" t="inlineStr">
@@ -25523,10 +25519,14 @@
       <c r="H350" s="2" t="inlineStr"/>
       <c r="I350" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/p/Council-Corner-Cafe-61560625214132/</t>
-        </is>
-      </c>
-      <c r="J350" s="2" t="inlineStr"/>
+          <t>https://www.facebook.com/fishermansdaughterdeceptionbay/</t>
+        </is>
+      </c>
+      <c r="J350" s="2" t="inlineStr">
+        <is>
+          <t>+61 7 3204 8144</t>
+        </is>
+      </c>
       <c r="K350" s="2" t="inlineStr"/>
       <c r="L350" s="2" t="inlineStr">
         <is>
@@ -25535,7 +25535,7 @@
       </c>
       <c r="M350" s="2" t="inlineStr">
         <is>
-          <t>Hi Council Corner Cafe team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Council Corner Cafe, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
+          <t>Hi Fishermans Daughter team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Fishermans Daughter, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
         </is>
       </c>
       <c r="N350" s="4" t="inlineStr">
@@ -25569,7 +25569,7 @@
       </c>
       <c r="D351" s="2" t="inlineStr">
         <is>
-          <t>Fishermans Daughter</t>
+          <t>Johnny's Pizza Place</t>
         </is>
       </c>
       <c r="E351" s="2" t="inlineStr">
@@ -25590,12 +25590,12 @@
       <c r="H351" s="2" t="inlineStr"/>
       <c r="I351" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/fishermansdaughterdeceptionbay/</t>
+          <t>https://www.facebook.com/johnnyspizzaplace</t>
         </is>
       </c>
       <c r="J351" s="2" t="inlineStr">
         <is>
-          <t>+61 7 3204 8144</t>
+          <t>+61 7 3425 2208</t>
         </is>
       </c>
       <c r="K351" s="2" t="inlineStr"/>
@@ -25606,7 +25606,7 @@
       </c>
       <c r="M351" s="2" t="inlineStr">
         <is>
-          <t>Hi Fishermans Daughter team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Fishermans Daughter, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
+          <t>Hi Johnny's Pizza Place team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Johnny's Pizza Place, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
         </is>
       </c>
       <c r="N351" s="4" t="inlineStr">
@@ -25640,17 +25640,17 @@
       </c>
       <c r="D352" s="2" t="inlineStr">
         <is>
-          <t>Johnny's Pizza Place</t>
+          <t>Emjay Spa &amp; Beauty</t>
         </is>
       </c>
       <c r="E352" s="2" t="inlineStr">
         <is>
-          <t>takeaway</t>
+          <t>beauty salon</t>
         </is>
       </c>
       <c r="F352" s="2" t="inlineStr">
         <is>
-          <t>Moreton Bay</t>
+          <t>Redlands</t>
         </is>
       </c>
       <c r="G352" s="2" t="inlineStr">
@@ -25661,14 +25661,10 @@
       <c r="H352" s="2" t="inlineStr"/>
       <c r="I352" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/johnnyspizzaplace</t>
-        </is>
-      </c>
-      <c r="J352" s="2" t="inlineStr">
-        <is>
-          <t>+61 7 3425 2208</t>
-        </is>
-      </c>
+          <t>https://www.facebook.com/emjaybeautyspa/</t>
+        </is>
+      </c>
+      <c r="J352" s="2" t="inlineStr"/>
       <c r="K352" s="2" t="inlineStr"/>
       <c r="L352" s="2" t="inlineStr">
         <is>
@@ -25677,7 +25673,7 @@
       </c>
       <c r="M352" s="2" t="inlineStr">
         <is>
-          <t>Hi Johnny's Pizza Place team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Johnny's Pizza Place, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
+          <t>Hi Emjay Spa &amp; Beauty team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Emjay Spa &amp; Beauty, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
         </is>
       </c>
       <c r="N352" s="4" t="inlineStr">
@@ -25711,12 +25707,12 @@
       </c>
       <c r="D353" s="2" t="inlineStr">
         <is>
-          <t>Emjay Spa &amp; Beauty</t>
+          <t>Curlew Cafe</t>
         </is>
       </c>
       <c r="E353" s="2" t="inlineStr">
         <is>
-          <t>beauty salon</t>
+          <t>cafe</t>
         </is>
       </c>
       <c r="F353" s="2" t="inlineStr">
@@ -25732,7 +25728,7 @@
       <c r="H353" s="2" t="inlineStr"/>
       <c r="I353" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/emjaybeautyspa/</t>
+          <t>https://www.facebook.com/curlewcoochie</t>
         </is>
       </c>
       <c r="J353" s="2" t="inlineStr"/>
@@ -25744,7 +25740,7 @@
       </c>
       <c r="M353" s="2" t="inlineStr">
         <is>
-          <t>Hi Emjay Spa &amp; Beauty team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Emjay Spa &amp; Beauty, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
+          <t>Hi Curlew Cafe team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Curlew Cafe, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
         </is>
       </c>
       <c r="N353" s="4" t="inlineStr">
@@ -25778,7 +25774,7 @@
       </c>
       <c r="D354" s="2" t="inlineStr">
         <is>
-          <t>Curlew Cafe</t>
+          <t>Pelican Cafe</t>
         </is>
       </c>
       <c r="E354" s="2" t="inlineStr">
@@ -25799,7 +25795,7 @@
       <c r="H354" s="2" t="inlineStr"/>
       <c r="I354" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/curlewcoochie</t>
+          <t>https://www.facebook.com/PelicanCafe293/</t>
         </is>
       </c>
       <c r="J354" s="2" t="inlineStr"/>
@@ -25811,7 +25807,7 @@
       </c>
       <c r="M354" s="2" t="inlineStr">
         <is>
-          <t>Hi Curlew Cafe team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Curlew Cafe, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
+          <t>Hi Pelican Cafe team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Pelican Cafe, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
         </is>
       </c>
       <c r="N354" s="4" t="inlineStr">
@@ -25845,12 +25841,12 @@
       </c>
       <c r="D355" s="2" t="inlineStr">
         <is>
-          <t>Pelican Cafe</t>
+          <t>The Big Mushroom Fruit Barn</t>
         </is>
       </c>
       <c r="E355" s="2" t="inlineStr">
         <is>
-          <t>cafe</t>
+          <t>deli or specialty food</t>
         </is>
       </c>
       <c r="F355" s="2" t="inlineStr">
@@ -25866,10 +25862,14 @@
       <c r="H355" s="2" t="inlineStr"/>
       <c r="I355" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/PelicanCafe293/</t>
-        </is>
-      </c>
-      <c r="J355" s="2" t="inlineStr"/>
+          <t>https://www.facebook.com/103601592445707</t>
+        </is>
+      </c>
+      <c r="J355" s="2" t="inlineStr">
+        <is>
+          <t>+61 490 871 225</t>
+        </is>
+      </c>
       <c r="K355" s="2" t="inlineStr"/>
       <c r="L355" s="2" t="inlineStr">
         <is>
@@ -25878,7 +25878,7 @@
       </c>
       <c r="M355" s="2" t="inlineStr">
         <is>
-          <t>Hi Pelican Cafe team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Pelican Cafe, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
+          <t>Hi The Big Mushroom Fruit Barn team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for The Big Mushroom Fruit Barn, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
         </is>
       </c>
       <c r="N355" s="4" t="inlineStr">
@@ -25912,12 +25912,12 @@
       </c>
       <c r="D356" s="2" t="inlineStr">
         <is>
-          <t>The Big Mushroom Fruit Barn</t>
+          <t>Top Gun Restorations</t>
         </is>
       </c>
       <c r="E356" s="2" t="inlineStr">
         <is>
-          <t>deli or specialty food</t>
+          <t>mechanic</t>
         </is>
       </c>
       <c r="F356" s="2" t="inlineStr">
@@ -25933,14 +25933,10 @@
       <c r="H356" s="2" t="inlineStr"/>
       <c r="I356" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/103601592445707</t>
-        </is>
-      </c>
-      <c r="J356" s="2" t="inlineStr">
-        <is>
-          <t>+61 490 871 225</t>
-        </is>
-      </c>
+          <t>https://www.facebook.com/p/Top-Gun-Restoration-100063707569188</t>
+        </is>
+      </c>
+      <c r="J356" s="2" t="inlineStr"/>
       <c r="K356" s="2" t="inlineStr"/>
       <c r="L356" s="2" t="inlineStr">
         <is>
@@ -25949,7 +25945,7 @@
       </c>
       <c r="M356" s="2" t="inlineStr">
         <is>
-          <t>Hi The Big Mushroom Fruit Barn team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for The Big Mushroom Fruit Barn, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
+          <t>Hi Top Gun Restorations team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Top Gun Restorations, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
         </is>
       </c>
       <c r="N356" s="4" t="inlineStr">
@@ -25983,12 +25979,12 @@
       </c>
       <c r="D357" s="2" t="inlineStr">
         <is>
-          <t>Top Gun Restorations</t>
+          <t>Koala Park Veterinary Surgery</t>
         </is>
       </c>
       <c r="E357" s="2" t="inlineStr">
         <is>
-          <t>mechanic</t>
+          <t>pet business</t>
         </is>
       </c>
       <c r="F357" s="2" t="inlineStr">
@@ -26004,10 +26000,14 @@
       <c r="H357" s="2" t="inlineStr"/>
       <c r="I357" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/p/Top-Gun-Restoration-100063707569188</t>
-        </is>
-      </c>
-      <c r="J357" s="2" t="inlineStr"/>
+          <t>https://www.facebook.com/KoalaParkVeterinarySurgery?mibextid=ZbWKwL</t>
+        </is>
+      </c>
+      <c r="J357" s="2" t="inlineStr">
+        <is>
+          <t>+61 7 3207 6041</t>
+        </is>
+      </c>
       <c r="K357" s="2" t="inlineStr"/>
       <c r="L357" s="2" t="inlineStr">
         <is>
@@ -26016,7 +26016,7 @@
       </c>
       <c r="M357" s="2" t="inlineStr">
         <is>
-          <t>Hi Top Gun Restorations team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Top Gun Restorations, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
+          <t>Hi Koala Park Veterinary Surgery team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Koala Park Veterinary Surgery, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
         </is>
       </c>
       <c r="N357" s="4" t="inlineStr">
@@ -26050,12 +26050,12 @@
       </c>
       <c r="D358" s="2" t="inlineStr">
         <is>
-          <t>Koala Park Veterinary Surgery</t>
+          <t>Coochiemudlo Island Beach Bar and Grill</t>
         </is>
       </c>
       <c r="E358" s="2" t="inlineStr">
         <is>
-          <t>pet business</t>
+          <t>restaurant</t>
         </is>
       </c>
       <c r="F358" s="2" t="inlineStr">
@@ -26071,12 +26071,12 @@
       <c r="H358" s="2" t="inlineStr"/>
       <c r="I358" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/KoalaParkVeterinarySurgery?mibextid=ZbWKwL</t>
+          <t>https://www.facebook.com/coochiemudloislandbeachbar</t>
         </is>
       </c>
       <c r="J358" s="2" t="inlineStr">
         <is>
-          <t>+61 7 3207 6041</t>
+          <t>+61 484 064 014</t>
         </is>
       </c>
       <c r="K358" s="2" t="inlineStr"/>
@@ -26087,7 +26087,7 @@
       </c>
       <c r="M358" s="2" t="inlineStr">
         <is>
-          <t>Hi Koala Park Veterinary Surgery team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Koala Park Veterinary Surgery, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
+          <t>Hi Coochiemudlo Island Beach Bar and Grill team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Coochiemudlo Island Beach Bar and Grill, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
         </is>
       </c>
       <c r="N358" s="4" t="inlineStr">
@@ -26121,12 +26121,12 @@
       </c>
       <c r="D359" s="2" t="inlineStr">
         <is>
-          <t>Coochiemudlo Island Beach Bar and Grill</t>
+          <t>Jetty Store II</t>
         </is>
       </c>
       <c r="E359" s="2" t="inlineStr">
         <is>
-          <t>restaurant</t>
+          <t>takeaway</t>
         </is>
       </c>
       <c r="F359" s="2" t="inlineStr">
@@ -26142,12 +26142,12 @@
       <c r="H359" s="2" t="inlineStr"/>
       <c r="I359" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/coochiemudloislandbeachbar</t>
+          <t>https://www.facebook.com/TheJettyStore/</t>
         </is>
       </c>
       <c r="J359" s="2" t="inlineStr">
         <is>
-          <t>+61 484 064 014</t>
+          <t>+61 7 3206 7674</t>
         </is>
       </c>
       <c r="K359" s="2" t="inlineStr"/>
@@ -26158,7 +26158,7 @@
       </c>
       <c r="M359" s="2" t="inlineStr">
         <is>
-          <t>Hi Coochiemudlo Island Beach Bar and Grill team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Coochiemudlo Island Beach Bar and Grill, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
+          <t>Hi Jetty Store II team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Jetty Store II, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
         </is>
       </c>
       <c r="N359" s="4" t="inlineStr">
@@ -26192,33 +26192,37 @@
       </c>
       <c r="D360" s="2" t="inlineStr">
         <is>
-          <t>Jetty Store II</t>
+          <t>The Bakers Pantry</t>
         </is>
       </c>
       <c r="E360" s="2" t="inlineStr">
         <is>
-          <t>takeaway</t>
+          <t>bakery</t>
         </is>
       </c>
       <c r="F360" s="2" t="inlineStr">
         <is>
-          <t>Redlands</t>
+          <t>Sunshine Coast</t>
         </is>
       </c>
       <c r="G360" s="2" t="inlineStr">
         <is>
-          <t>Facebook</t>
-        </is>
-      </c>
-      <c r="H360" s="2" t="inlineStr"/>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="H360" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/thebakerspantrynoosa</t>
+        </is>
+      </c>
       <c r="I360" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/TheJettyStore/</t>
+          <t>https://www.facebook.com/thebakerspantrynoosa</t>
         </is>
       </c>
       <c r="J360" s="2" t="inlineStr">
         <is>
-          <t>+61 7 3206 7674</t>
+          <t>+61 7 5448 0780</t>
         </is>
       </c>
       <c r="K360" s="2" t="inlineStr"/>
@@ -26229,7 +26233,7 @@
       </c>
       <c r="M360" s="2" t="inlineStr">
         <is>
-          <t>Hi Jetty Store II team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Jetty Store II, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
+          <t>Hi The Bakers Pantry team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for The Bakers Pantry, only your Instagram. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
         </is>
       </c>
       <c r="N360" s="4" t="inlineStr">
@@ -26263,12 +26267,12 @@
       </c>
       <c r="D361" s="2" t="inlineStr">
         <is>
-          <t>The Bakers Pantry</t>
+          <t>Homegrown Cafe</t>
         </is>
       </c>
       <c r="E361" s="2" t="inlineStr">
         <is>
-          <t>bakery</t>
+          <t>cafe</t>
         </is>
       </c>
       <c r="F361" s="2" t="inlineStr">
@@ -26278,22 +26282,18 @@
       </c>
       <c r="G361" s="2" t="inlineStr">
         <is>
-          <t>Instagram</t>
-        </is>
-      </c>
-      <c r="H361" s="4" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/thebakerspantrynoosa</t>
-        </is>
-      </c>
+          <t>Facebook</t>
+        </is>
+      </c>
+      <c r="H361" s="2" t="inlineStr"/>
       <c r="I361" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/thebakerspantrynoosa</t>
+          <t>https://www.facebook.com/homegrownpalmwoods/</t>
         </is>
       </c>
       <c r="J361" s="2" t="inlineStr">
         <is>
-          <t>+61 7 5448 0780</t>
+          <t>+61 458 270 368</t>
         </is>
       </c>
       <c r="K361" s="2" t="inlineStr"/>
@@ -26304,7 +26304,7 @@
       </c>
       <c r="M361" s="2" t="inlineStr">
         <is>
-          <t>Hi The Bakers Pantry team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for The Bakers Pantry, only your Instagram. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
+          <t>Hi Homegrown Cafe team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Homegrown Cafe, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
         </is>
       </c>
       <c r="N361" s="4" t="inlineStr">
@@ -26338,7 +26338,7 @@
       </c>
       <c r="D362" s="2" t="inlineStr">
         <is>
-          <t>Homegrown Cafe</t>
+          <t>Nambour Social</t>
         </is>
       </c>
       <c r="E362" s="2" t="inlineStr">
@@ -26359,14 +26359,10 @@
       <c r="H362" s="2" t="inlineStr"/>
       <c r="I362" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/homegrownpalmwoods/</t>
-        </is>
-      </c>
-      <c r="J362" s="2" t="inlineStr">
-        <is>
-          <t>+61 458 270 368</t>
-        </is>
-      </c>
+          <t>https://www.facebook.com/namboursocial</t>
+        </is>
+      </c>
+      <c r="J362" s="2" t="inlineStr"/>
       <c r="K362" s="2" t="inlineStr"/>
       <c r="L362" s="2" t="inlineStr">
         <is>
@@ -26375,7 +26371,7 @@
       </c>
       <c r="M362" s="2" t="inlineStr">
         <is>
-          <t>Hi Homegrown Cafe team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Homegrown Cafe, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
+          <t>Hi Nambour Social team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Nambour Social, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
         </is>
       </c>
       <c r="N362" s="4" t="inlineStr">
@@ -26409,7 +26405,7 @@
       </c>
       <c r="D363" s="2" t="inlineStr">
         <is>
-          <t>Nambour Social</t>
+          <t>Press at Noosa</t>
         </is>
       </c>
       <c r="E363" s="2" t="inlineStr">
@@ -26430,7 +26426,7 @@
       <c r="H363" s="2" t="inlineStr"/>
       <c r="I363" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/namboursocial</t>
+          <t>https://www.facebook.com/profile.php?id=100054504337824</t>
         </is>
       </c>
       <c r="J363" s="2" t="inlineStr"/>
@@ -26442,7 +26438,7 @@
       </c>
       <c r="M363" s="2" t="inlineStr">
         <is>
-          <t>Hi Nambour Social team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Nambour Social, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
+          <t>Hi Press at Noosa team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Press at Noosa, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
         </is>
       </c>
       <c r="N363" s="4" t="inlineStr">
@@ -26476,12 +26472,12 @@
       </c>
       <c r="D364" s="2" t="inlineStr">
         <is>
-          <t>Press at Noosa</t>
+          <t>Brown Sugar Espresso</t>
         </is>
       </c>
       <c r="E364" s="2" t="inlineStr">
         <is>
-          <t>cafe</t>
+          <t>deli or specialty food</t>
         </is>
       </c>
       <c r="F364" s="2" t="inlineStr">
@@ -26497,7 +26493,7 @@
       <c r="H364" s="2" t="inlineStr"/>
       <c r="I364" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/profile.php?id=100054504337824</t>
+          <t>https://www.facebook.com/brownsugarespressonambour/</t>
         </is>
       </c>
       <c r="J364" s="2" t="inlineStr"/>
@@ -26509,7 +26505,7 @@
       </c>
       <c r="M364" s="2" t="inlineStr">
         <is>
-          <t>Hi Press at Noosa team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Press at Noosa, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
+          <t>Hi Brown Sugar Espresso team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Brown Sugar Espresso, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
         </is>
       </c>
       <c r="N364" s="4" t="inlineStr">
@@ -26543,7 +26539,7 @@
       </c>
       <c r="D365" s="2" t="inlineStr">
         <is>
-          <t>Brown Sugar Espresso</t>
+          <t>Yandina Market Garden</t>
         </is>
       </c>
       <c r="E365" s="2" t="inlineStr">
@@ -26564,10 +26560,14 @@
       <c r="H365" s="2" t="inlineStr"/>
       <c r="I365" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/brownsugarespressonambour/</t>
-        </is>
-      </c>
-      <c r="J365" s="2" t="inlineStr"/>
+          <t>https://www.facebook.com/yandinamarketgarden/</t>
+        </is>
+      </c>
+      <c r="J365" s="2" t="inlineStr">
+        <is>
+          <t>+61 7 5446 8944</t>
+        </is>
+      </c>
       <c r="K365" s="2" t="inlineStr"/>
       <c r="L365" s="2" t="inlineStr">
         <is>
@@ -26576,7 +26576,7 @@
       </c>
       <c r="M365" s="2" t="inlineStr">
         <is>
-          <t>Hi Brown Sugar Espresso team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Brown Sugar Espresso, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
+          <t>Hi Yandina Market Garden team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Yandina Market Garden, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
         </is>
       </c>
       <c r="N365" s="4" t="inlineStr">
@@ -26610,12 +26610,12 @@
       </c>
       <c r="D366" s="2" t="inlineStr">
         <is>
-          <t>Yandina Market Garden</t>
+          <t>Suncoast Mechanical</t>
         </is>
       </c>
       <c r="E366" s="2" t="inlineStr">
         <is>
-          <t>deli or specialty food</t>
+          <t>mechanic</t>
         </is>
       </c>
       <c r="F366" s="2" t="inlineStr">
@@ -26631,14 +26631,10 @@
       <c r="H366" s="2" t="inlineStr"/>
       <c r="I366" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/yandinamarketgarden/</t>
-        </is>
-      </c>
-      <c r="J366" s="2" t="inlineStr">
-        <is>
-          <t>+61 7 5446 8944</t>
-        </is>
-      </c>
+          <t>https://www.facebook.com/SuncoastMechanical/</t>
+        </is>
+      </c>
+      <c r="J366" s="2" t="inlineStr"/>
       <c r="K366" s="2" t="inlineStr"/>
       <c r="L366" s="2" t="inlineStr">
         <is>
@@ -26647,7 +26643,7 @@
       </c>
       <c r="M366" s="2" t="inlineStr">
         <is>
-          <t>Hi Yandina Market Garden team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Yandina Market Garden, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
+          <t>Hi Suncoast Mechanical team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Suncoast Mechanical, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
         </is>
       </c>
       <c r="N366" s="4" t="inlineStr">
@@ -26681,12 +26677,12 @@
       </c>
       <c r="D367" s="2" t="inlineStr">
         <is>
-          <t>Suncoast Mechanical</t>
+          <t>J J Sushi</t>
         </is>
       </c>
       <c r="E367" s="2" t="inlineStr">
         <is>
-          <t>mechanic</t>
+          <t>restaurant</t>
         </is>
       </c>
       <c r="F367" s="2" t="inlineStr">
@@ -26702,10 +26698,14 @@
       <c r="H367" s="2" t="inlineStr"/>
       <c r="I367" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/SuncoastMechanical/</t>
-        </is>
-      </c>
-      <c r="J367" s="2" t="inlineStr"/>
+          <t>https://www.facebook.com/jjsushichicken/</t>
+        </is>
+      </c>
+      <c r="J367" s="2" t="inlineStr">
+        <is>
+          <t>+61 480 253 468</t>
+        </is>
+      </c>
       <c r="K367" s="2" t="inlineStr"/>
       <c r="L367" s="2" t="inlineStr">
         <is>
@@ -26714,7 +26714,7 @@
       </c>
       <c r="M367" s="2" t="inlineStr">
         <is>
-          <t>Hi Suncoast Mechanical team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Suncoast Mechanical, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
+          <t>Hi J J Sushi team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for J J Sushi, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
         </is>
       </c>
       <c r="N367" s="4" t="inlineStr">
@@ -26748,35 +26748,35 @@
       </c>
       <c r="D368" s="2" t="inlineStr">
         <is>
-          <t>J J Sushi</t>
+          <t>MM&amp;</t>
         </is>
       </c>
       <c r="E368" s="2" t="inlineStr">
         <is>
-          <t>restaurant</t>
+          <t>bakery</t>
         </is>
       </c>
       <c r="F368" s="2" t="inlineStr">
         <is>
-          <t>Sunshine Coast</t>
+          <t>Townsville</t>
         </is>
       </c>
       <c r="G368" s="2" t="inlineStr">
         <is>
-          <t>Facebook</t>
-        </is>
-      </c>
-      <c r="H368" s="2" t="inlineStr"/>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="H368" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/mmandcoffeebaking</t>
+        </is>
+      </c>
       <c r="I368" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/jjsushichicken/</t>
-        </is>
-      </c>
-      <c r="J368" s="2" t="inlineStr">
-        <is>
-          <t>+61 480 253 468</t>
-        </is>
-      </c>
+          <t>https://www.facebook.com/mmandcoffeebaking/</t>
+        </is>
+      </c>
+      <c r="J368" s="2" t="inlineStr"/>
       <c r="K368" s="2" t="inlineStr"/>
       <c r="L368" s="2" t="inlineStr">
         <is>
@@ -26785,7 +26785,7 @@
       </c>
       <c r="M368" s="2" t="inlineStr">
         <is>
-          <t>Hi J J Sushi team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for J J Sushi, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
+          <t>Hi MM&amp; team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for MM&amp;, only your Instagram. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
         </is>
       </c>
       <c r="N368" s="4" t="inlineStr">
@@ -26819,12 +26819,12 @@
       </c>
       <c r="D369" s="2" t="inlineStr">
         <is>
-          <t>MM&amp;</t>
+          <t>Hotel Allen</t>
         </is>
       </c>
       <c r="E369" s="2" t="inlineStr">
         <is>
-          <t>bakery</t>
+          <t>bar or pub</t>
         </is>
       </c>
       <c r="F369" s="2" t="inlineStr">
@@ -26834,20 +26834,20 @@
       </c>
       <c r="G369" s="2" t="inlineStr">
         <is>
-          <t>Instagram</t>
-        </is>
-      </c>
-      <c r="H369" s="4" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/mmandcoffeebaking</t>
-        </is>
-      </c>
+          <t>Facebook</t>
+        </is>
+      </c>
+      <c r="H369" s="2" t="inlineStr"/>
       <c r="I369" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/mmandcoffeebaking/</t>
-        </is>
-      </c>
-      <c r="J369" s="2" t="inlineStr"/>
+          <t>https://www.facebook.com/hotelallentownsville</t>
+        </is>
+      </c>
+      <c r="J369" s="2" t="inlineStr">
+        <is>
+          <t>+61 7 3051 7692</t>
+        </is>
+      </c>
       <c r="K369" s="2" t="inlineStr"/>
       <c r="L369" s="2" t="inlineStr">
         <is>
@@ -26856,7 +26856,7 @@
       </c>
       <c r="M369" s="2" t="inlineStr">
         <is>
-          <t>Hi MM&amp; team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for MM&amp;, only your Instagram. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
+          <t>Hi Hotel Allen team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Hotel Allen, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
         </is>
       </c>
       <c r="N369" s="4" t="inlineStr">
@@ -26890,12 +26890,12 @@
       </c>
       <c r="D370" s="2" t="inlineStr">
         <is>
-          <t>Hotel Allen</t>
+          <t>Lads 'n' Ladies Barber Shop</t>
         </is>
       </c>
       <c r="E370" s="2" t="inlineStr">
         <is>
-          <t>bar or pub</t>
+          <t>barber or hairdresser</t>
         </is>
       </c>
       <c r="F370" s="2" t="inlineStr">
@@ -26911,12 +26911,12 @@
       <c r="H370" s="2" t="inlineStr"/>
       <c r="I370" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/hotelallentownsville</t>
+          <t>https://www.facebook.com/p/Lads-n-Ladies-Barber-Shop-100069962165987/</t>
         </is>
       </c>
       <c r="J370" s="2" t="inlineStr">
         <is>
-          <t>+61 7 3051 7692</t>
+          <t>+61 7 4723 6234</t>
         </is>
       </c>
       <c r="K370" s="2" t="inlineStr"/>
@@ -26927,7 +26927,7 @@
       </c>
       <c r="M370" s="2" t="inlineStr">
         <is>
-          <t>Hi Hotel Allen team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Hotel Allen, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
+          <t>Hi Lads 'n' Ladies Barber Shop team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Lads 'n' Ladies Barber Shop, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
         </is>
       </c>
       <c r="N370" s="4" t="inlineStr">
@@ -26961,12 +26961,12 @@
       </c>
       <c r="D371" s="2" t="inlineStr">
         <is>
-          <t>Lads 'n' Ladies Barber Shop</t>
+          <t>Artside</t>
         </is>
       </c>
       <c r="E371" s="2" t="inlineStr">
         <is>
-          <t>barber or hairdresser</t>
+          <t>beauty salon</t>
         </is>
       </c>
       <c r="F371" s="2" t="inlineStr">
@@ -26976,20 +26976,16 @@
       </c>
       <c r="G371" s="2" t="inlineStr">
         <is>
-          <t>Facebook</t>
-        </is>
-      </c>
-      <c r="H371" s="2" t="inlineStr"/>
-      <c r="I371" s="4" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/p/Lads-n-Ladies-Barber-Shop-100069962165987/</t>
-        </is>
-      </c>
-      <c r="J371" s="2" t="inlineStr">
-        <is>
-          <t>+61 7 4723 6234</t>
-        </is>
-      </c>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="H371" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/artside.studio</t>
+        </is>
+      </c>
+      <c r="I371" s="2" t="inlineStr"/>
+      <c r="J371" s="2" t="inlineStr"/>
       <c r="K371" s="2" t="inlineStr"/>
       <c r="L371" s="2" t="inlineStr">
         <is>
@@ -26998,7 +26994,7 @@
       </c>
       <c r="M371" s="2" t="inlineStr">
         <is>
-          <t>Hi Lads 'n' Ladies Barber Shop team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Lads 'n' Ladies Barber Shop, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
+          <t>Hi Artside team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Artside, only your Instagram. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
         </is>
       </c>
       <c r="N371" s="4" t="inlineStr">
@@ -27032,7 +27028,7 @@
       </c>
       <c r="D372" s="2" t="inlineStr">
         <is>
-          <t>Artside</t>
+          <t>Leena's Nail and Beauty</t>
         </is>
       </c>
       <c r="E372" s="2" t="inlineStr">
@@ -27047,16 +27043,20 @@
       </c>
       <c r="G372" s="2" t="inlineStr">
         <is>
-          <t>Instagram</t>
-        </is>
-      </c>
-      <c r="H372" s="4" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/artside.studio</t>
-        </is>
-      </c>
-      <c r="I372" s="2" t="inlineStr"/>
-      <c r="J372" s="2" t="inlineStr"/>
+          <t>Facebook</t>
+        </is>
+      </c>
+      <c r="H372" s="2" t="inlineStr"/>
+      <c r="I372" s="4" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/QueensNailsNBeauty</t>
+        </is>
+      </c>
+      <c r="J372" s="2" t="inlineStr">
+        <is>
+          <t>+61 401 774 252</t>
+        </is>
+      </c>
       <c r="K372" s="2" t="inlineStr"/>
       <c r="L372" s="2" t="inlineStr">
         <is>
@@ -27065,7 +27065,7 @@
       </c>
       <c r="M372" s="2" t="inlineStr">
         <is>
-          <t>Hi Artside team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Artside, only your Instagram. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
+          <t>Hi Leena's Nail and Beauty team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Leena's Nail and Beauty, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
         </is>
       </c>
       <c r="N372" s="4" t="inlineStr">
@@ -27099,12 +27099,12 @@
       </c>
       <c r="D373" s="2" t="inlineStr">
         <is>
-          <t>Leena's Nail and Beauty</t>
+          <t>Axell Rose</t>
         </is>
       </c>
       <c r="E373" s="2" t="inlineStr">
         <is>
-          <t>beauty salon</t>
+          <t>boutique</t>
         </is>
       </c>
       <c r="F373" s="2" t="inlineStr">
@@ -27114,18 +27114,22 @@
       </c>
       <c r="G373" s="2" t="inlineStr">
         <is>
-          <t>Facebook</t>
-        </is>
-      </c>
-      <c r="H373" s="2" t="inlineStr"/>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="H373" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/axellroseboutique</t>
+        </is>
+      </c>
       <c r="I373" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/QueensNailsNBeauty</t>
+          <t>https://www.facebook.com/Axell-Rose-Boutique-102241341219356/</t>
         </is>
       </c>
       <c r="J373" s="2" t="inlineStr">
         <is>
-          <t>+61 401 774 252</t>
+          <t>+61 417 079 165</t>
         </is>
       </c>
       <c r="K373" s="2" t="inlineStr"/>
@@ -27136,7 +27140,7 @@
       </c>
       <c r="M373" s="2" t="inlineStr">
         <is>
-          <t>Hi Leena's Nail and Beauty team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Leena's Nail and Beauty, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
+          <t>Hi Axell Rose team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Axell Rose, only your Instagram. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
         </is>
       </c>
       <c r="N373" s="4" t="inlineStr">
@@ -27170,7 +27174,7 @@
       </c>
       <c r="D374" s="2" t="inlineStr">
         <is>
-          <t>Axell Rose</t>
+          <t>Summer Land</t>
         </is>
       </c>
       <c r="E374" s="2" t="inlineStr">
@@ -27190,17 +27194,13 @@
       </c>
       <c r="H374" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/axellroseboutique</t>
-        </is>
-      </c>
-      <c r="I374" s="4" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/Axell-Rose-Boutique-102241341219356/</t>
-        </is>
-      </c>
+          <t>https://www.instagram.com/summerland_aus</t>
+        </is>
+      </c>
+      <c r="I374" s="2" t="inlineStr"/>
       <c r="J374" s="2" t="inlineStr">
         <is>
-          <t>+61 417 079 165</t>
+          <t>+61 7 4724 2346</t>
         </is>
       </c>
       <c r="K374" s="2" t="inlineStr"/>
@@ -27211,7 +27211,7 @@
       </c>
       <c r="M374" s="2" t="inlineStr">
         <is>
-          <t>Hi Axell Rose team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Axell Rose, only your Instagram. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
+          <t>Hi Summer Land team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Summer Land, only your Instagram. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
         </is>
       </c>
       <c r="N374" s="4" t="inlineStr">
@@ -27245,7 +27245,7 @@
       </c>
       <c r="D375" s="2" t="inlineStr">
         <is>
-          <t>Summer Land</t>
+          <t>Urban Loft Lifestyle</t>
         </is>
       </c>
       <c r="E375" s="2" t="inlineStr">
@@ -27260,18 +27260,18 @@
       </c>
       <c r="G375" s="2" t="inlineStr">
         <is>
-          <t>Instagram</t>
-        </is>
-      </c>
-      <c r="H375" s="4" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/summerland_aus</t>
-        </is>
-      </c>
-      <c r="I375" s="2" t="inlineStr"/>
+          <t>Facebook</t>
+        </is>
+      </c>
+      <c r="H375" s="2" t="inlineStr"/>
+      <c r="I375" s="4" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/northwardtownsville</t>
+        </is>
+      </c>
       <c r="J375" s="2" t="inlineStr">
         <is>
-          <t>+61 7 4724 2346</t>
+          <t>+61 7 4724 5665</t>
         </is>
       </c>
       <c r="K375" s="2" t="inlineStr"/>
@@ -27282,7 +27282,7 @@
       </c>
       <c r="M375" s="2" t="inlineStr">
         <is>
-          <t>Hi Summer Land team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Summer Land, only your Instagram. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
+          <t>Hi Urban Loft Lifestyle team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Urban Loft Lifestyle, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
         </is>
       </c>
       <c r="N375" s="4" t="inlineStr">
@@ -27316,12 +27316,12 @@
       </c>
       <c r="D376" s="2" t="inlineStr">
         <is>
-          <t>Urban Loft Lifestyle</t>
+          <t>Balabite</t>
         </is>
       </c>
       <c r="E376" s="2" t="inlineStr">
         <is>
-          <t>boutique</t>
+          <t>cafe</t>
         </is>
       </c>
       <c r="F376" s="2" t="inlineStr">
@@ -27331,20 +27331,20 @@
       </c>
       <c r="G376" s="2" t="inlineStr">
         <is>
-          <t>Facebook</t>
-        </is>
-      </c>
-      <c r="H376" s="2" t="inlineStr"/>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="H376" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/balabite</t>
+        </is>
+      </c>
       <c r="I376" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/northwardtownsville</t>
-        </is>
-      </c>
-      <c r="J376" s="2" t="inlineStr">
-        <is>
-          <t>+61 7 4724 5665</t>
-        </is>
-      </c>
+          <t>https://www.facebook.com/balabite/</t>
+        </is>
+      </c>
+      <c r="J376" s="2" t="inlineStr"/>
       <c r="K376" s="2" t="inlineStr"/>
       <c r="L376" s="2" t="inlineStr">
         <is>
@@ -27353,7 +27353,7 @@
       </c>
       <c r="M376" s="2" t="inlineStr">
         <is>
-          <t>Hi Urban Loft Lifestyle team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Urban Loft Lifestyle, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
+          <t>Hi Balabite team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Balabite, only your Instagram. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
         </is>
       </c>
       <c r="N376" s="4" t="inlineStr">
@@ -27387,7 +27387,7 @@
       </c>
       <c r="D377" s="2" t="inlineStr">
         <is>
-          <t>Balabite</t>
+          <t>Bubble Shack</t>
         </is>
       </c>
       <c r="E377" s="2" t="inlineStr">
@@ -27402,20 +27402,20 @@
       </c>
       <c r="G377" s="2" t="inlineStr">
         <is>
-          <t>Instagram</t>
-        </is>
-      </c>
-      <c r="H377" s="4" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/balabite</t>
-        </is>
-      </c>
+          <t>Facebook</t>
+        </is>
+      </c>
+      <c r="H377" s="2" t="inlineStr"/>
       <c r="I377" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/balabite/</t>
-        </is>
-      </c>
-      <c r="J377" s="2" t="inlineStr"/>
+          <t>https://www.facebook.com/thebubbleshackbubbletea</t>
+        </is>
+      </c>
+      <c r="J377" s="2" t="inlineStr">
+        <is>
+          <t>+61 7 4772 0103</t>
+        </is>
+      </c>
       <c r="K377" s="2" t="inlineStr"/>
       <c r="L377" s="2" t="inlineStr">
         <is>
@@ -27424,7 +27424,7 @@
       </c>
       <c r="M377" s="2" t="inlineStr">
         <is>
-          <t>Hi Balabite team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Balabite, only your Instagram. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
+          <t>Hi Bubble Shack team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Bubble Shack, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
         </is>
       </c>
       <c r="N377" s="4" t="inlineStr">
@@ -27458,12 +27458,12 @@
       </c>
       <c r="D378" s="2" t="inlineStr">
         <is>
-          <t>Bubble Shack</t>
+          <t>Sunvale Meats</t>
         </is>
       </c>
       <c r="E378" s="2" t="inlineStr">
         <is>
-          <t>cafe</t>
+          <t>deli or specialty food</t>
         </is>
       </c>
       <c r="F378" s="2" t="inlineStr">
@@ -27479,12 +27479,12 @@
       <c r="H378" s="2" t="inlineStr"/>
       <c r="I378" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/thebubbleshackbubbletea</t>
+          <t>https://m.facebook.com/people/Sunvale-Meats/100063491471034/</t>
         </is>
       </c>
       <c r="J378" s="2" t="inlineStr">
         <is>
-          <t>+61 7 4772 0103</t>
+          <t>+61 7 4775 3750</t>
         </is>
       </c>
       <c r="K378" s="2" t="inlineStr"/>
@@ -27495,7 +27495,7 @@
       </c>
       <c r="M378" s="2" t="inlineStr">
         <is>
-          <t>Hi Bubble Shack team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Bubble Shack, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
+          <t>Hi Sunvale Meats team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Sunvale Meats, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
         </is>
       </c>
       <c r="N378" s="4" t="inlineStr">
@@ -27529,12 +27529,12 @@
       </c>
       <c r="D379" s="2" t="inlineStr">
         <is>
-          <t>Sunvale Meats</t>
+          <t>Aussie Thai Fusion</t>
         </is>
       </c>
       <c r="E379" s="2" t="inlineStr">
         <is>
-          <t>deli or specialty food</t>
+          <t>restaurant</t>
         </is>
       </c>
       <c r="F379" s="2" t="inlineStr">
@@ -27550,12 +27550,12 @@
       <c r="H379" s="2" t="inlineStr"/>
       <c r="I379" s="4" t="inlineStr">
         <is>
-          <t>https://m.facebook.com/people/Sunvale-Meats/100063491471034/</t>
+          <t>https://www.facebook.com/Aussie-Thai-Fusion-413149449023841</t>
         </is>
       </c>
       <c r="J379" s="2" t="inlineStr">
         <is>
-          <t>+61 7 4775 3750</t>
+          <t>+61 7 4721 2524</t>
         </is>
       </c>
       <c r="K379" s="2" t="inlineStr"/>
@@ -27566,7 +27566,7 @@
       </c>
       <c r="M379" s="2" t="inlineStr">
         <is>
-          <t>Hi Sunvale Meats team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Sunvale Meats, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
+          <t>Hi Aussie Thai Fusion team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Aussie Thai Fusion, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
         </is>
       </c>
       <c r="N379" s="4" t="inlineStr">
@@ -27600,7 +27600,7 @@
       </c>
       <c r="D380" s="2" t="inlineStr">
         <is>
-          <t>Aussie Thai Fusion</t>
+          <t>Bountiful Thai</t>
         </is>
       </c>
       <c r="E380" s="2" t="inlineStr">
@@ -27621,12 +27621,12 @@
       <c r="H380" s="2" t="inlineStr"/>
       <c r="I380" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/Aussie-Thai-Fusion-413149449023841</t>
+          <t>https://www.facebook.com/bountifulthai</t>
         </is>
       </c>
       <c r="J380" s="2" t="inlineStr">
         <is>
-          <t>+61 7 4721 2524</t>
+          <t>+61 7 4771 5578</t>
         </is>
       </c>
       <c r="K380" s="2" t="inlineStr"/>
@@ -27637,7 +27637,7 @@
       </c>
       <c r="M380" s="2" t="inlineStr">
         <is>
-          <t>Hi Aussie Thai Fusion team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Aussie Thai Fusion, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
+          <t>Hi Bountiful Thai team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Bountiful Thai, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
         </is>
       </c>
       <c r="N380" s="4" t="inlineStr">
@@ -27671,7 +27671,7 @@
       </c>
       <c r="D381" s="2" t="inlineStr">
         <is>
-          <t>Bountiful Thai</t>
+          <t>Chico Rio</t>
         </is>
       </c>
       <c r="E381" s="2" t="inlineStr">
@@ -27692,12 +27692,12 @@
       <c r="H381" s="2" t="inlineStr"/>
       <c r="I381" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/bountifulthai</t>
+          <t>https://www.facebook.com/chicoriotsv</t>
         </is>
       </c>
       <c r="J381" s="2" t="inlineStr">
         <is>
-          <t>+61 7 4771 5578</t>
+          <t>+61 7 4772 1073</t>
         </is>
       </c>
       <c r="K381" s="2" t="inlineStr"/>
@@ -27708,7 +27708,7 @@
       </c>
       <c r="M381" s="2" t="inlineStr">
         <is>
-          <t>Hi Bountiful Thai team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Bountiful Thai, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
+          <t>Hi Chico Rio team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Chico Rio, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
         </is>
       </c>
       <c r="N381" s="4" t="inlineStr">
@@ -27742,7 +27742,7 @@
       </c>
       <c r="D382" s="2" t="inlineStr">
         <is>
-          <t>Chico Rio</t>
+          <t>Wild Rice</t>
         </is>
       </c>
       <c r="E382" s="2" t="inlineStr">
@@ -27763,12 +27763,12 @@
       <c r="H382" s="2" t="inlineStr"/>
       <c r="I382" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/chicoriotsv</t>
+          <t>https://www.facebook.com/WildRiceLaoThai</t>
         </is>
       </c>
       <c r="J382" s="2" t="inlineStr">
         <is>
-          <t>+61 7 4772 1073</t>
+          <t>+61 7 4771 6242</t>
         </is>
       </c>
       <c r="K382" s="2" t="inlineStr"/>
@@ -27779,7 +27779,7 @@
       </c>
       <c r="M382" s="2" t="inlineStr">
         <is>
-          <t>Hi Chico Rio team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Chico Rio, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
+          <t>Hi Wild Rice team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Wild Rice, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
         </is>
       </c>
       <c r="N382" s="4" t="inlineStr">
@@ -27813,12 +27813,12 @@
       </c>
       <c r="D383" s="2" t="inlineStr">
         <is>
-          <t>Wild Rice</t>
+          <t>Fish N Chip Delights</t>
         </is>
       </c>
       <c r="E383" s="2" t="inlineStr">
         <is>
-          <t>restaurant</t>
+          <t>takeaway</t>
         </is>
       </c>
       <c r="F383" s="2" t="inlineStr">
@@ -27834,12 +27834,12 @@
       <c r="H383" s="2" t="inlineStr"/>
       <c r="I383" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/WildRiceLaoThai</t>
+          <t>https://facebook.com/FISHnCHIPDelights</t>
         </is>
       </c>
       <c r="J383" s="2" t="inlineStr">
         <is>
-          <t>+61 7 4771 6242</t>
+          <t>+61 7 4740 4949</t>
         </is>
       </c>
       <c r="K383" s="2" t="inlineStr"/>
@@ -27850,7 +27850,7 @@
       </c>
       <c r="M383" s="2" t="inlineStr">
         <is>
-          <t>Hi Wild Rice team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Wild Rice, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
+          <t>Hi Fish N Chip Delights team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Fish N Chip Delights, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
         </is>
       </c>
       <c r="N383" s="4" t="inlineStr">
@@ -27879,12 +27879,12 @@
       </c>
       <c r="C384" s="2" t="inlineStr">
         <is>
-          <t>No website found</t>
+          <t>Site shows an error</t>
         </is>
       </c>
       <c r="D384" s="2" t="inlineStr">
         <is>
-          <t>Fish N Chip Delights</t>
+          <t>Squeeze Me</t>
         </is>
       </c>
       <c r="E384" s="2" t="inlineStr">
@@ -27905,23 +27905,27 @@
       <c r="H384" s="2" t="inlineStr"/>
       <c r="I384" s="4" t="inlineStr">
         <is>
-          <t>https://facebook.com/FISHnCHIPDelights</t>
+          <t>https://www.facebook.com/Squeezemetownsville</t>
         </is>
       </c>
       <c r="J384" s="2" t="inlineStr">
         <is>
-          <t>+61 7 4740 4949</t>
-        </is>
-      </c>
-      <c r="K384" s="2" t="inlineStr"/>
+          <t>+61 7 4721 0322</t>
+        </is>
+      </c>
+      <c r="K384" s="4" t="inlineStr">
+        <is>
+          <t>https://www.squeezeme.com.au/</t>
+        </is>
+      </c>
       <c r="L384" s="2" t="inlineStr">
         <is>
-          <t>no website listed, only social media (verify on Google Maps)</t>
+          <t>homepage shows an error page (HTTP 404)</t>
         </is>
       </c>
       <c r="M384" s="2" t="inlineStr">
         <is>
-          <t>Hi Fish N Chip Delights team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Fish N Chip Delights, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
+          <t>Hi Squeeze Me team! [one real detail from their page]. We're AceAds, a web design studio. We noticed your website was showing an error page when we tried it. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
         </is>
       </c>
       <c r="N384" s="4" t="inlineStr">
@@ -27950,17 +27954,17 @@
       </c>
       <c r="C385" s="2" t="inlineStr">
         <is>
-          <t>Site shows an error</t>
+          <t>No website found</t>
         </is>
       </c>
       <c r="D385" s="2" t="inlineStr">
         <is>
-          <t>Squeeze Me</t>
+          <t>Dark Arts Tattoo</t>
         </is>
       </c>
       <c r="E385" s="2" t="inlineStr">
         <is>
-          <t>takeaway</t>
+          <t>tattoo studio</t>
         </is>
       </c>
       <c r="F385" s="2" t="inlineStr">
@@ -27976,27 +27980,19 @@
       <c r="H385" s="2" t="inlineStr"/>
       <c r="I385" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/Squeezemetownsville</t>
-        </is>
-      </c>
-      <c r="J385" s="2" t="inlineStr">
-        <is>
-          <t>+61 7 4721 0322</t>
-        </is>
-      </c>
-      <c r="K385" s="4" t="inlineStr">
-        <is>
-          <t>https://www.squeezeme.com.au/</t>
-        </is>
-      </c>
+          <t>https://www.facebook.com/DarkArtsTattooTsv/</t>
+        </is>
+      </c>
+      <c r="J385" s="2" t="inlineStr"/>
+      <c r="K385" s="2" t="inlineStr"/>
       <c r="L385" s="2" t="inlineStr">
         <is>
-          <t>homepage shows an error page (HTTP 404)</t>
+          <t>no website listed, only social media (verify on Google Maps)</t>
         </is>
       </c>
       <c r="M385" s="2" t="inlineStr">
         <is>
-          <t>Hi Squeeze Me team! [one real detail from their page]. We're AceAds, a web design studio. We noticed your website was showing an error page when we tried it. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
+          <t>Hi Dark Arts Tattoo team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Dark Arts Tattoo, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
         </is>
       </c>
       <c r="N385" s="4" t="inlineStr">
@@ -28018,29 +28014,29 @@
       <c r="A386" s="2" t="n">
         <v>385</v>
       </c>
-      <c r="B386" s="5" t="inlineStr">
-        <is>
-          <t>VERIFY FIRST</t>
+      <c r="B386" s="6" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="C386" s="2" t="inlineStr">
         <is>
-          <t>No website found</t>
+          <t>Weak website</t>
         </is>
       </c>
       <c r="D386" s="2" t="inlineStr">
         <is>
-          <t>Dark Arts Tattoo</t>
+          <t>Proactive Coaching</t>
         </is>
       </c>
       <c r="E386" s="2" t="inlineStr">
         <is>
-          <t>tattoo studio</t>
+          <t>allied health</t>
         </is>
       </c>
       <c r="F386" s="2" t="inlineStr">
         <is>
-          <t>Townsville</t>
+          <t>Brisbane</t>
         </is>
       </c>
       <c r="G386" s="2" t="inlineStr">
@@ -28051,19 +28047,27 @@
       <c r="H386" s="2" t="inlineStr"/>
       <c r="I386" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/DarkArtsTattooTsv/</t>
-        </is>
-      </c>
-      <c r="J386" s="2" t="inlineStr"/>
-      <c r="K386" s="2" t="inlineStr"/>
+          <t>https://www.facebook.com/lindsay.trims</t>
+        </is>
+      </c>
+      <c r="J386" s="2" t="inlineStr">
+        <is>
+          <t>+61 411 036 297</t>
+        </is>
+      </c>
+      <c r="K386" s="4" t="inlineStr">
+        <is>
+          <t>http://proactivecoaching.net/</t>
+        </is>
+      </c>
       <c r="L386" s="2" t="inlineStr">
         <is>
-          <t>no website listed, only social media (verify on Google Maps)</t>
+          <t>no HTTPS (browser shows 'Not secure'); not mobile-friendly (no viewport tag)</t>
         </is>
       </c>
       <c r="M386" s="2" t="inlineStr">
         <is>
-          <t>Hi Dark Arts Tattoo team! [one real detail from their page]. We're AceAds, a web design studio. We couldn't find a website for Dark Arts Tattoo, only your Facebook. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
+          <t>Hi Proactive Coaching team! [one real detail from their page]. We're AceAds, a web design studio. We noticed your website is hard to use on a phone. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
         </is>
       </c>
       <c r="N386" s="4" t="inlineStr">
@@ -28097,12 +28101,12 @@
       </c>
       <c r="D387" s="2" t="inlineStr">
         <is>
-          <t>Proactive Coaching</t>
+          <t>Contrasts Hair Studio</t>
         </is>
       </c>
       <c r="E387" s="2" t="inlineStr">
         <is>
-          <t>allied health</t>
+          <t>barber or hairdresser</t>
         </is>
       </c>
       <c r="F387" s="2" t="inlineStr">
@@ -28118,27 +28122,27 @@
       <c r="H387" s="2" t="inlineStr"/>
       <c r="I387" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/lindsay.trims</t>
+          <t>https://www.facebook.com/Contrastshairstudio</t>
         </is>
       </c>
       <c r="J387" s="2" t="inlineStr">
         <is>
-          <t>+61 411 036 297</t>
+          <t>+61 7 3356 4433</t>
         </is>
       </c>
       <c r="K387" s="4" t="inlineStr">
         <is>
-          <t>http://proactivecoaching.net/</t>
+          <t>https://contrasts.com.au/</t>
         </is>
       </c>
       <c r="L387" s="2" t="inlineStr">
         <is>
-          <t>no HTTPS (browser shows 'Not secure'); not mobile-friendly (no viewport tag)</t>
+          <t>not mobile-friendly (no viewport tag); missing meta description</t>
         </is>
       </c>
       <c r="M387" s="2" t="inlineStr">
         <is>
-          <t>Hi Proactive Coaching team! [one real detail from their page]. We're AceAds, a web design studio. We noticed your website is hard to use on a phone. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
+          <t>Hi Contrasts Hair Studio team! [one real detail from their page]. We're AceAds, a web design studio. We noticed your website is hard to use on a phone. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
         </is>
       </c>
       <c r="N387" s="4" t="inlineStr">
@@ -28172,12 +28176,12 @@
       </c>
       <c r="D388" s="2" t="inlineStr">
         <is>
-          <t>Contrasts Hair Studio</t>
+          <t>Embroidery Queen</t>
         </is>
       </c>
       <c r="E388" s="2" t="inlineStr">
         <is>
-          <t>barber or hairdresser</t>
+          <t>boutique</t>
         </is>
       </c>
       <c r="F388" s="2" t="inlineStr">
@@ -28187,33 +28191,37 @@
       </c>
       <c r="G388" s="2" t="inlineStr">
         <is>
-          <t>Facebook</t>
-        </is>
-      </c>
-      <c r="H388" s="2" t="inlineStr"/>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="H388" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/embroideryqueenau</t>
+        </is>
+      </c>
       <c r="I388" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/Contrastshairstudio</t>
+          <t>https://www.facebook.com/EmbroideryQueens</t>
         </is>
       </c>
       <c r="J388" s="2" t="inlineStr">
         <is>
-          <t>+61 7 3356 4433</t>
+          <t>+61 422 597 294</t>
         </is>
       </c>
       <c r="K388" s="4" t="inlineStr">
         <is>
-          <t>https://contrasts.com.au/</t>
+          <t>http://www.embroideryqueen.com.au/</t>
         </is>
       </c>
       <c r="L388" s="2" t="inlineStr">
         <is>
-          <t>not mobile-friendly (no viewport tag); missing meta description</t>
+          <t>no HTTPS (browser shows 'Not secure'); not mobile-friendly (no viewport tag)</t>
         </is>
       </c>
       <c r="M388" s="2" t="inlineStr">
         <is>
-          <t>Hi Contrasts Hair Studio team! [one real detail from their page]. We're AceAds, a web design studio. We noticed your website is hard to use on a phone. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
+          <t>Hi Embroidery Queen team! [one real detail from their page]. We're AceAds, a web design studio. We noticed your website is hard to use on a phone. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
         </is>
       </c>
       <c r="N388" s="4" t="inlineStr">
@@ -28247,12 +28255,12 @@
       </c>
       <c r="D389" s="2" t="inlineStr">
         <is>
-          <t>Embroidery Queen</t>
+          <t>Forages</t>
         </is>
       </c>
       <c r="E389" s="2" t="inlineStr">
         <is>
-          <t>boutique</t>
+          <t>cafe</t>
         </is>
       </c>
       <c r="F389" s="2" t="inlineStr">
@@ -28262,37 +28270,29 @@
       </c>
       <c r="G389" s="2" t="inlineStr">
         <is>
-          <t>Instagram</t>
-        </is>
-      </c>
-      <c r="H389" s="4" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/embroideryqueenau</t>
-        </is>
-      </c>
+          <t>Facebook</t>
+        </is>
+      </c>
+      <c r="H389" s="2" t="inlineStr"/>
       <c r="I389" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/EmbroideryQueens</t>
-        </is>
-      </c>
-      <c r="J389" s="2" t="inlineStr">
-        <is>
-          <t>+61 422 597 294</t>
-        </is>
-      </c>
+          <t>https://www.facebook.com/foragesdelicafe</t>
+        </is>
+      </c>
+      <c r="J389" s="2" t="inlineStr"/>
       <c r="K389" s="4" t="inlineStr">
         <is>
-          <t>http://www.embroideryqueen.com.au/</t>
+          <t>https://www.foragesdelicafe.com.au/</t>
         </is>
       </c>
       <c r="L389" s="2" t="inlineStr">
         <is>
-          <t>no HTTPS (browser shows 'Not secure'); not mobile-friendly (no viewport tag)</t>
+          <t>looks outdated (copyright 2018); missing meta description; slow to load (4.1s)</t>
         </is>
       </c>
       <c r="M389" s="2" t="inlineStr">
         <is>
-          <t>Hi Embroidery Queen team! [one real detail from their page]. We're AceAds, a web design studio. We noticed your website is hard to use on a phone. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
+          <t>Hi Forages team! [one real detail from their page]. We're AceAds, a web design studio. We noticed your website takes a while to load on a phone, which is where most people will first see it. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
         </is>
       </c>
       <c r="N389" s="4" t="inlineStr">
@@ -28326,7 +28326,7 @@
       </c>
       <c r="D390" s="2" t="inlineStr">
         <is>
-          <t>Forages</t>
+          <t>Mia Bella's Coffee Drive Thru</t>
         </is>
       </c>
       <c r="E390" s="2" t="inlineStr">
@@ -28347,23 +28347,23 @@
       <c r="H390" s="2" t="inlineStr"/>
       <c r="I390" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/foragesdelicafe</t>
+          <t>https://www.facebook.com/miabellascoffee</t>
         </is>
       </c>
       <c r="J390" s="2" t="inlineStr"/>
       <c r="K390" s="4" t="inlineStr">
         <is>
-          <t>https://www.foragesdelicafe.com.au/</t>
+          <t>http://miabellascoffee.com/</t>
         </is>
       </c>
       <c r="L390" s="2" t="inlineStr">
         <is>
-          <t>looks outdated (copyright 2018); missing meta description; slow to load (4.1s)</t>
+          <t>no HTTPS (browser shows 'Not secure'); looks outdated (copyright 2015); missing meta description</t>
         </is>
       </c>
       <c r="M390" s="2" t="inlineStr">
         <is>
-          <t>Hi Forages team! [one real detail from their page]. We're AceAds, a web design studio. We think your website could be doing more to bring in customers. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
+          <t>Hi Mia Bella's Coffee Drive Thru team! [one real detail from their page]. We're AceAds, a web design studio. We think your website could be doing more to bring in customers. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
         </is>
       </c>
       <c r="N390" s="4" t="inlineStr">
@@ -28397,12 +28397,12 @@
       </c>
       <c r="D391" s="2" t="inlineStr">
         <is>
-          <t>Mia Bella's Coffee Drive Thru</t>
+          <t>Alderley Kindergarten</t>
         </is>
       </c>
       <c r="E391" s="2" t="inlineStr">
         <is>
-          <t>cafe</t>
+          <t>childcare</t>
         </is>
       </c>
       <c r="F391" s="2" t="inlineStr">
@@ -28418,23 +28418,23 @@
       <c r="H391" s="2" t="inlineStr"/>
       <c r="I391" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/miabellascoffee</t>
+          <t>https://www.facebook.com/AlderleyKindy</t>
         </is>
       </c>
       <c r="J391" s="2" t="inlineStr"/>
       <c r="K391" s="4" t="inlineStr">
         <is>
-          <t>http://miabellascoffee.com/</t>
+          <t>https://alderleykindy.com.au</t>
         </is>
       </c>
       <c r="L391" s="2" t="inlineStr">
         <is>
-          <t>no HTTPS (browser shows 'Not secure'); looks outdated (copyright 2015); missing meta description</t>
+          <t>looks outdated (copyright 2020); missing meta description; slow to load (3.3s)</t>
         </is>
       </c>
       <c r="M391" s="2" t="inlineStr">
         <is>
-          <t>Hi Mia Bella's Coffee Drive Thru team! [one real detail from their page]. We're AceAds, a web design studio. We think your website could be doing more to bring in customers. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
+          <t>Hi Alderley Kindergarten team! [one real detail from their page]. We're AceAds, a web design studio. We noticed your website takes a while to load on a phone, which is where most people will first see it. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
         </is>
       </c>
       <c r="N391" s="4" t="inlineStr">
@@ -28468,7 +28468,7 @@
       </c>
       <c r="D392" s="2" t="inlineStr">
         <is>
-          <t>Alderley Kindergarten</t>
+          <t>Little Bouncing Bears Early Learning Centre</t>
         </is>
       </c>
       <c r="E392" s="2" t="inlineStr">
@@ -28489,23 +28489,23 @@
       <c r="H392" s="2" t="inlineStr"/>
       <c r="I392" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/AlderleyKindy</t>
+          <t>https://www.facebook.com/littlebouncingbears</t>
         </is>
       </c>
       <c r="J392" s="2" t="inlineStr"/>
       <c r="K392" s="4" t="inlineStr">
         <is>
-          <t>https://alderleykindy.com.au</t>
+          <t>https://littlebouncingbears.com.au/</t>
         </is>
       </c>
       <c r="L392" s="2" t="inlineStr">
         <is>
-          <t>looks outdated (copyright 2020); missing meta description; slow to load (3.3s)</t>
+          <t>looks outdated (copyright 2023); missing meta description; slow to load (3.1s)</t>
         </is>
       </c>
       <c r="M392" s="2" t="inlineStr">
         <is>
-          <t>Hi Alderley Kindergarten team! [one real detail from their page]. We're AceAds, a web design studio. We think your website could be doing more to bring in customers. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
+          <t>Hi Little Bouncing Bears Early Learning Centre team! [one real detail from their page]. We're AceAds, a web design studio. We noticed your website takes a while to load on a phone, which is where most people will first see it. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
         </is>
       </c>
       <c r="N392" s="4" t="inlineStr">
@@ -28539,7 +28539,7 @@
       </c>
       <c r="D393" s="2" t="inlineStr">
         <is>
-          <t>Little Bouncing Bears Early Learning Centre</t>
+          <t>Little School Loganholme</t>
         </is>
       </c>
       <c r="E393" s="2" t="inlineStr">
@@ -28554,29 +28554,33 @@
       </c>
       <c r="G393" s="2" t="inlineStr">
         <is>
-          <t>Facebook</t>
-        </is>
-      </c>
-      <c r="H393" s="2" t="inlineStr"/>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="H393" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/littleschoolhighlandpark</t>
+        </is>
+      </c>
       <c r="I393" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/littlebouncingbears</t>
+          <t>https://www.facebook.com/littleschoolhighlandpark</t>
         </is>
       </c>
       <c r="J393" s="2" t="inlineStr"/>
       <c r="K393" s="4" t="inlineStr">
         <is>
-          <t>https://littlebouncingbears.com.au/</t>
+          <t>https://littleschoolelc.com.au/loganholme/</t>
         </is>
       </c>
       <c r="L393" s="2" t="inlineStr">
         <is>
-          <t>looks outdated (copyright 2023); missing meta description; slow to load (3.1s)</t>
+          <t>looks outdated (copyright 2015); missing meta description; slow to load (3.2s)</t>
         </is>
       </c>
       <c r="M393" s="2" t="inlineStr">
         <is>
-          <t>Hi Little Bouncing Bears Early Learning Centre team! [one real detail from their page]. We're AceAds, a web design studio. We think your website could be doing more to bring in customers. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
+          <t>Hi Little School Loganholme team! [one real detail from their page]. We're AceAds, a web design studio. We noticed your website takes a while to load on a phone, which is where most people will first see it. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
         </is>
       </c>
       <c r="N393" s="4" t="inlineStr">
@@ -28610,12 +28614,12 @@
       </c>
       <c r="D394" s="2" t="inlineStr">
         <is>
-          <t>Little School Loganholme</t>
+          <t>Fit N Fab Fitness</t>
         </is>
       </c>
       <c r="E394" s="2" t="inlineStr">
         <is>
-          <t>childcare</t>
+          <t>gym or studio</t>
         </is>
       </c>
       <c r="F394" s="2" t="inlineStr">
@@ -28630,28 +28634,28 @@
       </c>
       <c r="H394" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/littleschoolhighlandpark</t>
+          <t>https://www.instagram.com/fitnfabfitness</t>
         </is>
       </c>
       <c r="I394" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/littleschoolhighlandpark</t>
+          <t>https://www.facebook.com/fitty.fabbo.7</t>
         </is>
       </c>
       <c r="J394" s="2" t="inlineStr"/>
       <c r="K394" s="4" t="inlineStr">
         <is>
-          <t>https://littleschoolelc.com.au/loganholme/</t>
+          <t>https://www.fitnfab.com.au/</t>
         </is>
       </c>
       <c r="L394" s="2" t="inlineStr">
         <is>
-          <t>looks outdated (copyright 2015); missing meta description; slow to load (3.2s)</t>
+          <t>looks outdated (copyright 2021); missing meta description; slow to load (5.9s)</t>
         </is>
       </c>
       <c r="M394" s="2" t="inlineStr">
         <is>
-          <t>Hi Little School Loganholme team! [one real detail from their page]. We're AceAds, a web design studio. We think your website could be doing more to bring in customers. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
+          <t>Hi Fit N Fab Fitness team! [one real detail from their page]. We're AceAds, a web design studio. We noticed your website takes a while to load on a phone, which is where most people will first see it. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
         </is>
       </c>
       <c r="N394" s="4" t="inlineStr">
@@ -28685,12 +28689,12 @@
       </c>
       <c r="D395" s="2" t="inlineStr">
         <is>
-          <t>Fit N Fab Fitness</t>
+          <t>Parkinson Veterinary Surgery</t>
         </is>
       </c>
       <c r="E395" s="2" t="inlineStr">
         <is>
-          <t>gym or studio</t>
+          <t>pet business</t>
         </is>
       </c>
       <c r="F395" s="2" t="inlineStr">
@@ -28705,28 +28709,28 @@
       </c>
       <c r="H395" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/fitnfabfitness</t>
+          <t>https://www.instagram.com/parkinsonvetsurgery</t>
         </is>
       </c>
       <c r="I395" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/fitty.fabbo.7</t>
+          <t>https://www.facebook.com/parkinsonvetclinic</t>
         </is>
       </c>
       <c r="J395" s="2" t="inlineStr"/>
       <c r="K395" s="4" t="inlineStr">
         <is>
-          <t>https://www.fitnfab.com.au/</t>
+          <t>https://parkinsonvet.com.au/</t>
         </is>
       </c>
       <c r="L395" s="2" t="inlineStr">
         <is>
-          <t>looks outdated (copyright 2021); missing meta description; slow to load (5.9s)</t>
+          <t>looks outdated (copyright 2020); missing meta description; slow to load (3.2s)</t>
         </is>
       </c>
       <c r="M395" s="2" t="inlineStr">
         <is>
-          <t>Hi Fit N Fab Fitness team! [one real detail from their page]. We're AceAds, a web design studio. We think your website could be doing more to bring in customers. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
+          <t>Hi Parkinson Veterinary Surgery team! [one real detail from their page]. We're AceAds, a web design studio. We noticed your website takes a while to load on a phone, which is where most people will first see it. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
         </is>
       </c>
       <c r="N395" s="4" t="inlineStr">
@@ -28760,12 +28764,12 @@
       </c>
       <c r="D396" s="2" t="inlineStr">
         <is>
-          <t>Parkinson Veterinary Surgery</t>
+          <t>Burrito Bar</t>
         </is>
       </c>
       <c r="E396" s="2" t="inlineStr">
         <is>
-          <t>pet business</t>
+          <t>restaurant</t>
         </is>
       </c>
       <c r="F396" s="2" t="inlineStr">
@@ -28780,28 +28784,28 @@
       </c>
       <c r="H396" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/parkinsonvetsurgery</t>
+          <t>https://instagram.com/burritobar_</t>
         </is>
       </c>
       <c r="I396" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/parkinsonvetclinic</t>
+          <t>https://www.facebook.com/TheBurritoBar</t>
         </is>
       </c>
       <c r="J396" s="2" t="inlineStr"/>
       <c r="K396" s="4" t="inlineStr">
         <is>
-          <t>https://parkinsonvet.com.au/</t>
+          <t>http://theburritobar.com.au</t>
         </is>
       </c>
       <c r="L396" s="2" t="inlineStr">
         <is>
-          <t>looks outdated (copyright 2020); missing meta description; slow to load (3.2s)</t>
+          <t>no HTTPS (browser shows 'Not secure'); looks outdated (copyright 2023)</t>
         </is>
       </c>
       <c r="M396" s="2" t="inlineStr">
         <is>
-          <t>Hi Parkinson Veterinary Surgery team! [one real detail from their page]. We're AceAds, a web design studio. We think your website could be doing more to bring in customers. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
+          <t>Hi Burrito Bar team! [one real detail from their page]. We're AceAds, a web design studio. We think your website could be doing more to bring in customers. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
         </is>
       </c>
       <c r="N396" s="4" t="inlineStr">
@@ -28835,7 +28839,7 @@
       </c>
       <c r="D397" s="2" t="inlineStr">
         <is>
-          <t>Burrito Bar</t>
+          <t>Lilong West End</t>
         </is>
       </c>
       <c r="E397" s="2" t="inlineStr">
@@ -28855,28 +28859,32 @@
       </c>
       <c r="H397" s="4" t="inlineStr">
         <is>
-          <t>https://instagram.com/burritobar_</t>
+          <t>https://www.instagram.com/tasteofshanghai</t>
         </is>
       </c>
       <c r="I397" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/TheBurritoBar</t>
-        </is>
-      </c>
-      <c r="J397" s="2" t="inlineStr"/>
+          <t>https://www.facebook.com/tasteofshanghaiaus</t>
+        </is>
+      </c>
+      <c r="J397" s="2" t="inlineStr">
+        <is>
+          <t>+61 478 235 886</t>
+        </is>
+      </c>
       <c r="K397" s="4" t="inlineStr">
         <is>
-          <t>http://theburritobar.com.au</t>
+          <t>https://tasteofshanghai.com.au/lilong-2/</t>
         </is>
       </c>
       <c r="L397" s="2" t="inlineStr">
         <is>
-          <t>no HTTPS (browser shows 'Not secure'); looks outdated (copyright 2023)</t>
+          <t>looks outdated (copyright 2022); missing meta description; slow to load (3.8s)</t>
         </is>
       </c>
       <c r="M397" s="2" t="inlineStr">
         <is>
-          <t>Hi Burrito Bar team! [one real detail from their page]. We're AceAds, a web design studio. We think your website could be doing more to bring in customers. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
+          <t>Hi Lilong West End team! [one real detail from their page]. We're AceAds, a web design studio. We noticed your website takes a while to load on a phone, which is where most people will first see it. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
         </is>
       </c>
       <c r="N397" s="4" t="inlineStr">
@@ -28910,7 +28918,7 @@
       </c>
       <c r="D398" s="2" t="inlineStr">
         <is>
-          <t>Lilong West End</t>
+          <t>Maru</t>
         </is>
       </c>
       <c r="E398" s="2" t="inlineStr">
@@ -28925,37 +28933,29 @@
       </c>
       <c r="G398" s="2" t="inlineStr">
         <is>
-          <t>Instagram</t>
-        </is>
-      </c>
-      <c r="H398" s="4" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/tasteofshanghai</t>
-        </is>
-      </c>
+          <t>Facebook</t>
+        </is>
+      </c>
+      <c r="H398" s="2" t="inlineStr"/>
       <c r="I398" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/tasteofshanghaiaus</t>
-        </is>
-      </c>
-      <c r="J398" s="2" t="inlineStr">
-        <is>
-          <t>+61 478 235 886</t>
-        </is>
-      </c>
+          <t>http://www.facebook.com/pages/Maru-Korean-Restaurant/170697606348616</t>
+        </is>
+      </c>
+      <c r="J398" s="2" t="inlineStr"/>
       <c r="K398" s="4" t="inlineStr">
         <is>
-          <t>https://tasteofshanghai.com.au/lilong-2/</t>
+          <t>https://marukoreanbbq.weebly.com/</t>
         </is>
       </c>
       <c r="L398" s="2" t="inlineStr">
         <is>
-          <t>looks outdated (copyright 2022); missing meta description; slow to load (3.8s)</t>
+          <t>not mobile-friendly (no viewport tag); missing meta description</t>
         </is>
       </c>
       <c r="M398" s="2" t="inlineStr">
         <is>
-          <t>Hi Lilong West End team! [one real detail from their page]. We're AceAds, a web design studio. We think your website could be doing more to bring in customers. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
+          <t>Hi Maru team! [one real detail from their page]. We're AceAds, a web design studio. We noticed your website is hard to use on a phone. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
         </is>
       </c>
       <c r="N398" s="4" t="inlineStr">
@@ -28989,12 +28989,12 @@
       </c>
       <c r="D399" s="2" t="inlineStr">
         <is>
-          <t>Maru</t>
+          <t>Boba Chicken</t>
         </is>
       </c>
       <c r="E399" s="2" t="inlineStr">
         <is>
-          <t>restaurant</t>
+          <t>takeaway</t>
         </is>
       </c>
       <c r="F399" s="2" t="inlineStr">
@@ -29010,13 +29010,13 @@
       <c r="H399" s="2" t="inlineStr"/>
       <c r="I399" s="4" t="inlineStr">
         <is>
-          <t>http://www.facebook.com/pages/Maru-Korean-Restaurant/170697606348616</t>
+          <t>https://www.facebook.com/login</t>
         </is>
       </c>
       <c r="J399" s="2" t="inlineStr"/>
       <c r="K399" s="4" t="inlineStr">
         <is>
-          <t>https://marukoreanbbq.weebly.com/</t>
+          <t>www.bobachicken.com</t>
         </is>
       </c>
       <c r="L399" s="2" t="inlineStr">
@@ -29026,7 +29026,7 @@
       </c>
       <c r="M399" s="2" t="inlineStr">
         <is>
-          <t>Hi Maru team! [one real detail from their page]. We're AceAds, a web design studio. We noticed your website is hard to use on a phone. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
+          <t>Hi Boba Chicken team! [one real detail from their page]. We're AceAds, a web design studio. We noticed your website is hard to use on a phone. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
         </is>
       </c>
       <c r="N399" s="4" t="inlineStr">
@@ -29060,44 +29060,52 @@
       </c>
       <c r="D400" s="2" t="inlineStr">
         <is>
-          <t>Boba Chicken</t>
+          <t>Mama Coco</t>
         </is>
       </c>
       <c r="E400" s="2" t="inlineStr">
         <is>
-          <t>takeaway</t>
+          <t>cafe</t>
         </is>
       </c>
       <c r="F400" s="2" t="inlineStr">
         <is>
-          <t>Brisbane</t>
+          <t>Cairns</t>
         </is>
       </c>
       <c r="G400" s="2" t="inlineStr">
         <is>
-          <t>Facebook</t>
-        </is>
-      </c>
-      <c r="H400" s="2" t="inlineStr"/>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="H400" s="4" t="inlineStr">
+        <is>
+          <t>http://instagram.com/mama_coco</t>
+        </is>
+      </c>
       <c r="I400" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/login</t>
-        </is>
-      </c>
-      <c r="J400" s="2" t="inlineStr"/>
+          <t>https://www.facebook.com/mamacococafe</t>
+        </is>
+      </c>
+      <c r="J400" s="2" t="inlineStr">
+        <is>
+          <t>+61 7 4052 1226</t>
+        </is>
+      </c>
       <c r="K400" s="4" t="inlineStr">
         <is>
-          <t>www.bobachicken.com</t>
+          <t>http://www.mamacoco.com.au</t>
         </is>
       </c>
       <c r="L400" s="2" t="inlineStr">
         <is>
-          <t>not mobile-friendly (no viewport tag); missing meta description</t>
+          <t>no HTTPS (browser shows 'Not secure'); missing meta description; slow to load (4.2s)</t>
         </is>
       </c>
       <c r="M400" s="2" t="inlineStr">
         <is>
-          <t>Hi Boba Chicken team! [one real detail from their page]. We're AceAds, a web design studio. We noticed your website is hard to use on a phone. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
+          <t>Hi Mama Coco team! [one real detail from their page]. We're AceAds, a web design studio. We noticed your website takes a while to load on a phone, which is where most people will first see it. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
         </is>
       </c>
       <c r="N400" s="4" t="inlineStr">
@@ -29131,17 +29139,17 @@
       </c>
       <c r="D401" s="2" t="inlineStr">
         <is>
-          <t>Mama Coco</t>
+          <t>Sugar Me Baby</t>
         </is>
       </c>
       <c r="E401" s="2" t="inlineStr">
         <is>
-          <t>cafe</t>
+          <t>beauty salon</t>
         </is>
       </c>
       <c r="F401" s="2" t="inlineStr">
         <is>
-          <t>Cairns</t>
+          <t>Gold Coast</t>
         </is>
       </c>
       <c r="G401" s="2" t="inlineStr">
@@ -29151,32 +29159,32 @@
       </c>
       <c r="H401" s="4" t="inlineStr">
         <is>
-          <t>http://instagram.com/mama_coco</t>
+          <t>http://instagram.com/sugarme_baby</t>
         </is>
       </c>
       <c r="I401" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/mamacococafe</t>
+          <t>https://www.facebook.com/sugarmebaby</t>
         </is>
       </c>
       <c r="J401" s="2" t="inlineStr">
         <is>
-          <t>+61 7 4052 1226</t>
+          <t>+61 432 128 318</t>
         </is>
       </c>
       <c r="K401" s="4" t="inlineStr">
         <is>
-          <t>http://www.mamacoco.com.au</t>
+          <t>http://www.sugarmebaby.com.au/home/</t>
         </is>
       </c>
       <c r="L401" s="2" t="inlineStr">
         <is>
-          <t>no HTTPS (browser shows 'Not secure'); missing meta description; slow to load (4.2s)</t>
+          <t>no HTTPS (browser shows 'Not secure'); looks outdated (copyright 2023)</t>
         </is>
       </c>
       <c r="M401" s="2" t="inlineStr">
         <is>
-          <t>Hi Mama Coco team! [one real detail from their page]. We're AceAds, a web design studio. We think your website could be doing more to bring in customers. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
+          <t>Hi Sugar Me Baby team! [one real detail from their page]. We're AceAds, a web design studio. We think your website could be doing more to bring in customers. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
         </is>
       </c>
       <c r="N401" s="4" t="inlineStr">
@@ -29210,12 +29218,12 @@
       </c>
       <c r="D402" s="2" t="inlineStr">
         <is>
-          <t>Sugar Me Baby</t>
+          <t>Love Lara Jewellers</t>
         </is>
       </c>
       <c r="E402" s="2" t="inlineStr">
         <is>
-          <t>beauty salon</t>
+          <t>boutique</t>
         </is>
       </c>
       <c r="F402" s="2" t="inlineStr">
@@ -29230,32 +29238,32 @@
       </c>
       <c r="H402" s="4" t="inlineStr">
         <is>
-          <t>http://instagram.com/sugarme_baby</t>
+          <t>https://www.instagram.com/lovelarajewellery</t>
         </is>
       </c>
       <c r="I402" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/sugarmebaby</t>
+          <t>https://www.facebook.com/Love-Lara-Jewellery-191476280881144</t>
         </is>
       </c>
       <c r="J402" s="2" t="inlineStr">
         <is>
-          <t>+61 432 128 318</t>
+          <t>+61 7 5593 6262</t>
         </is>
       </c>
       <c r="K402" s="4" t="inlineStr">
         <is>
-          <t>http://www.sugarmebaby.com.au/home/</t>
+          <t>https://lovelarajewellery.com.au/</t>
         </is>
       </c>
       <c r="L402" s="2" t="inlineStr">
         <is>
-          <t>no HTTPS (browser shows 'Not secure'); looks outdated (copyright 2023)</t>
+          <t>looks outdated (copyright 2020); missing meta description; slow to load (3.7s)</t>
         </is>
       </c>
       <c r="M402" s="2" t="inlineStr">
         <is>
-          <t>Hi Sugar Me Baby team! [one real detail from their page]. We're AceAds, a web design studio. We think your website could be doing more to bring in customers. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
+          <t>Hi Love Lara Jewellers team! [one real detail from their page]. We're AceAds, a web design studio. We noticed your website takes a while to load on a phone, which is where most people will first see it. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
         </is>
       </c>
       <c r="N402" s="4" t="inlineStr">
@@ -29289,12 +29297,12 @@
       </c>
       <c r="D403" s="2" t="inlineStr">
         <is>
-          <t>Love Lara Jewellers</t>
+          <t>Benowa Hills Early Learning Centre</t>
         </is>
       </c>
       <c r="E403" s="2" t="inlineStr">
         <is>
-          <t>boutique</t>
+          <t>childcare</t>
         </is>
       </c>
       <c r="F403" s="2" t="inlineStr">
@@ -29309,32 +29317,28 @@
       </c>
       <c r="H403" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/lovelarajewellery</t>
+          <t>https://instagram.com/Benowaandbenowahillselc</t>
         </is>
       </c>
       <c r="I403" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/Love-Lara-Jewellery-191476280881144</t>
-        </is>
-      </c>
-      <c r="J403" s="2" t="inlineStr">
-        <is>
-          <t>+61 7 5593 6262</t>
-        </is>
-      </c>
+          <t>https://www.facebook.com/people/Benowa-Hills-Early-Learning-Centre/100057676358993</t>
+        </is>
+      </c>
+      <c r="J403" s="2" t="inlineStr"/>
       <c r="K403" s="4" t="inlineStr">
         <is>
-          <t>https://lovelarajewellery.com.au/</t>
+          <t>https://www.benowahillsearlylearning.com.au/</t>
         </is>
       </c>
       <c r="L403" s="2" t="inlineStr">
         <is>
-          <t>looks outdated (copyright 2020); missing meta description; slow to load (3.7s)</t>
+          <t>looks outdated (copyright 2015); missing meta description; slow to load (12.2s)</t>
         </is>
       </c>
       <c r="M403" s="2" t="inlineStr">
         <is>
-          <t>Hi Love Lara Jewellers team! [one real detail from their page]. We're AceAds, a web design studio. We think your website could be doing more to bring in customers. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
+          <t>Hi Benowa Hills Early Learning Centre team! [one real detail from their page]. We're AceAds, a web design studio. We noticed your website takes a while to load on a phone, which is where most people will first see it. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
         </is>
       </c>
       <c r="N403" s="4" t="inlineStr">
@@ -29368,12 +29372,12 @@
       </c>
       <c r="D404" s="2" t="inlineStr">
         <is>
-          <t>Benowa Hills Early Learning Centre</t>
+          <t>Grimmo's garage</t>
         </is>
       </c>
       <c r="E404" s="2" t="inlineStr">
         <is>
-          <t>childcare</t>
+          <t>mechanic</t>
         </is>
       </c>
       <c r="F404" s="2" t="inlineStr">
@@ -29383,33 +29387,29 @@
       </c>
       <c r="G404" s="2" t="inlineStr">
         <is>
-          <t>Instagram</t>
-        </is>
-      </c>
-      <c r="H404" s="4" t="inlineStr">
-        <is>
-          <t>https://instagram.com/Benowaandbenowahillselc</t>
-        </is>
-      </c>
+          <t>Facebook</t>
+        </is>
+      </c>
+      <c r="H404" s="2" t="inlineStr"/>
       <c r="I404" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/people/Benowa-Hills-Early-Learning-Centre/100057676358993</t>
+          <t>https://www.facebook.com/GrimmosGarage</t>
         </is>
       </c>
       <c r="J404" s="2" t="inlineStr"/>
       <c r="K404" s="4" t="inlineStr">
         <is>
-          <t>https://www.benowahillsearlylearning.com.au/</t>
+          <t>https://www.grimmos.com.au/</t>
         </is>
       </c>
       <c r="L404" s="2" t="inlineStr">
         <is>
-          <t>looks outdated (copyright 2015); missing meta description; slow to load (12.2s)</t>
+          <t>looks outdated (copyright 2019); missing meta description; slow to load (3.1s)</t>
         </is>
       </c>
       <c r="M404" s="2" t="inlineStr">
         <is>
-          <t>Hi Benowa Hills Early Learning Centre team! [one real detail from their page]. We're AceAds, a web design studio. We think your website could be doing more to bring in customers. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
+          <t>Hi Grimmo's garage team! [one real detail from their page]. We're AceAds, a web design studio. We noticed your website takes a while to load on a phone, which is where most people will first see it. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
         </is>
       </c>
       <c r="N404" s="4" t="inlineStr">
@@ -29443,7 +29443,7 @@
       </c>
       <c r="D405" s="2" t="inlineStr">
         <is>
-          <t>Grimmo's garage</t>
+          <t>Southport Exhaust</t>
         </is>
       </c>
       <c r="E405" s="2" t="inlineStr">
@@ -29464,23 +29464,27 @@
       <c r="H405" s="2" t="inlineStr"/>
       <c r="I405" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/GrimmosGarage</t>
-        </is>
-      </c>
-      <c r="J405" s="2" t="inlineStr"/>
+          <t>https://www.facebook.com/southportexhaust</t>
+        </is>
+      </c>
+      <c r="J405" s="2" t="inlineStr">
+        <is>
+          <t>+61 7 5532 4707</t>
+        </is>
+      </c>
       <c r="K405" s="4" t="inlineStr">
         <is>
-          <t>https://www.grimmos.com.au/</t>
+          <t>https://southportexhaust.com.au/</t>
         </is>
       </c>
       <c r="L405" s="2" t="inlineStr">
         <is>
-          <t>looks outdated (copyright 2019); missing meta description; slow to load (3.1s)</t>
+          <t>looks outdated (copyright 2015); missing meta description; slow to load (3.3s)</t>
         </is>
       </c>
       <c r="M405" s="2" t="inlineStr">
         <is>
-          <t>Hi Grimmo's garage team! [one real detail from their page]. We're AceAds, a web design studio. We think your website could be doing more to bring in customers. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
+          <t>Hi Southport Exhaust team! [one real detail from their page]. We're AceAds, a web design studio. We noticed your website takes a while to load on a phone, which is where most people will first see it. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
         </is>
       </c>
       <c r="N405" s="4" t="inlineStr">
@@ -29514,12 +29518,12 @@
       </c>
       <c r="D406" s="2" t="inlineStr">
         <is>
-          <t>Southport Exhaust</t>
+          <t>Willow Dining Room</t>
         </is>
       </c>
       <c r="E406" s="2" t="inlineStr">
         <is>
-          <t>mechanic</t>
+          <t>restaurant</t>
         </is>
       </c>
       <c r="F406" s="2" t="inlineStr">
@@ -29535,27 +29539,27 @@
       <c r="H406" s="2" t="inlineStr"/>
       <c r="I406" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/southportexhaust</t>
+          <t>https://www.facebook.com/WillowDiningRoom</t>
         </is>
       </c>
       <c r="J406" s="2" t="inlineStr">
         <is>
-          <t>+61 7 5532 4707</t>
+          <t>+61 7 5576 4110</t>
         </is>
       </c>
       <c r="K406" s="4" t="inlineStr">
         <is>
-          <t>https://southportexhaust.com.au/</t>
+          <t>http://willowdiningroom.com/homepage/</t>
         </is>
       </c>
       <c r="L406" s="2" t="inlineStr">
         <is>
-          <t>looks outdated (copyright 2015); missing meta description; slow to load (3.3s)</t>
+          <t>no HTTPS (browser shows 'Not secure'); looks outdated (copyright 2015); missing meta description</t>
         </is>
       </c>
       <c r="M406" s="2" t="inlineStr">
         <is>
-          <t>Hi Southport Exhaust team! [one real detail from their page]. We're AceAds, a web design studio. We think your website could be doing more to bring in customers. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
+          <t>Hi Willow Dining Room team! [one real detail from their page]. We're AceAds, a web design studio. We think your website could be doing more to bring in customers. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
         </is>
       </c>
       <c r="N406" s="4" t="inlineStr">
@@ -29589,7 +29593,7 @@
       </c>
       <c r="D407" s="2" t="inlineStr">
         <is>
-          <t>Willow Dining Room</t>
+          <t>Barcella</t>
         </is>
       </c>
       <c r="E407" s="2" t="inlineStr">
@@ -29599,38 +29603,42 @@
       </c>
       <c r="F407" s="2" t="inlineStr">
         <is>
-          <t>Gold Coast</t>
+          <t>Redlands</t>
         </is>
       </c>
       <c r="G407" s="2" t="inlineStr">
         <is>
-          <t>Facebook</t>
-        </is>
-      </c>
-      <c r="H407" s="2" t="inlineStr"/>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="H407" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/barcelladining</t>
+        </is>
+      </c>
       <c r="I407" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/WillowDiningRoom</t>
+          <t>https://www.facebook.com/BarcellaRestaurantVictoriaPoint</t>
         </is>
       </c>
       <c r="J407" s="2" t="inlineStr">
         <is>
-          <t>+61 7 5576 4110</t>
+          <t>+61 7 3207 6668</t>
         </is>
       </c>
       <c r="K407" s="4" t="inlineStr">
         <is>
-          <t>http://willowdiningroom.com/homepage/</t>
+          <t>https://barcella.com.au/</t>
         </is>
       </c>
       <c r="L407" s="2" t="inlineStr">
         <is>
-          <t>no HTTPS (browser shows 'Not secure'); looks outdated (copyright 2015); missing meta description</t>
+          <t>looks outdated (copyright 2022); missing meta description; slow to load (3.9s)</t>
         </is>
       </c>
       <c r="M407" s="2" t="inlineStr">
         <is>
-          <t>Hi Willow Dining Room team! [one real detail from their page]. We're AceAds, a web design studio. We think your website could be doing more to bring in customers. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
+          <t>Hi Barcella team! [one real detail from their page]. We're AceAds, a web design studio. We noticed your website takes a while to load on a phone, which is where most people will first see it. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
         </is>
       </c>
       <c r="N407" s="4" t="inlineStr">
@@ -29664,52 +29672,44 @@
       </c>
       <c r="D408" s="2" t="inlineStr">
         <is>
-          <t>Barcella</t>
+          <t>De Lish Fish @ Kings</t>
         </is>
       </c>
       <c r="E408" s="2" t="inlineStr">
         <is>
-          <t>restaurant</t>
+          <t>takeaway</t>
         </is>
       </c>
       <c r="F408" s="2" t="inlineStr">
         <is>
-          <t>Redlands</t>
+          <t>Sunshine Coast</t>
         </is>
       </c>
       <c r="G408" s="2" t="inlineStr">
         <is>
-          <t>Instagram</t>
-        </is>
-      </c>
-      <c r="H408" s="4" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/barcelladining</t>
-        </is>
-      </c>
+          <t>Facebook</t>
+        </is>
+      </c>
+      <c r="H408" s="2" t="inlineStr"/>
       <c r="I408" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/BarcellaRestaurantVictoriaPoint</t>
-        </is>
-      </c>
-      <c r="J408" s="2" t="inlineStr">
-        <is>
-          <t>+61 7 3207 6668</t>
-        </is>
-      </c>
+          <t>https://www.facebook.com/pages/De-Lish-Fish-at-Kings/547467392024234</t>
+        </is>
+      </c>
+      <c r="J408" s="2" t="inlineStr"/>
       <c r="K408" s="4" t="inlineStr">
         <is>
-          <t>https://barcella.com.au/</t>
+          <t>http://delishfish.com.au/</t>
         </is>
       </c>
       <c r="L408" s="2" t="inlineStr">
         <is>
-          <t>looks outdated (copyright 2022); missing meta description; slow to load (3.9s)</t>
+          <t>no HTTPS (browser shows 'Not secure'); looks outdated (copyright 2014)</t>
         </is>
       </c>
       <c r="M408" s="2" t="inlineStr">
         <is>
-          <t>Hi Barcella team! [one real detail from their page]. We're AceAds, a web design studio. We think your website could be doing more to bring in customers. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
+          <t>Hi De Lish Fish @ Kings team! [one real detail from their page]. We're AceAds, a web design studio. We think your website could be doing more to bring in customers. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
         </is>
       </c>
       <c r="N408" s="4" t="inlineStr">
@@ -29743,12 +29743,12 @@
       </c>
       <c r="D409" s="2" t="inlineStr">
         <is>
-          <t>De Lish Fish @ Kings</t>
+          <t>Ink Attack Tattoo</t>
         </is>
       </c>
       <c r="E409" s="2" t="inlineStr">
         <is>
-          <t>takeaway</t>
+          <t>tattoo studio</t>
         </is>
       </c>
       <c r="F409" s="2" t="inlineStr">
@@ -29758,29 +29758,33 @@
       </c>
       <c r="G409" s="2" t="inlineStr">
         <is>
-          <t>Facebook</t>
-        </is>
-      </c>
-      <c r="H409" s="2" t="inlineStr"/>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="H409" s="4" t="inlineStr">
+        <is>
+          <t>http://instagram.com/ink_attack</t>
+        </is>
+      </c>
       <c r="I409" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/pages/De-Lish-Fish-at-Kings/547467392024234</t>
+          <t>https://www.facebook.com/InkAttackTattooStudio</t>
         </is>
       </c>
       <c r="J409" s="2" t="inlineStr"/>
       <c r="K409" s="4" t="inlineStr">
         <is>
-          <t>http://delishfish.com.au/</t>
+          <t>http://www.inkattack.com.au</t>
         </is>
       </c>
       <c r="L409" s="2" t="inlineStr">
         <is>
-          <t>no HTTPS (browser shows 'Not secure'); looks outdated (copyright 2014)</t>
+          <t>no HTTPS (browser shows 'Not secure'); looks outdated (copyright 2019)</t>
         </is>
       </c>
       <c r="M409" s="2" t="inlineStr">
         <is>
-          <t>Hi De Lish Fish @ Kings team! [one real detail from their page]. We're AceAds, a web design studio. We think your website could be doing more to bring in customers. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
+          <t>Hi Ink Attack Tattoo team! [one real detail from their page]. We're AceAds, a web design studio. We think your website could be doing more to bring in customers. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
         </is>
       </c>
       <c r="N409" s="4" t="inlineStr">
@@ -29814,12 +29818,12 @@
       </c>
       <c r="D410" s="2" t="inlineStr">
         <is>
-          <t>Ink Attack Tattoo</t>
+          <t>RJH Electrical</t>
         </is>
       </c>
       <c r="E410" s="2" t="inlineStr">
         <is>
-          <t>tattoo studio</t>
+          <t>trades</t>
         </is>
       </c>
       <c r="F410" s="2" t="inlineStr">
@@ -29829,33 +29833,33 @@
       </c>
       <c r="G410" s="2" t="inlineStr">
         <is>
-          <t>Instagram</t>
-        </is>
-      </c>
-      <c r="H410" s="4" t="inlineStr">
-        <is>
-          <t>http://instagram.com/ink_attack</t>
-        </is>
-      </c>
+          <t>Facebook</t>
+        </is>
+      </c>
+      <c r="H410" s="2" t="inlineStr"/>
       <c r="I410" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/InkAttackTattooStudio</t>
-        </is>
-      </c>
-      <c r="J410" s="2" t="inlineStr"/>
+          <t>https://www.facebook.com/SunshineCoastElectrician1</t>
+        </is>
+      </c>
+      <c r="J410" s="2" t="inlineStr">
+        <is>
+          <t>+61 448 960 299</t>
+        </is>
+      </c>
       <c r="K410" s="4" t="inlineStr">
         <is>
-          <t>http://www.inkattack.com.au</t>
+          <t>http://www.rjhelectrical.com.au/</t>
         </is>
       </c>
       <c r="L410" s="2" t="inlineStr">
         <is>
-          <t>no HTTPS (browser shows 'Not secure'); looks outdated (copyright 2019)</t>
+          <t>no HTTPS (browser shows 'Not secure'); looks outdated (copyright 2015); slow to load (3.3s)</t>
         </is>
       </c>
       <c r="M410" s="2" t="inlineStr">
         <is>
-          <t>Hi Ink Attack Tattoo team! [one real detail from their page]. We're AceAds, a web design studio. We think your website could be doing more to bring in customers. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
+          <t>Hi RJH Electrical team! [one real detail from their page]. We're AceAds, a web design studio. We noticed your website takes a while to load on a phone, which is where most people will first see it. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
         </is>
       </c>
       <c r="N410" s="4" t="inlineStr">
@@ -29889,17 +29893,17 @@
       </c>
       <c r="D411" s="2" t="inlineStr">
         <is>
-          <t>RJH Electrical</t>
+          <t>Bou's For Men Barber Shop</t>
         </is>
       </c>
       <c r="E411" s="2" t="inlineStr">
         <is>
-          <t>trades</t>
+          <t>barber or hairdresser</t>
         </is>
       </c>
       <c r="F411" s="2" t="inlineStr">
         <is>
-          <t>Sunshine Coast</t>
+          <t>Toowoomba</t>
         </is>
       </c>
       <c r="G411" s="2" t="inlineStr">
@@ -29910,27 +29914,27 @@
       <c r="H411" s="2" t="inlineStr"/>
       <c r="I411" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/SunshineCoastElectrician1</t>
+          <t>https://www.facebook.com/BousForMen</t>
         </is>
       </c>
       <c r="J411" s="2" t="inlineStr">
         <is>
-          <t>+61 448 960 299</t>
+          <t>+61 7 4615 4881</t>
         </is>
       </c>
       <c r="K411" s="4" t="inlineStr">
         <is>
-          <t>http://www.rjhelectrical.com.au/</t>
+          <t>https://www.bousformen.com.au/</t>
         </is>
       </c>
       <c r="L411" s="2" t="inlineStr">
         <is>
-          <t>no HTTPS (browser shows 'Not secure'); looks outdated (copyright 2015); slow to load (3.3s)</t>
+          <t>not mobile-friendly (no viewport tag); missing meta description</t>
         </is>
       </c>
       <c r="M411" s="2" t="inlineStr">
         <is>
-          <t>Hi RJH Electrical team! [one real detail from their page]. We're AceAds, a web design studio. We think your website could be doing more to bring in customers. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
+          <t>Hi Bou's For Men Barber Shop team! [one real detail from their page]. We're AceAds, a web design studio. We noticed your website is hard to use on a phone. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
         </is>
       </c>
       <c r="N411" s="4" t="inlineStr">
@@ -29964,17 +29968,17 @@
       </c>
       <c r="D412" s="2" t="inlineStr">
         <is>
-          <t>Bou's For Men Barber Shop</t>
+          <t>The Great Jewel Of India</t>
         </is>
       </c>
       <c r="E412" s="2" t="inlineStr">
         <is>
-          <t>barber or hairdresser</t>
+          <t>restaurant</t>
         </is>
       </c>
       <c r="F412" s="2" t="inlineStr">
         <is>
-          <t>Toowoomba</t>
+          <t>Townsville</t>
         </is>
       </c>
       <c r="G412" s="2" t="inlineStr">
@@ -29985,27 +29989,27 @@
       <c r="H412" s="2" t="inlineStr"/>
       <c r="I412" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/BousForMen</t>
+          <t>https://www.facebook.com/TheGreatJewelOfIndia</t>
         </is>
       </c>
       <c r="J412" s="2" t="inlineStr">
         <is>
-          <t>+61 7 4615 4881</t>
+          <t>+61 7 4771 3144</t>
         </is>
       </c>
       <c r="K412" s="4" t="inlineStr">
         <is>
-          <t>https://www.bousformen.com.au/</t>
+          <t>http://www.thegreatjewelofindia.com/</t>
         </is>
       </c>
       <c r="L412" s="2" t="inlineStr">
         <is>
-          <t>not mobile-friendly (no viewport tag); missing meta description</t>
+          <t>no HTTPS (browser shows 'Not secure'); missing page title; missing meta description</t>
         </is>
       </c>
       <c r="M412" s="2" t="inlineStr">
         <is>
-          <t>Hi Bou's For Men Barber Shop team! [one real detail from their page]. We're AceAds, a web design studio. We noticed your website is hard to use on a phone. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
+          <t>Hi The Great Jewel Of India team! [one real detail from their page]. We're AceAds, a web design studio. We think your website could be doing more to bring in customers. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
         </is>
       </c>
       <c r="N412" s="4" t="inlineStr">
@@ -30023,84 +30027,9 @@
       <c r="R412" s="2" t="inlineStr"/>
       <c r="S412" s="2" t="inlineStr"/>
     </row>
-    <row r="413">
-      <c r="A413" s="2" t="n">
-        <v>412</v>
-      </c>
-      <c r="B413" s="6" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="C413" s="2" t="inlineStr">
-        <is>
-          <t>Weak website</t>
-        </is>
-      </c>
-      <c r="D413" s="2" t="inlineStr">
-        <is>
-          <t>The Great Jewel Of India</t>
-        </is>
-      </c>
-      <c r="E413" s="2" t="inlineStr">
-        <is>
-          <t>restaurant</t>
-        </is>
-      </c>
-      <c r="F413" s="2" t="inlineStr">
-        <is>
-          <t>Townsville</t>
-        </is>
-      </c>
-      <c r="G413" s="2" t="inlineStr">
-        <is>
-          <t>Facebook</t>
-        </is>
-      </c>
-      <c r="H413" s="2" t="inlineStr"/>
-      <c r="I413" s="4" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/TheGreatJewelOfIndia</t>
-        </is>
-      </c>
-      <c r="J413" s="2" t="inlineStr">
-        <is>
-          <t>+61 7 4771 3144</t>
-        </is>
-      </c>
-      <c r="K413" s="4" t="inlineStr">
-        <is>
-          <t>http://www.thegreatjewelofindia.com/</t>
-        </is>
-      </c>
-      <c r="L413" s="2" t="inlineStr">
-        <is>
-          <t>no HTTPS (browser shows 'Not secure'); missing page title; missing meta description</t>
-        </is>
-      </c>
-      <c r="M413" s="2" t="inlineStr">
-        <is>
-          <t>Hi The Great Jewel Of India team! [one real detail from their page]. We're AceAds, a web design studio. We think your website could be doing more to bring in customers. We'd be happy to make you a free preview of what a website could look like. Want one? No cost, no obligation.</t>
-        </is>
-      </c>
-      <c r="N413" s="4" t="inlineStr">
-        <is>
-          <t>Open map</t>
-        </is>
-      </c>
-      <c r="O413" s="2" t="inlineStr">
-        <is>
-          <t>Not contacted</t>
-        </is>
-      </c>
-      <c r="P413" s="2" t="inlineStr"/>
-      <c r="Q413" s="2" t="inlineStr"/>
-      <c r="R413" s="2" t="inlineStr"/>
-      <c r="S413" s="2" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:S413"/>
-  <conditionalFormatting sqref="A2:S413">
+  <autoFilter ref="A1:S412"/>
+  <conditionalFormatting sqref="A2:S412">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$O2="Won"</formula>
     </cfRule>
@@ -30118,10 +30047,10 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation sqref="O2:O413" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="O2:O412" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Not contacted,DM sent,Replied,Preview sent,Meeting booked,Won,Not interested,Business closed"</formula1>
     </dataValidation>
-    <dataValidation sqref="Q2:R413" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="date"/>
+    <dataValidation sqref="Q2:R412" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="date"/>
   </dataValidations>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I2" r:id="rId1"/>
@@ -30700,13 +30629,13 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N219" r:id="rId574"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I220" r:id="rId575"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N220" r:id="rId576"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I221" r:id="rId577"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H221" r:id="rId577"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N221" r:id="rId578"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H222" r:id="rId579"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I222" r:id="rId579"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N222" r:id="rId580"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I223" r:id="rId581"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H223" r:id="rId581"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N223" r:id="rId582"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H224" r:id="rId583"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I224" r:id="rId583"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N224" r:id="rId584"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I225" r:id="rId585"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N225" r:id="rId586"/>
@@ -30762,9 +30691,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N250" r:id="rId636"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I251" r:id="rId637"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N251" r:id="rId638"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I252" r:id="rId639"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N252" r:id="rId640"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H253" r:id="rId641"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H252" r:id="rId639"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I252" r:id="rId640"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N252" r:id="rId641"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I253" r:id="rId642"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N253" r:id="rId643"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I254" r:id="rId644"/>
@@ -30791,17 +30720,17 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N264" r:id="rId665"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I265" r:id="rId666"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N265" r:id="rId667"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I266" r:id="rId668"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H266" r:id="rId668"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N266" r:id="rId669"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H267" r:id="rId670"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N267" r:id="rId671"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H268" r:id="rId672"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I268" r:id="rId673"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K268" r:id="rId674"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I267" r:id="rId671"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K267" r:id="rId672"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N267" r:id="rId673"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I268" r:id="rId674"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N268" r:id="rId675"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I269" r:id="rId676"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H269" r:id="rId676"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N269" r:id="rId677"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H270" r:id="rId678"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I270" r:id="rId678"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N270" r:id="rId679"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I271" r:id="rId680"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N271" r:id="rId681"/>
@@ -30817,66 +30746,66 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N276" r:id="rId691"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I277" r:id="rId692"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N277" r:id="rId693"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I278" r:id="rId694"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H278" r:id="rId694"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N278" r:id="rId695"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H279" r:id="rId696"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I279" r:id="rId696"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N279" r:id="rId697"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I280" r:id="rId698"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N280" r:id="rId699"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I281" r:id="rId700"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H281" r:id="rId700"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N281" r:id="rId701"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H282" r:id="rId702"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I282" r:id="rId702"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N282" r:id="rId703"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I283" r:id="rId704"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N283" r:id="rId705"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H284" r:id="rId706"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I284" r:id="rId707"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K284" r:id="rId708"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H283" r:id="rId704"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I283" r:id="rId705"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K283" r:id="rId706"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N283" r:id="rId707"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H284" r:id="rId708"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N284" r:id="rId709"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H285" r:id="rId710"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N285" r:id="rId711"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H286" r:id="rId712"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I285" r:id="rId711"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N285" r:id="rId712"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I286" r:id="rId713"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N286" r:id="rId714"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I287" r:id="rId715"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N287" r:id="rId716"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H288" r:id="rId717"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H287" r:id="rId715"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I287" r:id="rId716"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N287" r:id="rId717"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I288" r:id="rId718"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N288" r:id="rId719"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I289" r:id="rId720"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N289" r:id="rId721"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I290" r:id="rId722"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N290" r:id="rId723"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I291" r:id="rId724"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N291" r:id="rId725"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H292" r:id="rId726"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H291" r:id="rId724"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I291" r:id="rId725"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N291" r:id="rId726"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I292" r:id="rId727"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N292" r:id="rId728"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I293" r:id="rId729"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N293" r:id="rId730"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I294" r:id="rId731"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H294" r:id="rId731"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N294" r:id="rId732"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H295" r:id="rId733"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N295" r:id="rId734"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H296" r:id="rId735"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I296" r:id="rId735"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N296" r:id="rId736"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I297" r:id="rId737"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N297" r:id="rId738"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I298" r:id="rId739"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N298" r:id="rId740"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I299" r:id="rId741"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N299" r:id="rId742"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H300" r:id="rId743"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H299" r:id="rId741"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I299" r:id="rId742"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N299" r:id="rId743"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I300" r:id="rId744"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N300" r:id="rId745"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I301" r:id="rId746"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N301" r:id="rId747"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H302" r:id="rId748"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H301" r:id="rId746"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I301" r:id="rId747"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N301" r:id="rId748"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I302" r:id="rId749"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N302" r:id="rId750"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I303" r:id="rId751"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N303" r:id="rId752"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H304" r:id="rId753"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H303" r:id="rId751"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I303" r:id="rId752"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N303" r:id="rId753"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I304" r:id="rId754"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N304" r:id="rId755"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I305" r:id="rId756"/>
@@ -30909,15 +30838,15 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N318" r:id="rId783"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I319" r:id="rId784"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N319" r:id="rId785"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I320" r:id="rId786"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H320" r:id="rId786"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N320" r:id="rId787"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H321" r:id="rId788"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I321" r:id="rId788"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N321" r:id="rId789"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I322" r:id="rId790"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N322" r:id="rId791"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I323" r:id="rId792"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H323" r:id="rId792"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N323" r:id="rId793"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H324" r:id="rId794"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I324" r:id="rId794"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N324" r:id="rId795"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I325" r:id="rId796"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N325" r:id="rId797"/>
@@ -30927,14 +30856,14 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N327" r:id="rId801"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I328" r:id="rId802"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N328" r:id="rId803"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I329" r:id="rId804"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N329" r:id="rId805"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H330" r:id="rId806"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I330" r:id="rId807"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H329" r:id="rId804"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I329" r:id="rId805"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N329" r:id="rId806"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H330" r:id="rId807"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N330" r:id="rId808"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H331" r:id="rId809"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N331" r:id="rId810"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H332" r:id="rId811"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I331" r:id="rId810"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N331" r:id="rId811"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I332" r:id="rId812"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N332" r:id="rId813"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I333" r:id="rId814"/>
@@ -30947,9 +30876,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N336" r:id="rId821"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I337" r:id="rId822"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N337" r:id="rId823"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I338" r:id="rId824"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H338" r:id="rId824"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N338" r:id="rId825"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H339" r:id="rId826"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I339" r:id="rId826"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N339" r:id="rId827"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I340" r:id="rId828"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N340" r:id="rId829"/>
@@ -30963,9 +30892,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N344" r:id="rId837"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I345" r:id="rId838"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N345" r:id="rId839"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I346" r:id="rId840"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N346" r:id="rId841"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H347" r:id="rId842"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H346" r:id="rId840"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I346" r:id="rId841"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N346" r:id="rId842"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I347" r:id="rId843"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N347" r:id="rId844"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I348" r:id="rId845"/>
@@ -30992,9 +30921,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N358" r:id="rId866"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I359" r:id="rId867"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N359" r:id="rId868"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I360" r:id="rId869"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N360" r:id="rId870"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H361" r:id="rId871"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H360" r:id="rId869"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I360" r:id="rId870"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N360" r:id="rId871"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I361" r:id="rId872"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N361" r:id="rId873"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I362" r:id="rId874"/>
@@ -31009,27 +30938,27 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N366" r:id="rId883"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I367" r:id="rId884"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N367" r:id="rId885"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I368" r:id="rId886"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N368" r:id="rId887"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H369" r:id="rId888"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H368" r:id="rId886"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I368" r:id="rId887"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N368" r:id="rId888"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I369" r:id="rId889"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N369" r:id="rId890"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I370" r:id="rId891"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N370" r:id="rId892"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I371" r:id="rId893"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H371" r:id="rId893"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N371" r:id="rId894"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H372" r:id="rId895"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I372" r:id="rId895"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N372" r:id="rId896"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I373" r:id="rId897"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N373" r:id="rId898"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H374" r:id="rId899"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I374" r:id="rId900"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H373" r:id="rId897"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I373" r:id="rId898"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N373" r:id="rId899"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H374" r:id="rId900"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N374" r:id="rId901"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H375" r:id="rId902"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I375" r:id="rId902"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N375" r:id="rId903"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I376" r:id="rId904"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N376" r:id="rId905"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H377" r:id="rId906"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H376" r:id="rId904"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I376" r:id="rId905"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N376" r:id="rId906"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I377" r:id="rId907"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N377" r:id="rId908"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I378" r:id="rId909"/>
@@ -31045,105 +30974,103 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I383" r:id="rId919"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N383" r:id="rId920"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I384" r:id="rId921"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N384" r:id="rId922"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I385" r:id="rId923"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K385" r:id="rId924"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K384" r:id="rId922"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N384" r:id="rId923"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I385" r:id="rId924"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N385" r:id="rId925"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I386" r:id="rId926"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N386" r:id="rId927"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I387" r:id="rId928"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K387" r:id="rId929"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N387" r:id="rId930"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I388" r:id="rId931"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K388" r:id="rId932"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N388" r:id="rId933"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H389" r:id="rId934"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I389" r:id="rId935"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K389" r:id="rId936"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N389" r:id="rId937"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I390" r:id="rId938"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K390" r:id="rId939"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N390" r:id="rId940"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I391" r:id="rId941"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K391" r:id="rId942"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N391" r:id="rId943"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I392" r:id="rId944"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K392" r:id="rId945"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N392" r:id="rId946"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I393" r:id="rId947"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K393" r:id="rId948"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N393" r:id="rId949"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H394" r:id="rId950"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I394" r:id="rId951"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K394" r:id="rId952"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N394" r:id="rId953"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H395" r:id="rId954"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I395" r:id="rId955"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K395" r:id="rId956"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N395" r:id="rId957"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H396" r:id="rId958"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I396" r:id="rId959"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K396" r:id="rId960"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N396" r:id="rId961"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H397" r:id="rId962"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I397" r:id="rId963"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K397" r:id="rId964"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N397" r:id="rId965"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H398" r:id="rId966"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I398" r:id="rId967"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K398" r:id="rId968"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N398" r:id="rId969"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I399" r:id="rId970"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K399" r:id="rId971"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N399" r:id="rId972"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I400" r:id="rId973"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K400" r:id="rId974"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N400" r:id="rId975"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H401" r:id="rId976"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I401" r:id="rId977"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K401" r:id="rId978"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N401" r:id="rId979"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H402" r:id="rId980"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I402" r:id="rId981"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K402" r:id="rId982"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N402" r:id="rId983"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H403" r:id="rId984"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I403" r:id="rId985"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K403" r:id="rId986"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N403" r:id="rId987"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H404" r:id="rId988"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I404" r:id="rId989"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K404" r:id="rId990"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N404" r:id="rId991"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I405" r:id="rId992"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K405" r:id="rId993"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N405" r:id="rId994"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I406" r:id="rId995"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K406" r:id="rId996"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N406" r:id="rId997"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I407" r:id="rId998"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K407" r:id="rId999"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N407" r:id="rId1000"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H408" r:id="rId1001"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I408" r:id="rId1002"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K408" r:id="rId1003"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N408" r:id="rId1004"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I409" r:id="rId1005"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K409" r:id="rId1006"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N409" r:id="rId1007"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H410" r:id="rId1008"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I410" r:id="rId1009"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K410" r:id="rId1010"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N410" r:id="rId1011"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I411" r:id="rId1012"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K411" r:id="rId1013"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N411" r:id="rId1014"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I412" r:id="rId1015"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K412" r:id="rId1016"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N412" r:id="rId1017"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I413" r:id="rId1018"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K413" r:id="rId1019"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N413" r:id="rId1020"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K386" r:id="rId927"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N386" r:id="rId928"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I387" r:id="rId929"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K387" r:id="rId930"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N387" r:id="rId931"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H388" r:id="rId932"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I388" r:id="rId933"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K388" r:id="rId934"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N388" r:id="rId935"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I389" r:id="rId936"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K389" r:id="rId937"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N389" r:id="rId938"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I390" r:id="rId939"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K390" r:id="rId940"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N390" r:id="rId941"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I391" r:id="rId942"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K391" r:id="rId943"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N391" r:id="rId944"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I392" r:id="rId945"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K392" r:id="rId946"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N392" r:id="rId947"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H393" r:id="rId948"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I393" r:id="rId949"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K393" r:id="rId950"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N393" r:id="rId951"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H394" r:id="rId952"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I394" r:id="rId953"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K394" r:id="rId954"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N394" r:id="rId955"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H395" r:id="rId956"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I395" r:id="rId957"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K395" r:id="rId958"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N395" r:id="rId959"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H396" r:id="rId960"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I396" r:id="rId961"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K396" r:id="rId962"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N396" r:id="rId963"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H397" r:id="rId964"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I397" r:id="rId965"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K397" r:id="rId966"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N397" r:id="rId967"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I398" r:id="rId968"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K398" r:id="rId969"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N398" r:id="rId970"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I399" r:id="rId971"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K399" r:id="rId972"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N399" r:id="rId973"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H400" r:id="rId974"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I400" r:id="rId975"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K400" r:id="rId976"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N400" r:id="rId977"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H401" r:id="rId978"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I401" r:id="rId979"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K401" r:id="rId980"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N401" r:id="rId981"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H402" r:id="rId982"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I402" r:id="rId983"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K402" r:id="rId984"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N402" r:id="rId985"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H403" r:id="rId986"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I403" r:id="rId987"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K403" r:id="rId988"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N403" r:id="rId989"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I404" r:id="rId990"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K404" r:id="rId991"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N404" r:id="rId992"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I405" r:id="rId993"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K405" r:id="rId994"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N405" r:id="rId995"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I406" r:id="rId996"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K406" r:id="rId997"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N406" r:id="rId998"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H407" r:id="rId999"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I407" r:id="rId1000"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K407" r:id="rId1001"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N407" r:id="rId1002"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I408" r:id="rId1003"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K408" r:id="rId1004"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N408" r:id="rId1005"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H409" r:id="rId1006"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I409" r:id="rId1007"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K409" r:id="rId1008"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N409" r:id="rId1009"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I410" r:id="rId1010"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K410" r:id="rId1011"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N410" r:id="rId1012"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I411" r:id="rId1013"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K411" r:id="rId1014"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N411" r:id="rId1015"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I412" r:id="rId1016"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K412" r:id="rId1017"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N412" r:id="rId1018"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -31476,7 +31403,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A21"/>
+  <dimension ref="A1:A24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="120" customWidth="1" min="1" max="1"/>
@@ -31528,86 +31455,107 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr"/>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>4. 'Slow to load' was timed from an overseas server. Open the site on your own phone first; if it loads fine, skip that point.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="11" t="inlineStr">
+      <c r="A9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="11" t="inlineStr">
         <is>
           <t>Sending</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>4. Send from the AceAds business account, by hand. Max 20 new DMs per account per day.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>5. Never paste the identical message twice in a row. Personalise every one; Meta limits accounts that send copy-paste DMs.</t>
+          <t>5. Send from the AceAds business account, by hand. Max 20 new DMs per account per day.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>6. If they reply yes, ask AceAds for their preview (mockups/ in the repo), then send the screenshot and link.</t>
+          <t>6. Never paste the identical message twice in a row. Personalise every one; Meta limits accounts that send copy-paste DMs.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Set Status to 'Preview sent'.</t>
+          <t>7. If they reply yes, ask AceAds for their preview (mockups/ in the repo), then send the screenshot and link.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>7. One polite follow-up after 4-5 days, only if there was no reply. Then stop.</t>
+          <t xml:space="preserve">   Set Status to 'Preview sent'.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>8. If anyone says no or asks us to stop, set 'Not interested' and never contact them again.</t>
+          <t>8. One polite follow-up after 4-5 days, only if there was no reply. Then stop.</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr"/>
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>9. If anyone says no or asks us to stop, set 'Not interested' and never contact them again.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" s="11" t="inlineStr">
+      <c r="A17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="11" t="inlineStr">
         <is>
           <t>Do not</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>- Do not add these businesses to bulk email or automated DM tools.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>- Do not claim anything about their business you have not checked.</t>
+          <t>- Do not add these businesses to bulk email or automated DM tools.</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr"/>
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>- Email only to an address the business publishes on its own website, copied by hand. Say who we are, keep it</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  about their website, and end with: 'Not interested? Reply STOP and we won't contact you again.'</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>- Do not claim anything about their business you have not checked.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
         <is>
           <t>Source: OpenStreetMap (c) OpenStreetMap contributors, plus links found on the businesses' own websites.</t>
         </is>
